--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986731</v>
+        <v>128986495</v>
       </c>
       <c r="B2" t="n">
-        <v>98636</v>
+        <v>57824</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519104</v>
+        <v>518776</v>
       </c>
       <c r="R2" t="n">
-        <v>6982578</v>
+        <v>6982385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986495</v>
+        <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>57824</v>
+        <v>98636</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518776</v>
+        <v>519104</v>
       </c>
       <c r="R3" t="n">
-        <v>6982385</v>
+        <v>6982578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986513</v>
+        <v>128986473</v>
       </c>
       <c r="B7" t="n">
-        <v>92082</v>
+        <v>57561</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>102621</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519097</v>
+        <v>518872</v>
       </c>
       <c r="R7" t="n">
-        <v>6982582</v>
+        <v>6982457</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986706</v>
+        <v>128986513</v>
       </c>
       <c r="B8" t="n">
-        <v>80229</v>
+        <v>92082</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518979</v>
+        <v>519097</v>
       </c>
       <c r="R8" t="n">
-        <v>6982499</v>
+        <v>6982582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986473</v>
+        <v>128986701</v>
       </c>
       <c r="B9" t="n">
-        <v>57561</v>
+        <v>80230</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518872</v>
+        <v>519098</v>
       </c>
       <c r="R9" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1456,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986498</v>
+        <v>128986706</v>
       </c>
       <c r="B10" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519095</v>
+        <v>518979</v>
       </c>
       <c r="R10" t="n">
-        <v>6982524</v>
+        <v>6982499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986494</v>
+        <v>128986488</v>
       </c>
       <c r="B11" t="n">
-        <v>57824</v>
+        <v>80229</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519117</v>
+        <v>519036</v>
       </c>
       <c r="R11" t="n">
-        <v>6982667</v>
+        <v>6982781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1624,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986701</v>
+        <v>128986494</v>
       </c>
       <c r="B12" t="n">
-        <v>80230</v>
+        <v>57824</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519098</v>
+        <v>519117</v>
       </c>
       <c r="R12" t="n">
-        <v>6982579</v>
+        <v>6982667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1730,7 +1730,7 @@
       </c>
       <c r="AC12" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986488</v>
+        <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519036</v>
+        <v>519095</v>
       </c>
       <c r="R13" t="n">
-        <v>6982781</v>
+        <v>6982524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2048,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B16" t="n">
-        <v>57720</v>
+        <v>80264</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R16" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986515</v>
+        <v>128986485</v>
       </c>
       <c r="B17" t="n">
-        <v>80264</v>
+        <v>80229</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519023</v>
+        <v>519104</v>
       </c>
       <c r="R17" t="n">
-        <v>6982774</v>
+        <v>6982762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2247,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B18" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R18" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,6 +2313,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986732</v>
+        <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>98636</v>
+        <v>78881</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519137</v>
+        <v>518952</v>
       </c>
       <c r="R20" t="n">
-        <v>6982624</v>
+        <v>6982811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,7 +2543,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986505</v>
+        <v>128986732</v>
       </c>
       <c r="B21" t="n">
         <v>98636</v>
@@ -2583,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519089</v>
+        <v>519137</v>
       </c>
       <c r="R21" t="n">
-        <v>6982812</v>
+        <v>6982624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986730</v>
+        <v>128986505</v>
       </c>
       <c r="B22" t="n">
         <v>98636</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518956</v>
+        <v>519089</v>
       </c>
       <c r="R22" t="n">
-        <v>6982758</v>
+        <v>6982812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986729</v>
+        <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>78881</v>
+        <v>98636</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518952</v>
+        <v>518956</v>
       </c>
       <c r="R23" t="n">
-        <v>6982811</v>
+        <v>6982758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986716</v>
+        <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>80229</v>
+        <v>91508</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519149</v>
+        <v>518969</v>
       </c>
       <c r="R24" t="n">
-        <v>6982659</v>
+        <v>6982720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>91508</v>
+        <v>80230</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986489</v>
+        <v>128986716</v>
       </c>
       <c r="B26" t="n">
         <v>80229</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519023</v>
+        <v>519149</v>
       </c>
       <c r="R26" t="n">
-        <v>6982778</v>
+        <v>6982659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986475</v>
+        <v>128986489</v>
       </c>
       <c r="B27" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519074</v>
+        <v>519023</v>
       </c>
       <c r="R27" t="n">
-        <v>6982503</v>
+        <v>6982778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986510</v>
+        <v>128986726</v>
       </c>
       <c r="B28" t="n">
-        <v>56901</v>
+        <v>78881</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519116</v>
+        <v>519089</v>
       </c>
       <c r="R28" t="n">
-        <v>6982762</v>
+        <v>6982825</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986726</v>
+        <v>128986510</v>
       </c>
       <c r="B30" t="n">
-        <v>78881</v>
+        <v>56901</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519089</v>
+        <v>519116</v>
       </c>
       <c r="R30" t="n">
-        <v>6982825</v>
+        <v>6982762</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986500</v>
+        <v>128986463</v>
       </c>
       <c r="B31" t="n">
-        <v>98636</v>
+        <v>57720</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519090</v>
+        <v>519129</v>
       </c>
       <c r="R31" t="n">
-        <v>6982633</v>
+        <v>6982658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,6 +3589,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3615,32 +3620,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986463</v>
+        <v>128986500</v>
       </c>
       <c r="B32" t="n">
-        <v>57720</v>
+        <v>98636</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519129</v>
+        <v>519090</v>
       </c>
       <c r="R32" t="n">
-        <v>6982658</v>
+        <v>6982633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3686,11 +3691,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B34" t="n">
-        <v>57720</v>
+        <v>78881</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R34" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3916,10 +3911,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986728</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>78881</v>
+        <v>57720</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3927,21 +3922,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3951,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518928</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982835</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4207,10 +4207,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986457</v>
+        <v>128986723</v>
       </c>
       <c r="B38" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4218,21 +4218,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>518740</v>
+        <v>519011</v>
       </c>
       <c r="R38" t="n">
-        <v>6982426</v>
+        <v>6982694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4278,11 +4278,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4309,7 +4304,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986723</v>
+        <v>128986710</v>
       </c>
       <c r="B39" t="n">
         <v>80229</v>
@@ -4344,10 +4339,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519011</v>
+        <v>519088</v>
       </c>
       <c r="R39" t="n">
-        <v>6982694</v>
+        <v>6982506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4406,10 +4401,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986710</v>
+        <v>128986457</v>
       </c>
       <c r="B40" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4417,21 +4412,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4441,10 +4436,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519088</v>
+        <v>518740</v>
       </c>
       <c r="R40" t="n">
-        <v>6982506</v>
+        <v>6982426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,6 +4472,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986708</v>
+        <v>128986499</v>
       </c>
       <c r="B42" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518983</v>
+        <v>519106</v>
       </c>
       <c r="R42" t="n">
-        <v>6982481</v>
+        <v>6982616</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986499</v>
+        <v>128986502</v>
       </c>
       <c r="B43" t="n">
         <v>98636</v>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519106</v>
+        <v>519145</v>
       </c>
       <c r="R43" t="n">
-        <v>6982616</v>
+        <v>6982681</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986502</v>
+        <v>128986708</v>
       </c>
       <c r="B44" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519145</v>
+        <v>518983</v>
       </c>
       <c r="R44" t="n">
-        <v>6982681</v>
+        <v>6982481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986719</v>
+        <v>128986465</v>
       </c>
       <c r="B47" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519128</v>
+        <v>519109</v>
       </c>
       <c r="R47" t="n">
-        <v>6982688</v>
+        <v>6982756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,6 +5156,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5182,10 +5187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986493</v>
+        <v>128986461</v>
       </c>
       <c r="B48" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518940</v>
+        <v>519127</v>
       </c>
       <c r="R48" t="n">
-        <v>6982481</v>
+        <v>6982642</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5253,6 +5258,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5279,7 +5289,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986482</v>
+        <v>128986719</v>
       </c>
       <c r="B49" t="n">
         <v>80229</v>
@@ -5314,10 +5324,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519112</v>
+        <v>519128</v>
       </c>
       <c r="R49" t="n">
-        <v>6982533</v>
+        <v>6982688</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,7 +5386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986721</v>
+        <v>128986493</v>
       </c>
       <c r="B50" t="n">
         <v>80229</v>
@@ -5411,10 +5421,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519110</v>
+        <v>518940</v>
       </c>
       <c r="R50" t="n">
-        <v>6982770</v>
+        <v>6982481</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,10 +5483,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986465</v>
+        <v>128986482</v>
       </c>
       <c r="B51" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5494,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5518,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519109</v>
+        <v>519112</v>
       </c>
       <c r="R51" t="n">
-        <v>6982756</v>
+        <v>6982533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,11 +5554,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5575,10 +5580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986461</v>
+        <v>128986721</v>
       </c>
       <c r="B52" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5586,21 +5591,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5610,10 +5615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519127</v>
+        <v>519110</v>
       </c>
       <c r="R52" t="n">
-        <v>6982642</v>
+        <v>6982770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5646,11 +5651,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986477</v>
       </c>
       <c r="B57" t="n">
-        <v>80264</v>
+        <v>75019</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>6428</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>519000</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982781</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B58" t="n">
-        <v>75019</v>
+        <v>80264</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R58" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986497</v>
+        <v>128986486</v>
       </c>
       <c r="B59" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519074</v>
+        <v>519058</v>
       </c>
       <c r="R59" t="n">
-        <v>6982512</v>
+        <v>6982687</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,32 +6356,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986496</v>
+        <v>128986718</v>
       </c>
       <c r="B60" t="n">
-        <v>98636</v>
+        <v>80229</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518776</v>
+        <v>519135</v>
       </c>
       <c r="R60" t="n">
-        <v>6982502</v>
+        <v>6982678</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986486</v>
+        <v>128986715</v>
       </c>
       <c r="B61" t="n">
         <v>80229</v>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519058</v>
+        <v>519135</v>
       </c>
       <c r="R61" t="n">
-        <v>6982687</v>
+        <v>6982624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986718</v>
+        <v>128986724</v>
       </c>
       <c r="B62" t="n">
         <v>80229</v>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R62" t="n">
-        <v>6982678</v>
+        <v>6982673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,6 +6621,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6647,7 +6652,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986715</v>
+        <v>128986705</v>
       </c>
       <c r="B63" t="n">
         <v>80229</v>
@@ -6682,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519135</v>
+        <v>518809</v>
       </c>
       <c r="R63" t="n">
-        <v>6982624</v>
+        <v>6982489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6744,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986724</v>
+        <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6779,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518998</v>
+        <v>519074</v>
       </c>
       <c r="R64" t="n">
-        <v>6982673</v>
+        <v>6982512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6815,11 +6820,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986705</v>
+        <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>80229</v>
+        <v>98636</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518809</v>
+        <v>518776</v>
       </c>
       <c r="R65" t="n">
-        <v>6982489</v>
+        <v>6982502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>57720</v>
+        <v>79148</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R66" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986466</v>
+        <v>128986714</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>80229</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519061</v>
+        <v>519102</v>
       </c>
       <c r="R67" t="n">
-        <v>6982707</v>
+        <v>6982627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7116,11 +7111,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7147,32 +7137,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>79148</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7182,10 +7172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R68" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7218,6 +7208,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7244,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986714</v>
+        <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>80229</v>
+        <v>57720</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7255,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519102</v>
+        <v>519061</v>
       </c>
       <c r="R69" t="n">
-        <v>6982627</v>
+        <v>6982707</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,6 +7310,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986460</v>
+        <v>128986511</v>
       </c>
       <c r="B70" t="n">
-        <v>57720</v>
+        <v>56901</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7352,16 +7352,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519008</v>
+        <v>518948</v>
       </c>
       <c r="R70" t="n">
-        <v>6982491</v>
+        <v>6982848</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,11 +7412,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7443,27 +7438,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986511</v>
+        <v>128986472</v>
       </c>
       <c r="B71" t="n">
-        <v>56901</v>
+        <v>57561</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>102621</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518948</v>
+        <v>519067</v>
       </c>
       <c r="R71" t="n">
-        <v>6982848</v>
+        <v>6982817</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7540,27 +7535,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986472</v>
+        <v>128986460</v>
       </c>
       <c r="B72" t="n">
-        <v>57561</v>
+        <v>57720</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7575,10 +7570,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519067</v>
+        <v>519008</v>
       </c>
       <c r="R72" t="n">
-        <v>6982817</v>
+        <v>6982491</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7611,6 +7606,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7734,10 +7734,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986480</v>
+        <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7745,21 +7745,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519008</v>
+        <v>519099</v>
       </c>
       <c r="R74" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,10 +7831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986702</v>
+        <v>128986480</v>
       </c>
       <c r="B75" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7842,21 +7842,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519099</v>
+        <v>519008</v>
       </c>
       <c r="R75" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986699</v>
+        <v>128986727</v>
       </c>
       <c r="B83" t="n">
-        <v>79714</v>
+        <v>78881</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518952</v>
+        <v>519019</v>
       </c>
       <c r="R83" t="n">
-        <v>6982811</v>
+        <v>6982859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B84" t="n">
-        <v>78881</v>
+        <v>80229</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R84" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8775,6 +8775,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8801,32 +8806,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986703</v>
+        <v>128986517</v>
       </c>
       <c r="B85" t="n">
-        <v>80229</v>
+        <v>79380</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518965</v>
+        <v>518977</v>
       </c>
       <c r="R85" t="n">
-        <v>6982610</v>
+        <v>6982833</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8872,11 +8877,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986476</v>
+        <v>128986711</v>
       </c>
       <c r="B86" t="n">
-        <v>80230</v>
+        <v>80229</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519017</v>
+        <v>519123</v>
       </c>
       <c r="R86" t="n">
-        <v>6982756</v>
+        <v>6982555</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9000,32 +9000,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986517</v>
+        <v>128986699</v>
       </c>
       <c r="B87" t="n">
-        <v>79380</v>
+        <v>79714</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>229821</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518977</v>
+        <v>518952</v>
       </c>
       <c r="R87" t="n">
-        <v>6982833</v>
+        <v>6982811</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986711</v>
+        <v>128986476</v>
       </c>
       <c r="B88" t="n">
-        <v>80229</v>
+        <v>80230</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9108,21 +9108,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519123</v>
+        <v>519017</v>
       </c>
       <c r="R88" t="n">
-        <v>6982555</v>
+        <v>6982756</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986495</v>
+        <v>128986731</v>
       </c>
       <c r="B2" t="n">
-        <v>57824</v>
+        <v>98643</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518776</v>
+        <v>519104</v>
       </c>
       <c r="R2" t="n">
-        <v>6982385</v>
+        <v>6982578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986731</v>
+        <v>128986495</v>
       </c>
       <c r="B3" t="n">
-        <v>98636</v>
+        <v>57827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519104</v>
+        <v>518776</v>
       </c>
       <c r="R3" t="n">
-        <v>6982578</v>
+        <v>6982385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>79714</v>
+        <v>79619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B5" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R5" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R6" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986473</v>
+        <v>128986513</v>
       </c>
       <c r="B7" t="n">
-        <v>57561</v>
+        <v>92087</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>102621</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518872</v>
+        <v>519097</v>
       </c>
       <c r="R7" t="n">
-        <v>6982457</v>
+        <v>6982582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986513</v>
+        <v>128986473</v>
       </c>
       <c r="B8" t="n">
-        <v>92082</v>
+        <v>57564</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519097</v>
+        <v>518872</v>
       </c>
       <c r="R8" t="n">
-        <v>6982582</v>
+        <v>6982457</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986701</v>
+        <v>128986494</v>
       </c>
       <c r="B9" t="n">
-        <v>80230</v>
+        <v>57827</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519098</v>
+        <v>519117</v>
       </c>
       <c r="R9" t="n">
-        <v>6982579</v>
+        <v>6982667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1434,7 +1434,7 @@
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>På gran</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986706</v>
+        <v>128986701</v>
       </c>
       <c r="B10" t="n">
-        <v>80229</v>
+        <v>80135</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518979</v>
+        <v>519098</v>
       </c>
       <c r="R10" t="n">
-        <v>6982499</v>
+        <v>6982579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1563,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986488</v>
+        <v>128986706</v>
       </c>
       <c r="B11" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519036</v>
+        <v>518979</v>
       </c>
       <c r="R11" t="n">
-        <v>6982781</v>
+        <v>6982499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986494</v>
+        <v>128986488</v>
       </c>
       <c r="B12" t="n">
-        <v>57824</v>
+        <v>80134</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519117</v>
+        <v>519036</v>
       </c>
       <c r="R12" t="n">
-        <v>6982667</v>
+        <v>6982781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,7 +1760,7 @@
         <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1857,7 +1857,7 @@
         <v>128986707</v>
       </c>
       <c r="B14" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986478</v>
+        <v>128986485</v>
       </c>
       <c r="B15" t="n">
-        <v>75131</v>
+        <v>80134</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518949</v>
+        <v>519104</v>
       </c>
       <c r="R15" t="n">
-        <v>6982601</v>
+        <v>6982762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2051,7 +2051,7 @@
         <v>128986515</v>
       </c>
       <c r="B16" t="n">
-        <v>80264</v>
+        <v>80169</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R17" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,10 +2247,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986458</v>
+        <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518751</v>
+        <v>518944</v>
       </c>
       <c r="R18" t="n">
-        <v>6982439</v>
+        <v>6982537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2322,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986468</v>
+        <v>128986478</v>
       </c>
       <c r="B19" t="n">
-        <v>57720</v>
+        <v>75134</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518944</v>
+        <v>518949</v>
       </c>
       <c r="R19" t="n">
-        <v>6982537</v>
+        <v>6982601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2449,7 +2449,7 @@
         <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>78881</v>
+        <v>78786</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986732</v>
+        <v>128986730</v>
       </c>
       <c r="B21" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519137</v>
+        <v>518956</v>
       </c>
       <c r="R21" t="n">
-        <v>6982624</v>
+        <v>6982758</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2614,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986505</v>
+        <v>128986732</v>
       </c>
       <c r="B22" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519089</v>
+        <v>519137</v>
       </c>
       <c r="R22" t="n">
-        <v>6982812</v>
+        <v>6982624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986505</v>
       </c>
       <c r="B23" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>519089</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2842,7 +2842,7 @@
         <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>91508</v>
+        <v>91513</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986716</v>
       </c>
       <c r="B25" t="n">
-        <v>80230</v>
+        <v>80134</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>519149</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986716</v>
+        <v>128986489</v>
       </c>
       <c r="B26" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519149</v>
+        <v>519023</v>
       </c>
       <c r="R26" t="n">
-        <v>6982659</v>
+        <v>6982778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986489</v>
+        <v>128986475</v>
       </c>
       <c r="B27" t="n">
-        <v>80229</v>
+        <v>80135</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519023</v>
+        <v>519074</v>
       </c>
       <c r="R27" t="n">
-        <v>6982778</v>
+        <v>6982503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986726</v>
+        <v>128986492</v>
       </c>
       <c r="B28" t="n">
-        <v>78881</v>
+        <v>80134</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519089</v>
+        <v>518959</v>
       </c>
       <c r="R28" t="n">
-        <v>6982825</v>
+        <v>6982485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986492</v>
+        <v>128986726</v>
       </c>
       <c r="B29" t="n">
-        <v>80229</v>
+        <v>78786</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518959</v>
+        <v>519089</v>
       </c>
       <c r="R29" t="n">
-        <v>6982485</v>
+        <v>6982825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,7 +3424,7 @@
         <v>128986510</v>
       </c>
       <c r="B30" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986463</v>
+        <v>128986500</v>
       </c>
       <c r="B31" t="n">
-        <v>57720</v>
+        <v>98643</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519129</v>
+        <v>519090</v>
       </c>
       <c r="R31" t="n">
-        <v>6982658</v>
+        <v>6982633</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,11 +3589,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3620,10 +3615,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986500</v>
+        <v>128986501</v>
       </c>
       <c r="B32" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519090</v>
+        <v>519091</v>
       </c>
       <c r="R32" t="n">
-        <v>6982633</v>
+        <v>6982620</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,32 +3712,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986501</v>
+        <v>128986463</v>
       </c>
       <c r="B33" t="n">
-        <v>98636</v>
+        <v>57723</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519091</v>
+        <v>519129</v>
       </c>
       <c r="R33" t="n">
-        <v>6982620</v>
+        <v>6982658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3788,6 +3783,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986728</v>
+        <v>128986467</v>
       </c>
       <c r="B34" t="n">
-        <v>78881</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518928</v>
+        <v>518933</v>
       </c>
       <c r="R34" t="n">
-        <v>6982835</v>
+        <v>6982538</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,6 +3885,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3911,10 +3916,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B35" t="n">
-        <v>57720</v>
+        <v>78786</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,21 +3927,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,11 +3987,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4016,7 +4016,7 @@
         <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986713</v>
+        <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519091</v>
+        <v>518740</v>
       </c>
       <c r="R37" t="n">
-        <v>6982582</v>
+        <v>6982426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,6 +4181,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4207,10 +4212,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986723</v>
+        <v>128986710</v>
       </c>
       <c r="B38" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519011</v>
+        <v>519088</v>
       </c>
       <c r="R38" t="n">
-        <v>6982694</v>
+        <v>6982506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,10 +4309,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986710</v>
+        <v>128986713</v>
       </c>
       <c r="B39" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519088</v>
+        <v>519091</v>
       </c>
       <c r="R39" t="n">
-        <v>6982506</v>
+        <v>6982582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4401,10 +4406,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986457</v>
+        <v>128986723</v>
       </c>
       <c r="B40" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,21 +4417,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518740</v>
+        <v>519011</v>
       </c>
       <c r="R40" t="n">
-        <v>6982426</v>
+        <v>6982694</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4472,11 +4477,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4506,7 +4506,7 @@
         <v>128986509</v>
       </c>
       <c r="B41" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>128986499</v>
       </c>
       <c r="B42" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986502</v>
+        <v>128986708</v>
       </c>
       <c r="B43" t="n">
-        <v>98636</v>
+        <v>80134</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519145</v>
+        <v>518983</v>
       </c>
       <c r="R43" t="n">
-        <v>6982681</v>
+        <v>6982481</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,10 +4794,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986708</v>
+        <v>128986722</v>
       </c>
       <c r="B44" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518983</v>
+        <v>518975</v>
       </c>
       <c r="R44" t="n">
-        <v>6982481</v>
+        <v>6982829</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986722</v>
+        <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>80229</v>
+        <v>98643</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518975</v>
+        <v>519145</v>
       </c>
       <c r="R45" t="n">
-        <v>6982829</v>
+        <v>6982681</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986474</v>
+        <v>128986493</v>
       </c>
       <c r="B46" t="n">
-        <v>80230</v>
+        <v>80134</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518955</v>
+        <v>518940</v>
       </c>
       <c r="R46" t="n">
-        <v>6982588</v>
+        <v>6982481</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986465</v>
+        <v>128986482</v>
       </c>
       <c r="B47" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519109</v>
+        <v>519112</v>
       </c>
       <c r="R47" t="n">
-        <v>6982756</v>
+        <v>6982533</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,11 +5156,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5187,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986461</v>
+        <v>128986721</v>
       </c>
       <c r="B48" t="n">
-        <v>57720</v>
+        <v>80134</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5198,21 +5193,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519127</v>
+        <v>519110</v>
       </c>
       <c r="R48" t="n">
-        <v>6982642</v>
+        <v>6982770</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5258,11 +5253,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5289,10 +5279,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986719</v>
+        <v>128986484</v>
       </c>
       <c r="B49" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5324,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519128</v>
+        <v>519153</v>
       </c>
       <c r="R49" t="n">
-        <v>6982688</v>
+        <v>6982677</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5386,10 +5376,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986493</v>
+        <v>128986465</v>
       </c>
       <c r="B50" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5397,21 +5387,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5421,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518940</v>
+        <v>519109</v>
       </c>
       <c r="R50" t="n">
-        <v>6982481</v>
+        <v>6982756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5457,6 +5447,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5483,10 +5478,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986482</v>
+        <v>128986461</v>
       </c>
       <c r="B51" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5494,21 +5489,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5518,10 +5513,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519112</v>
+        <v>519127</v>
       </c>
       <c r="R51" t="n">
-        <v>6982533</v>
+        <v>6982642</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5554,6 +5549,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5580,10 +5580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986721</v>
+        <v>128986474</v>
       </c>
       <c r="B52" t="n">
-        <v>80229</v>
+        <v>80135</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5591,21 +5591,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5615,10 +5615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519110</v>
+        <v>518955</v>
       </c>
       <c r="R52" t="n">
-        <v>6982770</v>
+        <v>6982588</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5677,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986484</v>
+        <v>128986719</v>
       </c>
       <c r="B53" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519153</v>
+        <v>519128</v>
       </c>
       <c r="R53" t="n">
-        <v>6982677</v>
+        <v>6982688</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5777,7 +5777,7 @@
         <v>128986490</v>
       </c>
       <c r="B54" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5871,10 +5871,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128986717</v>
+        <v>128986481</v>
       </c>
       <c r="B55" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519151</v>
+        <v>519067</v>
       </c>
       <c r="R55" t="n">
-        <v>6982660</v>
+        <v>6982461</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5968,10 +5968,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128986481</v>
+        <v>128986717</v>
       </c>
       <c r="B56" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519067</v>
+        <v>519151</v>
       </c>
       <c r="R56" t="n">
-        <v>6982461</v>
+        <v>6982660</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6068,7 +6068,7 @@
         <v>128986477</v>
       </c>
       <c r="B57" t="n">
-        <v>75019</v>
+        <v>75022</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986514</v>
+        <v>128986486</v>
       </c>
       <c r="B58" t="n">
-        <v>80264</v>
+        <v>80134</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519096</v>
+        <v>519058</v>
       </c>
       <c r="R58" t="n">
-        <v>6982528</v>
+        <v>6982687</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,10 +6259,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986486</v>
+        <v>128986724</v>
       </c>
       <c r="B59" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519058</v>
+        <v>518998</v>
       </c>
       <c r="R59" t="n">
-        <v>6982687</v>
+        <v>6982673</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6330,6 +6330,11 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6359,7 +6364,7 @@
         <v>128986718</v>
       </c>
       <c r="B60" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6456,7 +6461,7 @@
         <v>128986715</v>
       </c>
       <c r="B61" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6550,10 +6555,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986724</v>
+        <v>128986705</v>
       </c>
       <c r="B62" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518998</v>
+        <v>518809</v>
       </c>
       <c r="R62" t="n">
-        <v>6982673</v>
+        <v>6982489</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,11 +6626,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,32 +6652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986705</v>
+        <v>128986514</v>
       </c>
       <c r="B63" t="n">
-        <v>80229</v>
+        <v>80169</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518809</v>
+        <v>519096</v>
       </c>
       <c r="R63" t="n">
-        <v>6982489</v>
+        <v>6982528</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
         <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986479</v>
+        <v>128986714</v>
       </c>
       <c r="B66" t="n">
-        <v>79148</v>
+        <v>80134</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518960</v>
+        <v>519102</v>
       </c>
       <c r="R66" t="n">
-        <v>6982834</v>
+        <v>6982627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986714</v>
+        <v>128986466</v>
       </c>
       <c r="B67" t="n">
-        <v>80229</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519102</v>
+        <v>519061</v>
       </c>
       <c r="R67" t="n">
-        <v>6982627</v>
+        <v>6982707</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7137,32 +7142,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>79053</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7172,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R68" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7208,11 +7213,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986466</v>
+        <v>128986470</v>
       </c>
       <c r="B69" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519061</v>
+        <v>518794</v>
       </c>
       <c r="R69" t="n">
-        <v>6982707</v>
+        <v>6982445</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7344,7 +7344,7 @@
         <v>128986511</v>
       </c>
       <c r="B70" t="n">
-        <v>56901</v>
+        <v>56904</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7438,27 +7438,27 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986472</v>
+        <v>128986460</v>
       </c>
       <c r="B71" t="n">
-        <v>57561</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519067</v>
+        <v>519008</v>
       </c>
       <c r="R71" t="n">
-        <v>6982817</v>
+        <v>6982491</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,6 +7509,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7535,27 +7540,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986460</v>
+        <v>128986472</v>
       </c>
       <c r="B72" t="n">
-        <v>57720</v>
+        <v>57564</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7570,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519008</v>
+        <v>519067</v>
       </c>
       <c r="R72" t="n">
-        <v>6982491</v>
+        <v>6982817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7606,11 +7611,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>80230</v>
+        <v>80135</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>128986480</v>
       </c>
       <c r="B75" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>128986491</v>
       </c>
       <c r="B76" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         <v>128986712</v>
       </c>
       <c r="B78" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986720</v>
+        <v>128986725</v>
       </c>
       <c r="B79" t="n">
-        <v>80229</v>
+        <v>78786</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519130</v>
+        <v>519052</v>
       </c>
       <c r="R79" t="n">
-        <v>6982756</v>
+        <v>6982433</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986725</v>
+        <v>128986720</v>
       </c>
       <c r="B80" t="n">
-        <v>78881</v>
+        <v>80134</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519052</v>
+        <v>519130</v>
       </c>
       <c r="R80" t="n">
-        <v>6982433</v>
+        <v>6982756</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8416,7 +8416,7 @@
         <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98636</v>
+        <v>98643</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986727</v>
+        <v>128986476</v>
       </c>
       <c r="B83" t="n">
-        <v>78881</v>
+        <v>80135</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519019</v>
+        <v>519017</v>
       </c>
       <c r="R83" t="n">
-        <v>6982859</v>
+        <v>6982756</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986703</v>
+        <v>128986699</v>
       </c>
       <c r="B84" t="n">
-        <v>80229</v>
+        <v>79619</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518965</v>
+        <v>518952</v>
       </c>
       <c r="R84" t="n">
-        <v>6982610</v>
+        <v>6982811</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8775,11 +8775,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8806,32 +8801,32 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986517</v>
+        <v>128986727</v>
       </c>
       <c r="B85" t="n">
-        <v>79380</v>
+        <v>78786</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6459</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518977</v>
+        <v>519019</v>
       </c>
       <c r="R85" t="n">
-        <v>6982833</v>
+        <v>6982859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8903,10 +8898,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986711</v>
+        <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>80229</v>
+        <v>80134</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8938,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519123</v>
+        <v>518965</v>
       </c>
       <c r="R86" t="n">
-        <v>6982555</v>
+        <v>6982610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,6 +8969,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9000,32 +9000,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986699</v>
+        <v>128986517</v>
       </c>
       <c r="B87" t="n">
-        <v>79714</v>
+        <v>79285</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>229821</v>
+        <v>6459</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518952</v>
+        <v>518977</v>
       </c>
       <c r="R87" t="n">
-        <v>6982811</v>
+        <v>6982833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986476</v>
+        <v>128986711</v>
       </c>
       <c r="B88" t="n">
-        <v>80230</v>
+        <v>80134</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9108,21 +9108,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519017</v>
+        <v>519123</v>
       </c>
       <c r="R88" t="n">
-        <v>6982756</v>
+        <v>6982555</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9197,7 +9197,7 @@
         <v>128986464</v>
       </c>
       <c r="B89" t="n">
-        <v>57720</v>
+        <v>57723</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986495</v>
+        <v>128986455</v>
       </c>
       <c r="B2" t="n">
-        <v>57827</v>
+        <v>79624</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518776</v>
+        <v>518927</v>
       </c>
       <c r="R2" t="n">
-        <v>6982385</v>
+        <v>6982838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986455</v>
+        <v>128986495</v>
       </c>
       <c r="B3" t="n">
-        <v>79624</v>
+        <v>57827</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518927</v>
+        <v>518776</v>
       </c>
       <c r="R3" t="n">
-        <v>6982838</v>
+        <v>6982385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986503</v>
+        <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>98651</v>
+        <v>80140</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519118</v>
+        <v>519099</v>
       </c>
       <c r="R74" t="n">
-        <v>6982684</v>
+        <v>6982579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,10 +7831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986702</v>
+        <v>128986480</v>
       </c>
       <c r="B75" t="n">
-        <v>80140</v>
+        <v>80139</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7842,21 +7842,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519099</v>
+        <v>519008</v>
       </c>
       <c r="R75" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986480</v>
+        <v>128986491</v>
       </c>
       <c r="B76" t="n">
         <v>80139</v>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519008</v>
+        <v>518942</v>
       </c>
       <c r="R76" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8025,32 +8025,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986491</v>
+        <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>80139</v>
+        <v>98651</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518942</v>
+        <v>519118</v>
       </c>
       <c r="R77" t="n">
-        <v>6982579</v>
+        <v>6982684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986464</v>
+        <v>128986476</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519152</v>
+        <v>519017</v>
       </c>
       <c r="R83" t="n">
-        <v>6982692</v>
+        <v>6982756</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,11 +8678,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8806,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986476</v>
+        <v>128986464</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519017</v>
+        <v>519152</v>
       </c>
       <c r="R85" t="n">
-        <v>6982756</v>
+        <v>6982692</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8877,6 +8872,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -872,7 +872,7 @@
         <v>128986731</v>
       </c>
       <c r="B4" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B5" t="n">
-        <v>98651</v>
+        <v>57723</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R5" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R6" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986701</v>
+        <v>128986513</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>92100</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519098</v>
+        <v>519097</v>
       </c>
       <c r="R7" t="n">
-        <v>6982579</v>
+        <v>6982582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986498</v>
+        <v>128986494</v>
       </c>
       <c r="B8" t="n">
-        <v>98651</v>
+        <v>57827</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519095</v>
+        <v>519117</v>
       </c>
       <c r="R8" t="n">
-        <v>6982524</v>
+        <v>6982667</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1338,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986513</v>
+        <v>128986701</v>
       </c>
       <c r="B9" t="n">
-        <v>92095</v>
+        <v>80140</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519097</v>
+        <v>519098</v>
       </c>
       <c r="R9" t="n">
-        <v>6982582</v>
+        <v>6982579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1435,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1752,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986494</v>
+        <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>57827</v>
+        <v>98656</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519117</v>
+        <v>519095</v>
       </c>
       <c r="R13" t="n">
-        <v>6982667</v>
+        <v>6982524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986478</v>
+        <v>128986458</v>
       </c>
       <c r="B15" t="n">
-        <v>75139</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518949</v>
+        <v>518751</v>
       </c>
       <c r="R15" t="n">
-        <v>6982601</v>
+        <v>6982439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,6 +2022,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,7 +2053,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986458</v>
+        <v>128986468</v>
       </c>
       <c r="B16" t="n">
         <v>57723</v>
@@ -2083,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518751</v>
+        <v>518944</v>
       </c>
       <c r="R16" t="n">
-        <v>6982439</v>
+        <v>6982537</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2123,7 +2128,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986468</v>
+        <v>128986478</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>75139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518944</v>
+        <v>518949</v>
       </c>
       <c r="R17" t="n">
-        <v>6982537</v>
+        <v>6982601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2221,11 +2226,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986729</v>
+        <v>128986732</v>
       </c>
       <c r="B20" t="n">
-        <v>78791</v>
+        <v>98656</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518952</v>
+        <v>519137</v>
       </c>
       <c r="R20" t="n">
-        <v>6982811</v>
+        <v>6982624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986732</v>
+        <v>128986505</v>
       </c>
       <c r="B21" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519137</v>
+        <v>519089</v>
       </c>
       <c r="R21" t="n">
-        <v>6982624</v>
+        <v>6982812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986505</v>
+        <v>128986730</v>
       </c>
       <c r="B22" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519089</v>
+        <v>518956</v>
       </c>
       <c r="R22" t="n">
-        <v>6982812</v>
+        <v>6982758</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986729</v>
       </c>
       <c r="B23" t="n">
-        <v>98651</v>
+        <v>78791</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>518952</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>91520</v>
+        <v>80140</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R24" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986716</v>
       </c>
       <c r="B25" t="n">
-        <v>80140</v>
+        <v>80139</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>519149</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986716</v>
+        <v>128986489</v>
       </c>
       <c r="B26" t="n">
         <v>80139</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519149</v>
+        <v>519023</v>
       </c>
       <c r="R26" t="n">
-        <v>6982659</v>
+        <v>6982778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986489</v>
+        <v>128986700</v>
       </c>
       <c r="B27" t="n">
-        <v>80139</v>
+        <v>91523</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519023</v>
+        <v>518969</v>
       </c>
       <c r="R27" t="n">
-        <v>6982778</v>
+        <v>6982720</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986463</v>
+        <v>128986501</v>
       </c>
       <c r="B28" t="n">
-        <v>57723</v>
+        <v>98656</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519129</v>
+        <v>519091</v>
       </c>
       <c r="R28" t="n">
-        <v>6982658</v>
+        <v>6982620</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986492</v>
+        <v>128986726</v>
       </c>
       <c r="B29" t="n">
-        <v>80139</v>
+        <v>78791</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518959</v>
+        <v>519089</v>
       </c>
       <c r="R29" t="n">
-        <v>6982485</v>
+        <v>6982825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3426,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986726</v>
+        <v>128986492</v>
       </c>
       <c r="B30" t="n">
-        <v>78791</v>
+        <v>80139</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519089</v>
+        <v>518959</v>
       </c>
       <c r="R30" t="n">
-        <v>6982825</v>
+        <v>6982485</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3523,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986510</v>
+        <v>128986463</v>
       </c>
       <c r="B31" t="n">
-        <v>56904</v>
+        <v>57723</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,16 +3529,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3558,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519116</v>
+        <v>519129</v>
       </c>
       <c r="R31" t="n">
-        <v>6982762</v>
+        <v>6982658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3594,6 +3589,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3620,32 +3620,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986500</v>
+        <v>128986510</v>
       </c>
       <c r="B32" t="n">
-        <v>98651</v>
+        <v>56904</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519090</v>
+        <v>519116</v>
       </c>
       <c r="R32" t="n">
-        <v>6982633</v>
+        <v>6982762</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986501</v>
+        <v>128986500</v>
       </c>
       <c r="B33" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519091</v>
+        <v>519090</v>
       </c>
       <c r="R33" t="n">
-        <v>6982620</v>
+        <v>6982633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>78791</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R34" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3916,10 +3911,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986728</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>78791</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3927,21 +3922,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3951,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518928</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982835</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4016,7 +4016,7 @@
         <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986722</v>
+        <v>128986509</v>
       </c>
       <c r="B41" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518975</v>
+        <v>518970</v>
       </c>
       <c r="R41" t="n">
-        <v>6982829</v>
+        <v>6982749</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986708</v>
+        <v>128986499</v>
       </c>
       <c r="B42" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518983</v>
+        <v>519106</v>
       </c>
       <c r="R42" t="n">
-        <v>6982481</v>
+        <v>6982616</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986509</v>
+        <v>128986502</v>
       </c>
       <c r="B43" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518970</v>
+        <v>519145</v>
       </c>
       <c r="R43" t="n">
-        <v>6982749</v>
+        <v>6982681</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986499</v>
+        <v>128986708</v>
       </c>
       <c r="B44" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519106</v>
+        <v>518983</v>
       </c>
       <c r="R44" t="n">
-        <v>6982616</v>
+        <v>6982481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986502</v>
+        <v>128986722</v>
       </c>
       <c r="B45" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519145</v>
+        <v>518975</v>
       </c>
       <c r="R45" t="n">
-        <v>6982681</v>
+        <v>6982829</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986474</v>
+        <v>128986719</v>
       </c>
       <c r="B46" t="n">
-        <v>80140</v>
+        <v>80139</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518955</v>
+        <v>519128</v>
       </c>
       <c r="R46" t="n">
-        <v>6982588</v>
+        <v>6982688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986719</v>
+        <v>128986493</v>
       </c>
       <c r="B47" t="n">
         <v>80139</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519128</v>
+        <v>518940</v>
       </c>
       <c r="R47" t="n">
-        <v>6982688</v>
+        <v>6982481</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986493</v>
+        <v>128986482</v>
       </c>
       <c r="B48" t="n">
         <v>80139</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518940</v>
+        <v>519112</v>
       </c>
       <c r="R48" t="n">
-        <v>6982481</v>
+        <v>6982533</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986482</v>
+        <v>128986721</v>
       </c>
       <c r="B49" t="n">
         <v>80139</v>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519112</v>
+        <v>519110</v>
       </c>
       <c r="R49" t="n">
-        <v>6982533</v>
+        <v>6982770</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986721</v>
+        <v>128986484</v>
       </c>
       <c r="B50" t="n">
         <v>80139</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519110</v>
+        <v>519153</v>
       </c>
       <c r="R50" t="n">
-        <v>6982770</v>
+        <v>6982677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986484</v>
+        <v>128986465</v>
       </c>
       <c r="B51" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519153</v>
+        <v>519109</v>
       </c>
       <c r="R51" t="n">
-        <v>6982677</v>
+        <v>6982756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,6 +5544,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5570,7 +5575,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986465</v>
+        <v>128986461</v>
       </c>
       <c r="B52" t="n">
         <v>57723</v>
@@ -5605,10 +5610,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519109</v>
+        <v>519127</v>
       </c>
       <c r="R52" t="n">
-        <v>6982756</v>
+        <v>6982642</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5645,7 +5650,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5672,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986461</v>
+        <v>128986474</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519127</v>
+        <v>518955</v>
       </c>
       <c r="R53" t="n">
-        <v>6982642</v>
+        <v>6982588</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,11 +5748,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5871,7 +5871,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128986481</v>
+        <v>128986717</v>
       </c>
       <c r="B55" t="n">
         <v>80139</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519067</v>
+        <v>519151</v>
       </c>
       <c r="R55" t="n">
-        <v>6982461</v>
+        <v>6982660</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5968,7 +5968,7 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128986717</v>
+        <v>128986481</v>
       </c>
       <c r="B56" t="n">
         <v>80139</v>
@@ -6003,10 +6003,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519151</v>
+        <v>519067</v>
       </c>
       <c r="R56" t="n">
-        <v>6982660</v>
+        <v>6982461</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986477</v>
       </c>
       <c r="B57" t="n">
-        <v>80174</v>
+        <v>75027</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>6428</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>519000</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982781</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B58" t="n">
-        <v>75027</v>
+        <v>80174</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R58" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986715</v>
+        <v>128986486</v>
       </c>
       <c r="B59" t="n">
         <v>80139</v>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519135</v>
+        <v>519058</v>
       </c>
       <c r="R59" t="n">
-        <v>6982624</v>
+        <v>6982687</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986724</v>
+        <v>128986718</v>
       </c>
       <c r="B60" t="n">
         <v>80139</v>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518998</v>
+        <v>519135</v>
       </c>
       <c r="R60" t="n">
-        <v>6982673</v>
+        <v>6982678</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6427,11 +6427,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6458,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986705</v>
+        <v>128986715</v>
       </c>
       <c r="B61" t="n">
         <v>80139</v>
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518809</v>
+        <v>519135</v>
       </c>
       <c r="R61" t="n">
-        <v>6982489</v>
+        <v>6982624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,32 +6550,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986497</v>
+        <v>128986724</v>
       </c>
       <c r="B62" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519074</v>
+        <v>518998</v>
       </c>
       <c r="R62" t="n">
-        <v>6982512</v>
+        <v>6982673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6626,6 +6621,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,32 +6652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986496</v>
+        <v>128986705</v>
       </c>
       <c r="B63" t="n">
-        <v>98651</v>
+        <v>80139</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518776</v>
+        <v>518809</v>
       </c>
       <c r="R63" t="n">
-        <v>6982502</v>
+        <v>6982489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986486</v>
+        <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519058</v>
+        <v>519074</v>
       </c>
       <c r="R64" t="n">
-        <v>6982687</v>
+        <v>6982512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986718</v>
+        <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>80139</v>
+        <v>98656</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519135</v>
+        <v>518776</v>
       </c>
       <c r="R65" t="n">
-        <v>6982678</v>
+        <v>6982502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>79058</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R66" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,7 +7040,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986466</v>
+        <v>128986470</v>
       </c>
       <c r="B67" t="n">
         <v>57723</v>
@@ -7080,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519061</v>
+        <v>518794</v>
       </c>
       <c r="R67" t="n">
-        <v>6982707</v>
+        <v>6982445</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7120,7 +7115,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7147,32 +7142,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986479</v>
+        <v>128986466</v>
       </c>
       <c r="B68" t="n">
-        <v>79058</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7182,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518960</v>
+        <v>519061</v>
       </c>
       <c r="R68" t="n">
-        <v>6982834</v>
+        <v>6982707</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7218,6 +7213,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128986712</v>
+        <v>128986725</v>
       </c>
       <c r="B78" t="n">
-        <v>80139</v>
+        <v>78791</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519121</v>
+        <v>519052</v>
       </c>
       <c r="R78" t="n">
-        <v>6982559</v>
+        <v>6982433</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986720</v>
+        <v>128986712</v>
       </c>
       <c r="B79" t="n">
         <v>80139</v>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519130</v>
+        <v>519121</v>
       </c>
       <c r="R79" t="n">
-        <v>6982756</v>
+        <v>6982559</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986725</v>
+        <v>128986720</v>
       </c>
       <c r="B80" t="n">
-        <v>78791</v>
+        <v>80139</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519052</v>
+        <v>519130</v>
       </c>
       <c r="R80" t="n">
-        <v>6982433</v>
+        <v>6982756</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98651</v>
+        <v>98656</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986476</v>
+        <v>128986464</v>
       </c>
       <c r="B83" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519017</v>
+        <v>519152</v>
       </c>
       <c r="R83" t="n">
-        <v>6982756</v>
+        <v>6982692</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,6 +8678,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8801,10 +8806,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986464</v>
+        <v>128986727</v>
       </c>
       <c r="B85" t="n">
-        <v>57723</v>
+        <v>78791</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8817,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519152</v>
+        <v>519019</v>
       </c>
       <c r="R85" t="n">
-        <v>6982692</v>
+        <v>6982859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8872,11 +8877,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>78791</v>
+        <v>80139</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R86" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,6 +8974,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9000,32 +9005,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986703</v>
+        <v>128986517</v>
       </c>
       <c r="B87" t="n">
-        <v>80139</v>
+        <v>79290</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518965</v>
+        <v>518977</v>
       </c>
       <c r="R87" t="n">
-        <v>6982610</v>
+        <v>6982833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9071,11 +9076,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9102,32 +9102,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986517</v>
+        <v>128986711</v>
       </c>
       <c r="B88" t="n">
-        <v>79290</v>
+        <v>80139</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518977</v>
+        <v>519123</v>
       </c>
       <c r="R88" t="n">
-        <v>6982833</v>
+        <v>6982555</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9199,10 +9199,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986711</v>
+        <v>128986476</v>
       </c>
       <c r="B89" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519123</v>
+        <v>519017</v>
       </c>
       <c r="R89" t="n">
-        <v>6982555</v>
+        <v>6982756</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986455</v>
+        <v>128986495</v>
       </c>
       <c r="B2" t="n">
-        <v>79624</v>
+        <v>57827</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518927</v>
+        <v>518776</v>
       </c>
       <c r="R2" t="n">
-        <v>6982838</v>
+        <v>6982385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986495</v>
+        <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>57827</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518776</v>
+        <v>519104</v>
       </c>
       <c r="R3" t="n">
-        <v>6982385</v>
+        <v>6982578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>98656</v>
+        <v>79625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R4" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128986513</v>
       </c>
       <c r="B7" t="n">
-        <v>92100</v>
+        <v>92103</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986494</v>
+        <v>128986701</v>
       </c>
       <c r="B8" t="n">
-        <v>57827</v>
+        <v>80141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103031</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519117</v>
+        <v>519098</v>
       </c>
       <c r="R8" t="n">
-        <v>6982667</v>
+        <v>6982579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1337,7 +1337,7 @@
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>3st</t>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,7 +1364,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986701</v>
+        <v>128986706</v>
       </c>
       <c r="B9" t="n">
         <v>80140</v>
@@ -1375,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519098</v>
+        <v>518979</v>
       </c>
       <c r="R9" t="n">
-        <v>6982579</v>
+        <v>6982499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1466,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986706</v>
+        <v>128986488</v>
       </c>
       <c r="B10" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518979</v>
+        <v>519036</v>
       </c>
       <c r="R10" t="n">
-        <v>6982499</v>
+        <v>6982781</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986488</v>
+        <v>128986473</v>
       </c>
       <c r="B11" t="n">
-        <v>80139</v>
+        <v>57564</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519036</v>
+        <v>518872</v>
       </c>
       <c r="R11" t="n">
-        <v>6982781</v>
+        <v>6982457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986473</v>
+        <v>128986498</v>
       </c>
       <c r="B12" t="n">
-        <v>57564</v>
+        <v>98659</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518872</v>
+        <v>519095</v>
       </c>
       <c r="R12" t="n">
-        <v>6982457</v>
+        <v>6982524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1757,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986498</v>
+        <v>128986494</v>
       </c>
       <c r="B13" t="n">
-        <v>98656</v>
+        <v>57827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519095</v>
+        <v>519117</v>
       </c>
       <c r="R13" t="n">
-        <v>6982524</v>
+        <v>6982667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1857,7 +1857,7 @@
         <v>128986707</v>
       </c>
       <c r="B14" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R15" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986468</v>
+        <v>128986485</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518944</v>
+        <v>519104</v>
       </c>
       <c r="R16" t="n">
-        <v>6982537</v>
+        <v>6982762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986478</v>
+        <v>128986468</v>
       </c>
       <c r="B17" t="n">
-        <v>75139</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518949</v>
+        <v>518944</v>
       </c>
       <c r="R17" t="n">
-        <v>6982601</v>
+        <v>6982537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2226,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986515</v>
+        <v>128986458</v>
       </c>
       <c r="B18" t="n">
-        <v>80174</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519023</v>
+        <v>518751</v>
       </c>
       <c r="R18" t="n">
-        <v>6982774</v>
+        <v>6982439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2318,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986485</v>
+        <v>128986478</v>
       </c>
       <c r="B19" t="n">
-        <v>80139</v>
+        <v>75139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519104</v>
+        <v>518949</v>
       </c>
       <c r="R19" t="n">
-        <v>6982762</v>
+        <v>6982601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986732</v>
+        <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>98656</v>
+        <v>78792</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519137</v>
+        <v>518952</v>
       </c>
       <c r="R20" t="n">
-        <v>6982624</v>
+        <v>6982811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986505</v>
+        <v>128986732</v>
       </c>
       <c r="B21" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2583,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519089</v>
+        <v>519137</v>
       </c>
       <c r="R21" t="n">
-        <v>6982812</v>
+        <v>6982624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2619,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2648,7 @@
         <v>128986730</v>
       </c>
       <c r="B22" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986729</v>
+        <v>128986505</v>
       </c>
       <c r="B23" t="n">
-        <v>78791</v>
+        <v>98659</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518952</v>
+        <v>519089</v>
       </c>
       <c r="R23" t="n">
-        <v>6982811</v>
+        <v>6982812</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>80140</v>
+        <v>91526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R24" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986716</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>80139</v>
+        <v>80141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519149</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982659</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986489</v>
+        <v>128986716</v>
       </c>
       <c r="B26" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519023</v>
+        <v>519149</v>
       </c>
       <c r="R26" t="n">
-        <v>6982778</v>
+        <v>6982659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986700</v>
+        <v>128986489</v>
       </c>
       <c r="B27" t="n">
-        <v>91523</v>
+        <v>80140</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518969</v>
+        <v>519023</v>
       </c>
       <c r="R27" t="n">
-        <v>6982720</v>
+        <v>6982778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986501</v>
+        <v>128986492</v>
       </c>
       <c r="B28" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519091</v>
+        <v>518959</v>
       </c>
       <c r="R28" t="n">
-        <v>6982620</v>
+        <v>6982485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3327,7 +3327,7 @@
         <v>128986726</v>
       </c>
       <c r="B29" t="n">
-        <v>78791</v>
+        <v>78792</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986492</v>
+        <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518959</v>
+        <v>519129</v>
       </c>
       <c r="R30" t="n">
-        <v>6982485</v>
+        <v>6982658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3518,10 +3523,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986463</v>
+        <v>128986510</v>
       </c>
       <c r="B31" t="n">
-        <v>57723</v>
+        <v>56904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3529,16 +3534,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3553,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519129</v>
+        <v>519116</v>
       </c>
       <c r="R31" t="n">
-        <v>6982658</v>
+        <v>6982762</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,11 +3594,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3620,32 +3620,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986510</v>
+        <v>128986500</v>
       </c>
       <c r="B32" t="n">
-        <v>56904</v>
+        <v>98659</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519116</v>
+        <v>519090</v>
       </c>
       <c r="R32" t="n">
-        <v>6982762</v>
+        <v>6982633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986500</v>
+        <v>128986501</v>
       </c>
       <c r="B33" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519090</v>
+        <v>519091</v>
       </c>
       <c r="R33" t="n">
-        <v>6982633</v>
+        <v>6982620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,32 +3814,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B34" t="n">
-        <v>78791</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R34" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,21 +3922,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,11 +3982,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4008,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B36" t="n">
-        <v>98656</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R36" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,6 +4079,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4215,7 +4215,7 @@
         <v>128986713</v>
       </c>
       <c r="B38" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4312,7 +4312,7 @@
         <v>128986723</v>
       </c>
       <c r="B39" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>128986710</v>
       </c>
       <c r="B40" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986509</v>
+        <v>128986708</v>
       </c>
       <c r="B41" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518970</v>
+        <v>518983</v>
       </c>
       <c r="R41" t="n">
-        <v>6982749</v>
+        <v>6982481</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986499</v>
+        <v>128986722</v>
       </c>
       <c r="B42" t="n">
-        <v>98656</v>
+        <v>80140</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519106</v>
+        <v>518975</v>
       </c>
       <c r="R42" t="n">
-        <v>6982616</v>
+        <v>6982829</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986502</v>
+        <v>128986509</v>
       </c>
       <c r="B43" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519145</v>
+        <v>518970</v>
       </c>
       <c r="R43" t="n">
-        <v>6982681</v>
+        <v>6982749</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986708</v>
+        <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518983</v>
+        <v>519106</v>
       </c>
       <c r="R44" t="n">
-        <v>6982481</v>
+        <v>6982616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986722</v>
+        <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>80139</v>
+        <v>98659</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518975</v>
+        <v>519145</v>
       </c>
       <c r="R45" t="n">
-        <v>6982829</v>
+        <v>6982681</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986719</v>
+        <v>128986474</v>
       </c>
       <c r="B46" t="n">
-        <v>80139</v>
+        <v>80141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519128</v>
+        <v>518955</v>
       </c>
       <c r="R46" t="n">
-        <v>6982688</v>
+        <v>6982588</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986493</v>
+        <v>128986719</v>
       </c>
       <c r="B47" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518940</v>
+        <v>519128</v>
       </c>
       <c r="R47" t="n">
-        <v>6982481</v>
+        <v>6982688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986482</v>
+        <v>128986493</v>
       </c>
       <c r="B48" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519112</v>
+        <v>518940</v>
       </c>
       <c r="R48" t="n">
-        <v>6982533</v>
+        <v>6982481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986721</v>
+        <v>128986482</v>
       </c>
       <c r="B49" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519110</v>
+        <v>519112</v>
       </c>
       <c r="R49" t="n">
-        <v>6982770</v>
+        <v>6982533</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986484</v>
+        <v>128986721</v>
       </c>
       <c r="B50" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519153</v>
+        <v>519110</v>
       </c>
       <c r="R50" t="n">
-        <v>6982677</v>
+        <v>6982770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986465</v>
+        <v>128986484</v>
       </c>
       <c r="B51" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519109</v>
+        <v>519153</v>
       </c>
       <c r="R51" t="n">
-        <v>6982756</v>
+        <v>6982677</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,11 +5544,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5677,10 +5672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986474</v>
+        <v>128986465</v>
       </c>
       <c r="B53" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5683,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518955</v>
+        <v>519109</v>
       </c>
       <c r="R53" t="n">
-        <v>6982588</v>
+        <v>6982756</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5748,6 +5743,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5777,7 +5777,7 @@
         <v>128986490</v>
       </c>
       <c r="B54" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>128986717</v>
       </c>
       <c r="B55" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128986481</v>
       </c>
       <c r="B56" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B57" t="n">
-        <v>75027</v>
+        <v>80175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R57" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986514</v>
+        <v>128986477</v>
       </c>
       <c r="B58" t="n">
-        <v>80174</v>
+        <v>75027</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6428</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519096</v>
+        <v>519000</v>
       </c>
       <c r="R58" t="n">
-        <v>6982528</v>
+        <v>6982781</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6262,7 +6262,7 @@
         <v>128986486</v>
       </c>
       <c r="B59" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>128986718</v>
       </c>
       <c r="B60" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>128986715</v>
       </c>
       <c r="B61" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>128986724</v>
       </c>
       <c r="B62" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>128986705</v>
       </c>
       <c r="B63" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6946,7 +6946,7 @@
         <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>79058</v>
+        <v>79059</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7040,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986470</v>
+        <v>128986714</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518794</v>
+        <v>519102</v>
       </c>
       <c r="R67" t="n">
-        <v>6982445</v>
+        <v>6982627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,11 +7111,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7244,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986714</v>
+        <v>128986470</v>
       </c>
       <c r="B69" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7255,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519102</v>
+        <v>518794</v>
       </c>
       <c r="R69" t="n">
-        <v>6982627</v>
+        <v>6982445</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,6 +7310,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>128986480</v>
       </c>
       <c r="B75" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7931,7 +7931,7 @@
         <v>128986491</v>
       </c>
       <c r="B76" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8028,7 +8028,7 @@
         <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128986725</v>
+        <v>128986712</v>
       </c>
       <c r="B78" t="n">
-        <v>78791</v>
+        <v>80140</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519052</v>
+        <v>519121</v>
       </c>
       <c r="R78" t="n">
-        <v>6982433</v>
+        <v>6982559</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986712</v>
+        <v>128986720</v>
       </c>
       <c r="B79" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519121</v>
+        <v>519130</v>
       </c>
       <c r="R79" t="n">
-        <v>6982559</v>
+        <v>6982756</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986720</v>
+        <v>128986725</v>
       </c>
       <c r="B80" t="n">
-        <v>80139</v>
+        <v>78792</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519130</v>
+        <v>519052</v>
       </c>
       <c r="R80" t="n">
-        <v>6982756</v>
+        <v>6982433</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8416,7 +8416,7 @@
         <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>80139</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98656</v>
+        <v>98659</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986464</v>
+        <v>128986476</v>
       </c>
       <c r="B83" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519152</v>
+        <v>519017</v>
       </c>
       <c r="R83" t="n">
-        <v>6982692</v>
+        <v>6982756</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,11 +8678,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8709,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986699</v>
+        <v>128986727</v>
       </c>
       <c r="B84" t="n">
-        <v>79624</v>
+        <v>78792</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8720,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518952</v>
+        <v>519019</v>
       </c>
       <c r="R84" t="n">
-        <v>6982811</v>
+        <v>6982859</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8806,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B85" t="n">
-        <v>78791</v>
+        <v>80140</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R85" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8877,6 +8872,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986703</v>
+        <v>128986517</v>
       </c>
       <c r="B86" t="n">
-        <v>80139</v>
+        <v>79291</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518965</v>
+        <v>518977</v>
       </c>
       <c r="R86" t="n">
-        <v>6982610</v>
+        <v>6982833</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,11 +8974,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9005,32 +9000,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986517</v>
+        <v>128986711</v>
       </c>
       <c r="B87" t="n">
-        <v>79290</v>
+        <v>80140</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9040,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518977</v>
+        <v>519123</v>
       </c>
       <c r="R87" t="n">
-        <v>6982833</v>
+        <v>6982555</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,10 +9097,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986711</v>
+        <v>128986464</v>
       </c>
       <c r="B88" t="n">
-        <v>80139</v>
+        <v>57723</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9113,21 +9108,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519123</v>
+        <v>519152</v>
       </c>
       <c r="R88" t="n">
-        <v>6982555</v>
+        <v>6982692</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9173,6 +9168,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9199,10 +9199,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986476</v>
+        <v>128986699</v>
       </c>
       <c r="B89" t="n">
-        <v>80140</v>
+        <v>79625</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519017</v>
+        <v>518952</v>
       </c>
       <c r="R89" t="n">
-        <v>6982756</v>
+        <v>6982811</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R3" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986455</v>
+        <v>128986731</v>
       </c>
       <c r="B4" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518927</v>
+        <v>519104</v>
       </c>
       <c r="R4" t="n">
-        <v>6982838</v>
+        <v>6982578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986513</v>
+        <v>128986701</v>
       </c>
       <c r="B7" t="n">
-        <v>92103</v>
+        <v>80141</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519097</v>
+        <v>519098</v>
       </c>
       <c r="R7" t="n">
-        <v>6982582</v>
+        <v>6982579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986701</v>
+        <v>128986513</v>
       </c>
       <c r="B8" t="n">
-        <v>80141</v>
+        <v>92103</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519098</v>
+        <v>519097</v>
       </c>
       <c r="R8" t="n">
-        <v>6982579</v>
+        <v>6982582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1655,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986498</v>
+        <v>128986494</v>
       </c>
       <c r="B12" t="n">
-        <v>98659</v>
+        <v>57827</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519095</v>
+        <v>519117</v>
       </c>
       <c r="R12" t="n">
-        <v>6982524</v>
+        <v>6982667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1752,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986494</v>
+        <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>57827</v>
+        <v>98659</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519117</v>
+        <v>519095</v>
       </c>
       <c r="R13" t="n">
-        <v>6982667</v>
+        <v>6982524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986515</v>
+        <v>128986478</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>75139</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>1460</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519023</v>
+        <v>518949</v>
       </c>
       <c r="R15" t="n">
-        <v>6982774</v>
+        <v>6982601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R16" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2247,32 +2252,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986478</v>
+        <v>128986485</v>
       </c>
       <c r="B19" t="n">
-        <v>75139</v>
+        <v>80140</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518949</v>
+        <v>519104</v>
       </c>
       <c r="R19" t="n">
-        <v>6982601</v>
+        <v>6982762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2645,7 +2645,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986730</v>
+        <v>128986505</v>
       </c>
       <c r="B22" t="n">
         <v>98659</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518956</v>
+        <v>519089</v>
       </c>
       <c r="R22" t="n">
-        <v>6982758</v>
+        <v>6982812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,7 +2742,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986505</v>
+        <v>128986730</v>
       </c>
       <c r="B23" t="n">
         <v>98659</v>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519089</v>
+        <v>518956</v>
       </c>
       <c r="R23" t="n">
-        <v>6982812</v>
+        <v>6982758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>91526</v>
+        <v>80141</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R24" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B25" t="n">
-        <v>80141</v>
+        <v>91526</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986492</v>
+        <v>128986510</v>
       </c>
       <c r="B28" t="n">
-        <v>80140</v>
+        <v>56904</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518959</v>
+        <v>519116</v>
       </c>
       <c r="R28" t="n">
-        <v>6982485</v>
+        <v>6982762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986726</v>
+        <v>128986463</v>
       </c>
       <c r="B29" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519089</v>
+        <v>519129</v>
       </c>
       <c r="R29" t="n">
-        <v>6982825</v>
+        <v>6982658</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,6 +3395,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3421,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986463</v>
+        <v>128986492</v>
       </c>
       <c r="B30" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519129</v>
+        <v>518959</v>
       </c>
       <c r="R30" t="n">
-        <v>6982658</v>
+        <v>6982485</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,11 +3497,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,10 +3523,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986510</v>
+        <v>128986726</v>
       </c>
       <c r="B31" t="n">
-        <v>56904</v>
+        <v>78792</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519116</v>
+        <v>519089</v>
       </c>
       <c r="R31" t="n">
-        <v>6982762</v>
+        <v>6982825</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3814,32 +3814,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R34" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,6 +3885,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3911,32 +3916,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>98659</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R35" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4008,10 +4013,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4019,21 +4024,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4043,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R36" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,11 +4084,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986457</v>
+        <v>128986713</v>
       </c>
       <c r="B37" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518740</v>
+        <v>519091</v>
       </c>
       <c r="R37" t="n">
-        <v>6982426</v>
+        <v>6982582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,11 +4181,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4212,7 +4207,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986713</v>
+        <v>128986723</v>
       </c>
       <c r="B38" t="n">
         <v>80140</v>
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519091</v>
+        <v>519011</v>
       </c>
       <c r="R38" t="n">
-        <v>6982582</v>
+        <v>6982694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,7 +4304,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986723</v>
+        <v>128986710</v>
       </c>
       <c r="B39" t="n">
         <v>80140</v>
@@ -4344,10 +4339,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519011</v>
+        <v>519088</v>
       </c>
       <c r="R39" t="n">
-        <v>6982694</v>
+        <v>6982506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4406,10 +4401,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986710</v>
+        <v>128986457</v>
       </c>
       <c r="B40" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4417,21 +4412,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4441,10 +4436,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519088</v>
+        <v>518740</v>
       </c>
       <c r="R40" t="n">
-        <v>6982506</v>
+        <v>6982426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,6 +4472,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5570,7 +5570,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986461</v>
+        <v>128986465</v>
       </c>
       <c r="B52" t="n">
         <v>57723</v>
@@ -5605,10 +5605,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519127</v>
+        <v>519109</v>
       </c>
       <c r="R52" t="n">
-        <v>6982642</v>
+        <v>6982756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5645,7 +5645,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5672,7 +5672,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986465</v>
+        <v>128986461</v>
       </c>
       <c r="B53" t="n">
         <v>57723</v>
@@ -5707,10 +5707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519109</v>
+        <v>519127</v>
       </c>
       <c r="R53" t="n">
-        <v>6982756</v>
+        <v>6982642</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5747,7 +5747,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986477</v>
       </c>
       <c r="B57" t="n">
-        <v>80175</v>
+        <v>75027</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>6428</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>519000</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982781</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,10 +6162,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B58" t="n">
-        <v>75027</v>
+        <v>80175</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6173,21 +6173,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R58" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B66" t="n">
-        <v>79059</v>
+        <v>57723</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R66" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,6 +7014,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986714</v>
+        <v>128986466</v>
       </c>
       <c r="B67" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7080,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519102</v>
+        <v>519061</v>
       </c>
       <c r="R67" t="n">
-        <v>6982627</v>
+        <v>6982707</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,6 +7116,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7137,32 +7147,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986466</v>
+        <v>128986479</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>79059</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7172,10 +7182,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519061</v>
+        <v>518960</v>
       </c>
       <c r="R68" t="n">
-        <v>6982707</v>
+        <v>6982834</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7208,11 +7218,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7244,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986470</v>
+        <v>128986714</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7255,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518794</v>
+        <v>519102</v>
       </c>
       <c r="R69" t="n">
-        <v>6982445</v>
+        <v>6982627</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7310,11 +7315,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,32 +7341,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986460</v>
+        <v>128986504</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519008</v>
+        <v>519130</v>
       </c>
       <c r="R70" t="n">
-        <v>6982491</v>
+        <v>6982767</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,11 +7412,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7443,10 +7438,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986511</v>
+        <v>128986460</v>
       </c>
       <c r="B71" t="n">
-        <v>56904</v>
+        <v>57723</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7454,16 +7449,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518948</v>
+        <v>519008</v>
       </c>
       <c r="R71" t="n">
-        <v>6982848</v>
+        <v>6982491</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7514,6 +7509,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7540,27 +7540,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986472</v>
+        <v>128986511</v>
       </c>
       <c r="B72" t="n">
-        <v>57564</v>
+        <v>56904</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519067</v>
+        <v>518948</v>
       </c>
       <c r="R72" t="n">
-        <v>6982817</v>
+        <v>6982848</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7637,32 +7637,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128986504</v>
+        <v>128986472</v>
       </c>
       <c r="B73" t="n">
-        <v>98659</v>
+        <v>57564</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519130</v>
+        <v>519067</v>
       </c>
       <c r="R73" t="n">
-        <v>6982767</v>
+        <v>6982817</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986702</v>
+        <v>128986480</v>
       </c>
       <c r="B74" t="n">
-        <v>80141</v>
+        <v>80140</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7745,21 +7745,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519099</v>
+        <v>519008</v>
       </c>
       <c r="R74" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986480</v>
+        <v>128986491</v>
       </c>
       <c r="B75" t="n">
         <v>80140</v>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519008</v>
+        <v>518942</v>
       </c>
       <c r="R75" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986491</v>
+        <v>128986702</v>
       </c>
       <c r="B76" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518942</v>
+        <v>519099</v>
       </c>
       <c r="R76" t="n">
         <v>6982579</v>
@@ -8413,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128986709</v>
+        <v>128986734</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518996</v>
+        <v>518945</v>
       </c>
       <c r="R81" t="n">
-        <v>6982470</v>
+        <v>6982764</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,32 +8510,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128986734</v>
+        <v>128986709</v>
       </c>
       <c r="B82" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518945</v>
+        <v>518996</v>
       </c>
       <c r="R82" t="n">
-        <v>6982764</v>
+        <v>6982470</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986701</v>
+        <v>128986706</v>
       </c>
       <c r="B7" t="n">
-        <v>80141</v>
+        <v>80140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519098</v>
+        <v>518979</v>
       </c>
       <c r="R7" t="n">
-        <v>6982579</v>
+        <v>6982499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986513</v>
+        <v>128986488</v>
       </c>
       <c r="B8" t="n">
-        <v>92103</v>
+        <v>80140</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519097</v>
+        <v>519036</v>
       </c>
       <c r="R8" t="n">
-        <v>6982582</v>
+        <v>6982781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,10 +1359,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986706</v>
+        <v>128986701</v>
       </c>
       <c r="B9" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518979</v>
+        <v>519098</v>
       </c>
       <c r="R9" t="n">
-        <v>6982499</v>
+        <v>6982579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986488</v>
+        <v>128986513</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>92103</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519036</v>
+        <v>519097</v>
       </c>
       <c r="R10" t="n">
-        <v>6982781</v>
+        <v>6982582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986473</v>
+        <v>128986494</v>
       </c>
       <c r="B11" t="n">
-        <v>57564</v>
+        <v>57827</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518872</v>
+        <v>519117</v>
       </c>
       <c r="R11" t="n">
-        <v>6982457</v>
+        <v>6982667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B12" t="n">
-        <v>57827</v>
+        <v>57564</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,16 +1671,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R12" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986478</v>
+        <v>128986458</v>
       </c>
       <c r="B15" t="n">
-        <v>75139</v>
+        <v>57723</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518949</v>
+        <v>518751</v>
       </c>
       <c r="R15" t="n">
-        <v>6982601</v>
+        <v>6982439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,6 +2022,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,7 +2053,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986458</v>
+        <v>128986468</v>
       </c>
       <c r="B16" t="n">
         <v>57723</v>
@@ -2083,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518751</v>
+        <v>518944</v>
       </c>
       <c r="R16" t="n">
-        <v>6982439</v>
+        <v>6982537</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2123,7 +2128,7 @@
       </c>
       <c r="AC16" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986468</v>
+        <v>128986478</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>75139</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518944</v>
+        <v>518949</v>
       </c>
       <c r="R17" t="n">
-        <v>6982537</v>
+        <v>6982601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2221,11 +2226,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B34" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R34" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3916,32 +3911,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3951,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>78792</v>
+        <v>98659</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R36" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986708</v>
+        <v>128986509</v>
       </c>
       <c r="B41" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518983</v>
+        <v>518970</v>
       </c>
       <c r="R41" t="n">
-        <v>6982481</v>
+        <v>6982749</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986722</v>
+        <v>128986499</v>
       </c>
       <c r="B42" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518975</v>
+        <v>519106</v>
       </c>
       <c r="R42" t="n">
-        <v>6982829</v>
+        <v>6982616</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986509</v>
+        <v>128986502</v>
       </c>
       <c r="B43" t="n">
         <v>98659</v>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518970</v>
+        <v>519145</v>
       </c>
       <c r="R43" t="n">
-        <v>6982749</v>
+        <v>6982681</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986499</v>
+        <v>128986708</v>
       </c>
       <c r="B44" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519106</v>
+        <v>518983</v>
       </c>
       <c r="R44" t="n">
-        <v>6982616</v>
+        <v>6982481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986502</v>
+        <v>128986722</v>
       </c>
       <c r="B45" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519145</v>
+        <v>518975</v>
       </c>
       <c r="R45" t="n">
-        <v>6982681</v>
+        <v>6982829</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986474</v>
+        <v>128986465</v>
       </c>
       <c r="B46" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518955</v>
+        <v>519109</v>
       </c>
       <c r="R46" t="n">
-        <v>6982588</v>
+        <v>6982756</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5059,6 +5059,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5085,10 +5090,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986719</v>
+        <v>128986461</v>
       </c>
       <c r="B47" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5101,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5125,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519128</v>
+        <v>519127</v>
       </c>
       <c r="R47" t="n">
-        <v>6982688</v>
+        <v>6982642</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,6 +5161,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5182,10 +5192,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986493</v>
+        <v>128986474</v>
       </c>
       <c r="B48" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5193,21 +5203,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5227,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518940</v>
+        <v>518955</v>
       </c>
       <c r="R48" t="n">
-        <v>6982481</v>
+        <v>6982588</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,7 +5289,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986482</v>
+        <v>128986719</v>
       </c>
       <c r="B49" t="n">
         <v>80140</v>
@@ -5314,10 +5324,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519112</v>
+        <v>519128</v>
       </c>
       <c r="R49" t="n">
-        <v>6982533</v>
+        <v>6982688</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,7 +5386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986721</v>
+        <v>128986493</v>
       </c>
       <c r="B50" t="n">
         <v>80140</v>
@@ -5411,10 +5421,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519110</v>
+        <v>518940</v>
       </c>
       <c r="R50" t="n">
-        <v>6982770</v>
+        <v>6982481</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,7 +5483,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986484</v>
+        <v>128986482</v>
       </c>
       <c r="B51" t="n">
         <v>80140</v>
@@ -5508,10 +5518,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519153</v>
+        <v>519112</v>
       </c>
       <c r="R51" t="n">
-        <v>6982677</v>
+        <v>6982533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,10 +5580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986465</v>
+        <v>128986721</v>
       </c>
       <c r="B52" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5581,21 +5591,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5605,10 +5615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519109</v>
+        <v>519110</v>
       </c>
       <c r="R52" t="n">
-        <v>6982756</v>
+        <v>6982770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5641,11 +5651,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5672,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986461</v>
+        <v>128986484</v>
       </c>
       <c r="B53" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519127</v>
+        <v>519153</v>
       </c>
       <c r="R53" t="n">
-        <v>6982642</v>
+        <v>6982677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,11 +5748,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986477</v>
+        <v>128986497</v>
       </c>
       <c r="B57" t="n">
-        <v>75027</v>
+        <v>98659</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519000</v>
+        <v>519074</v>
       </c>
       <c r="R57" t="n">
-        <v>6982781</v>
+        <v>6982512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986514</v>
+        <v>128986496</v>
       </c>
       <c r="B58" t="n">
-        <v>80175</v>
+        <v>98659</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519096</v>
+        <v>518776</v>
       </c>
       <c r="R58" t="n">
-        <v>6982528</v>
+        <v>6982502</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986486</v>
+        <v>128986477</v>
       </c>
       <c r="B59" t="n">
-        <v>80140</v>
+        <v>75027</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519058</v>
+        <v>519000</v>
       </c>
       <c r="R59" t="n">
-        <v>6982687</v>
+        <v>6982781</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986718</v>
+        <v>128986486</v>
       </c>
       <c r="B60" t="n">
         <v>80140</v>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519135</v>
+        <v>519058</v>
       </c>
       <c r="R60" t="n">
-        <v>6982678</v>
+        <v>6982687</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986715</v>
+        <v>128986718</v>
       </c>
       <c r="B61" t="n">
         <v>80140</v>
@@ -6491,7 +6491,7 @@
         <v>519135</v>
       </c>
       <c r="R61" t="n">
-        <v>6982624</v>
+        <v>6982678</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986724</v>
+        <v>128986715</v>
       </c>
       <c r="B62" t="n">
         <v>80140</v>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518998</v>
+        <v>519135</v>
       </c>
       <c r="R62" t="n">
-        <v>6982673</v>
+        <v>6982624</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,11 +6621,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,7 +6647,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986705</v>
+        <v>128986724</v>
       </c>
       <c r="B63" t="n">
         <v>80140</v>
@@ -6687,10 +6682,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518809</v>
+        <v>518998</v>
       </c>
       <c r="R63" t="n">
-        <v>6982489</v>
+        <v>6982673</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6723,6 +6718,11 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6749,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986497</v>
+        <v>128986705</v>
       </c>
       <c r="B64" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519074</v>
+        <v>518809</v>
       </c>
       <c r="R64" t="n">
-        <v>6982512</v>
+        <v>6982489</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986496</v>
+        <v>128986514</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>80175</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518776</v>
+        <v>519096</v>
       </c>
       <c r="R65" t="n">
-        <v>6982502</v>
+        <v>6982528</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7734,10 +7734,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986480</v>
+        <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7745,21 +7745,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519008</v>
+        <v>519099</v>
       </c>
       <c r="R74" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986491</v>
+        <v>128986480</v>
       </c>
       <c r="B75" t="n">
         <v>80140</v>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518942</v>
+        <v>519008</v>
       </c>
       <c r="R75" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986702</v>
+        <v>128986491</v>
       </c>
       <c r="B76" t="n">
-        <v>80141</v>
+        <v>80140</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519099</v>
+        <v>518942</v>
       </c>
       <c r="R76" t="n">
         <v>6982579</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986455</v>
+        <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>79625</v>
+        <v>98659</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518927</v>
+        <v>519104</v>
       </c>
       <c r="R3" t="n">
-        <v>6982838</v>
+        <v>6982578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>79625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R4" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B5" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R6" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986706</v>
+        <v>128986498</v>
       </c>
       <c r="B7" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518979</v>
+        <v>519095</v>
       </c>
       <c r="R7" t="n">
-        <v>6982499</v>
+        <v>6982524</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986488</v>
+        <v>128986701</v>
       </c>
       <c r="B8" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519036</v>
+        <v>519098</v>
       </c>
       <c r="R8" t="n">
-        <v>6982781</v>
+        <v>6982579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986701</v>
+        <v>128986513</v>
       </c>
       <c r="B9" t="n">
-        <v>80141</v>
+        <v>92103</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519098</v>
+        <v>519097</v>
       </c>
       <c r="R9" t="n">
-        <v>6982579</v>
+        <v>6982582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986513</v>
+        <v>128986706</v>
       </c>
       <c r="B10" t="n">
-        <v>92103</v>
+        <v>80140</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519097</v>
+        <v>518979</v>
       </c>
       <c r="R10" t="n">
-        <v>6982582</v>
+        <v>6982499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986494</v>
+        <v>128986488</v>
       </c>
       <c r="B11" t="n">
-        <v>57827</v>
+        <v>80140</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519117</v>
+        <v>519036</v>
       </c>
       <c r="R11" t="n">
-        <v>6982667</v>
+        <v>6982781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1757,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986498</v>
+        <v>128986494</v>
       </c>
       <c r="B13" t="n">
-        <v>98659</v>
+        <v>57827</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519095</v>
+        <v>519117</v>
       </c>
       <c r="R13" t="n">
-        <v>6982524</v>
+        <v>6982667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B15" t="n">
-        <v>57723</v>
+        <v>80175</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R15" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986468</v>
+        <v>128986485</v>
       </c>
       <c r="B16" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518944</v>
+        <v>519104</v>
       </c>
       <c r="R16" t="n">
-        <v>6982537</v>
+        <v>6982762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986478</v>
+        <v>128986468</v>
       </c>
       <c r="B17" t="n">
-        <v>75139</v>
+        <v>57723</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518949</v>
+        <v>518944</v>
       </c>
       <c r="R17" t="n">
-        <v>6982601</v>
+        <v>6982537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2226,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986515</v>
+        <v>128986458</v>
       </c>
       <c r="B18" t="n">
-        <v>80175</v>
+        <v>57723</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519023</v>
+        <v>518751</v>
       </c>
       <c r="R18" t="n">
-        <v>6982774</v>
+        <v>6982439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2318,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986485</v>
+        <v>128986478</v>
       </c>
       <c r="B19" t="n">
-        <v>80140</v>
+        <v>75139</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519104</v>
+        <v>518949</v>
       </c>
       <c r="R19" t="n">
-        <v>6982762</v>
+        <v>6982601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,7 +2543,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986732</v>
+        <v>128986730</v>
       </c>
       <c r="B21" t="n">
         <v>98659</v>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519137</v>
+        <v>518956</v>
       </c>
       <c r="R21" t="n">
-        <v>6982624</v>
+        <v>6982758</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2614,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2742,7 +2737,7 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986732</v>
       </c>
       <c r="B23" t="n">
         <v>98659</v>
@@ -2777,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>519137</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982624</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>80141</v>
+        <v>91526</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R24" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>91526</v>
+        <v>80141</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986510</v>
+        <v>128986501</v>
       </c>
       <c r="B28" t="n">
-        <v>56904</v>
+        <v>98659</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519116</v>
+        <v>519091</v>
       </c>
       <c r="R28" t="n">
-        <v>6982762</v>
+        <v>6982620</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986463</v>
+        <v>128986500</v>
       </c>
       <c r="B29" t="n">
-        <v>57723</v>
+        <v>98659</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519129</v>
+        <v>519090</v>
       </c>
       <c r="R29" t="n">
-        <v>6982658</v>
+        <v>6982633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3395,11 +3395,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3523,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986726</v>
+        <v>128986510</v>
       </c>
       <c r="B31" t="n">
-        <v>78792</v>
+        <v>56904</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,21 +3529,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519089</v>
+        <v>519116</v>
       </c>
       <c r="R31" t="n">
-        <v>6982825</v>
+        <v>6982762</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,32 +3615,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986500</v>
+        <v>128986463</v>
       </c>
       <c r="B32" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519090</v>
+        <v>519129</v>
       </c>
       <c r="R32" t="n">
-        <v>6982633</v>
+        <v>6982658</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3691,6 +3686,11 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3717,32 +3717,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986501</v>
+        <v>128986726</v>
       </c>
       <c r="B33" t="n">
-        <v>98659</v>
+        <v>78792</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519091</v>
+        <v>519089</v>
       </c>
       <c r="R33" t="n">
-        <v>6982620</v>
+        <v>6982825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,32 +3814,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B34" t="n">
-        <v>78792</v>
+        <v>98659</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R34" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B35" t="n">
-        <v>57723</v>
+        <v>78792</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,21 +3922,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,11 +3982,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4008,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B36" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R36" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,6 +4079,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,7 +4503,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986509</v>
+        <v>128986502</v>
       </c>
       <c r="B41" t="n">
         <v>98659</v>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518970</v>
+        <v>519145</v>
       </c>
       <c r="R41" t="n">
-        <v>6982749</v>
+        <v>6982681</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986502</v>
+        <v>128986509</v>
       </c>
       <c r="B43" t="n">
         <v>98659</v>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519145</v>
+        <v>518970</v>
       </c>
       <c r="R43" t="n">
-        <v>6982681</v>
+        <v>6982749</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986465</v>
+        <v>128986474</v>
       </c>
       <c r="B46" t="n">
-        <v>57723</v>
+        <v>80141</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519109</v>
+        <v>518955</v>
       </c>
       <c r="R46" t="n">
-        <v>6982756</v>
+        <v>6982588</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5059,11 +5059,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5090,7 +5085,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986461</v>
+        <v>128986465</v>
       </c>
       <c r="B47" t="n">
         <v>57723</v>
@@ -5125,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519127</v>
+        <v>519109</v>
       </c>
       <c r="R47" t="n">
-        <v>6982642</v>
+        <v>6982756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5165,7 +5160,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5192,10 +5187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986474</v>
+        <v>128986461</v>
       </c>
       <c r="B48" t="n">
-        <v>80141</v>
+        <v>57723</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5203,21 +5198,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5227,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518955</v>
+        <v>519127</v>
       </c>
       <c r="R48" t="n">
-        <v>6982588</v>
+        <v>6982642</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5263,6 +5258,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986497</v>
+        <v>128986514</v>
       </c>
       <c r="B57" t="n">
-        <v>98659</v>
+        <v>80175</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519074</v>
+        <v>519096</v>
       </c>
       <c r="R57" t="n">
-        <v>6982512</v>
+        <v>6982528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986496</v>
+        <v>128986486</v>
       </c>
       <c r="B58" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518776</v>
+        <v>519058</v>
       </c>
       <c r="R58" t="n">
-        <v>6982502</v>
+        <v>6982687</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986477</v>
+        <v>128986718</v>
       </c>
       <c r="B59" t="n">
-        <v>75027</v>
+        <v>80140</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519000</v>
+        <v>519135</v>
       </c>
       <c r="R59" t="n">
-        <v>6982781</v>
+        <v>6982678</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986486</v>
+        <v>128986715</v>
       </c>
       <c r="B60" t="n">
         <v>80140</v>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519058</v>
+        <v>519135</v>
       </c>
       <c r="R60" t="n">
-        <v>6982687</v>
+        <v>6982624</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986718</v>
+        <v>128986724</v>
       </c>
       <c r="B61" t="n">
         <v>80140</v>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R61" t="n">
-        <v>6982678</v>
+        <v>6982673</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6524,6 +6524,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6550,7 +6555,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986715</v>
+        <v>128986705</v>
       </c>
       <c r="B62" t="n">
         <v>80140</v>
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519135</v>
+        <v>518809</v>
       </c>
       <c r="R62" t="n">
-        <v>6982624</v>
+        <v>6982489</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6647,32 +6652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986724</v>
+        <v>128986477</v>
       </c>
       <c r="B63" t="n">
-        <v>80140</v>
+        <v>75027</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6682,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518998</v>
+        <v>519000</v>
       </c>
       <c r="R63" t="n">
-        <v>6982673</v>
+        <v>6982781</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6718,11 +6723,6 @@
       <c r="AA63" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -6749,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986705</v>
+        <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518809</v>
+        <v>519074</v>
       </c>
       <c r="R64" t="n">
-        <v>6982489</v>
+        <v>6982512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986514</v>
+        <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>80175</v>
+        <v>98659</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519096</v>
+        <v>518776</v>
       </c>
       <c r="R65" t="n">
-        <v>6982528</v>
+        <v>6982502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,10 +6943,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986470</v>
+        <v>128986714</v>
       </c>
       <c r="B66" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6954,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518794</v>
+        <v>519102</v>
       </c>
       <c r="R66" t="n">
-        <v>6982445</v>
+        <v>6982627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,32 +7040,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986466</v>
+        <v>128986479</v>
       </c>
       <c r="B67" t="n">
-        <v>57723</v>
+        <v>79059</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519061</v>
+        <v>518960</v>
       </c>
       <c r="R67" t="n">
-        <v>6982707</v>
+        <v>6982834</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7116,11 +7111,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7147,32 +7137,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>79059</v>
+        <v>57723</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7182,10 +7172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R68" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7218,6 +7208,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7244,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986714</v>
+        <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>80140</v>
+        <v>57723</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7255,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519102</v>
+        <v>519061</v>
       </c>
       <c r="R69" t="n">
-        <v>6982627</v>
+        <v>6982707</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,6 +7310,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,32 +7341,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986504</v>
+        <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>98659</v>
+        <v>57723</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519130</v>
+        <v>519008</v>
       </c>
       <c r="R70" t="n">
-        <v>6982767</v>
+        <v>6982491</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,6 +7412,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7438,10 +7443,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986460</v>
+        <v>128986511</v>
       </c>
       <c r="B71" t="n">
-        <v>57723</v>
+        <v>56904</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7449,16 +7454,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7473,10 +7478,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519008</v>
+        <v>518948</v>
       </c>
       <c r="R71" t="n">
-        <v>6982491</v>
+        <v>6982848</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,11 +7514,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7540,27 +7540,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986511</v>
+        <v>128986472</v>
       </c>
       <c r="B72" t="n">
-        <v>56904</v>
+        <v>57564</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102612</v>
+        <v>102621</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518948</v>
+        <v>519067</v>
       </c>
       <c r="R72" t="n">
-        <v>6982848</v>
+        <v>6982817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7637,32 +7637,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128986472</v>
+        <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>57564</v>
+        <v>98659</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519067</v>
+        <v>519130</v>
       </c>
       <c r="R73" t="n">
-        <v>6982817</v>
+        <v>6982767</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8413,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128986734</v>
+        <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>98659</v>
+        <v>80140</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518945</v>
+        <v>518996</v>
       </c>
       <c r="R81" t="n">
-        <v>6982764</v>
+        <v>6982470</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,32 +8510,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128986709</v>
+        <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>80140</v>
+        <v>98659</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518996</v>
+        <v>518945</v>
       </c>
       <c r="R82" t="n">
-        <v>6982470</v>
+        <v>6982764</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986476</v>
+        <v>128986727</v>
       </c>
       <c r="B83" t="n">
-        <v>80141</v>
+        <v>78792</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519017</v>
+        <v>519019</v>
       </c>
       <c r="R83" t="n">
-        <v>6982756</v>
+        <v>6982859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986727</v>
+        <v>128986464</v>
       </c>
       <c r="B84" t="n">
-        <v>78792</v>
+        <v>57723</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519019</v>
+        <v>519152</v>
       </c>
       <c r="R84" t="n">
-        <v>6982859</v>
+        <v>6982692</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8775,6 +8775,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8801,10 +8806,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986703</v>
+        <v>128986476</v>
       </c>
       <c r="B85" t="n">
-        <v>80140</v>
+        <v>80141</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8817,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518965</v>
+        <v>519017</v>
       </c>
       <c r="R85" t="n">
-        <v>6982610</v>
+        <v>6982756</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8872,11 +8877,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986517</v>
+        <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>79291</v>
+        <v>80140</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518977</v>
+        <v>518965</v>
       </c>
       <c r="R86" t="n">
-        <v>6982833</v>
+        <v>6982610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,6 +8974,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9000,32 +9005,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986711</v>
+        <v>128986517</v>
       </c>
       <c r="B87" t="n">
-        <v>80140</v>
+        <v>79291</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>519123</v>
+        <v>518977</v>
       </c>
       <c r="R87" t="n">
-        <v>6982555</v>
+        <v>6982833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9097,10 +9102,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986464</v>
+        <v>128986711</v>
       </c>
       <c r="B88" t="n">
-        <v>57723</v>
+        <v>80140</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9108,21 +9113,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9132,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519152</v>
+        <v>519123</v>
       </c>
       <c r="R88" t="n">
-        <v>6982692</v>
+        <v>6982555</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9168,11 +9173,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986495</v>
+        <v>128986731</v>
       </c>
       <c r="B2" t="n">
-        <v>57827</v>
+        <v>98669</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518776</v>
+        <v>519104</v>
       </c>
       <c r="R2" t="n">
-        <v>6982385</v>
+        <v>6982578</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986731</v>
+        <v>128986495</v>
       </c>
       <c r="B3" t="n">
-        <v>98659</v>
+        <v>57829</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519104</v>
+        <v>518776</v>
       </c>
       <c r="R3" t="n">
-        <v>6982578</v>
+        <v>6982385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B5" t="n">
-        <v>98659</v>
+        <v>57725</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R5" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R6" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986498</v>
+        <v>128986513</v>
       </c>
       <c r="B7" t="n">
-        <v>98659</v>
+        <v>92110</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519095</v>
+        <v>519097</v>
       </c>
       <c r="R7" t="n">
-        <v>6982524</v>
+        <v>6982582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986701</v>
+        <v>128986473</v>
       </c>
       <c r="B8" t="n">
-        <v>80141</v>
+        <v>57566</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519098</v>
+        <v>518872</v>
       </c>
       <c r="R8" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1333,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986513</v>
+        <v>128986706</v>
       </c>
       <c r="B9" t="n">
-        <v>92103</v>
+        <v>80144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519097</v>
+        <v>518979</v>
       </c>
       <c r="R9" t="n">
-        <v>6982582</v>
+        <v>6982499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986706</v>
+        <v>128986488</v>
       </c>
       <c r="B10" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518979</v>
+        <v>519036</v>
       </c>
       <c r="R10" t="n">
-        <v>6982499</v>
+        <v>6982781</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,10 +1553,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986488</v>
+        <v>128986701</v>
       </c>
       <c r="B11" t="n">
-        <v>80140</v>
+        <v>80145</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519036</v>
+        <v>519098</v>
       </c>
       <c r="R11" t="n">
-        <v>6982781</v>
+        <v>6982579</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1624,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986473</v>
+        <v>128986494</v>
       </c>
       <c r="B12" t="n">
-        <v>57564</v>
+        <v>57829</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,16 +1666,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518872</v>
+        <v>519117</v>
       </c>
       <c r="R12" t="n">
-        <v>6982457</v>
+        <v>6982667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1752,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986494</v>
+        <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>57827</v>
+        <v>98669</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519117</v>
+        <v>519095</v>
       </c>
       <c r="R13" t="n">
-        <v>6982667</v>
+        <v>6982524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1857,7 +1857,7 @@
         <v>128986707</v>
       </c>
       <c r="B14" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986515</v>
+        <v>128986485</v>
       </c>
       <c r="B15" t="n">
-        <v>80175</v>
+        <v>80144</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519023</v>
+        <v>519104</v>
       </c>
       <c r="R15" t="n">
-        <v>6982774</v>
+        <v>6982762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B16" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R16" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2148,7 +2153,7 @@
         <v>128986468</v>
       </c>
       <c r="B17" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2247,32 +2252,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B18" t="n">
-        <v>57723</v>
+        <v>80179</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2352,7 +2352,7 @@
         <v>128986478</v>
       </c>
       <c r="B19" t="n">
-        <v>75139</v>
+        <v>75141</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2449,7 +2449,7 @@
         <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986730</v>
+        <v>128986732</v>
       </c>
       <c r="B21" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518956</v>
+        <v>519137</v>
       </c>
       <c r="R21" t="n">
-        <v>6982758</v>
+        <v>6982624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2643,7 +2648,7 @@
         <v>128986505</v>
       </c>
       <c r="B22" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986732</v>
+        <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519137</v>
+        <v>518956</v>
       </c>
       <c r="R23" t="n">
-        <v>6982624</v>
+        <v>6982758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2813,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2842,7 +2842,7 @@
         <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>91526</v>
+        <v>91533</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986716</v>
       </c>
       <c r="B25" t="n">
-        <v>80141</v>
+        <v>80144</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>519149</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986716</v>
+        <v>128986489</v>
       </c>
       <c r="B26" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519149</v>
+        <v>519023</v>
       </c>
       <c r="R26" t="n">
-        <v>6982659</v>
+        <v>6982778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986489</v>
+        <v>128986475</v>
       </c>
       <c r="B27" t="n">
-        <v>80140</v>
+        <v>80145</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519023</v>
+        <v>519074</v>
       </c>
       <c r="R27" t="n">
-        <v>6982778</v>
+        <v>6982503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986501</v>
+        <v>128986500</v>
       </c>
       <c r="B28" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519091</v>
+        <v>519090</v>
       </c>
       <c r="R28" t="n">
-        <v>6982620</v>
+        <v>6982633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986500</v>
+        <v>128986501</v>
       </c>
       <c r="B29" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519090</v>
+        <v>519091</v>
       </c>
       <c r="R29" t="n">
-        <v>6982633</v>
+        <v>6982620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3424,7 +3424,7 @@
         <v>128986492</v>
       </c>
       <c r="B30" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3518,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986510</v>
+        <v>128986726</v>
       </c>
       <c r="B31" t="n">
-        <v>56904</v>
+        <v>78796</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3529,21 +3529,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519116</v>
+        <v>519089</v>
       </c>
       <c r="R31" t="n">
-        <v>6982762</v>
+        <v>6982825</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3618,7 +3618,7 @@
         <v>128986463</v>
       </c>
       <c r="B32" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986726</v>
+        <v>128986510</v>
       </c>
       <c r="B33" t="n">
-        <v>78792</v>
+        <v>56906</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519089</v>
+        <v>519116</v>
       </c>
       <c r="R33" t="n">
-        <v>6982825</v>
+        <v>6982762</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,32 +3814,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986508</v>
+        <v>128986728</v>
       </c>
       <c r="B34" t="n">
-        <v>98659</v>
+        <v>78796</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518986</v>
+        <v>518928</v>
       </c>
       <c r="R34" t="n">
-        <v>6982827</v>
+        <v>6982835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986728</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>78792</v>
+        <v>57725</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,21 +3922,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518928</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982835</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4008,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986467</v>
+        <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>57723</v>
+        <v>98669</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4043,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518933</v>
+        <v>518986</v>
       </c>
       <c r="R36" t="n">
-        <v>6982538</v>
+        <v>6982827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,11 +4084,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986713</v>
+        <v>128986723</v>
       </c>
       <c r="B37" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519091</v>
+        <v>519011</v>
       </c>
       <c r="R37" t="n">
-        <v>6982582</v>
+        <v>6982694</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4207,10 +4207,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986723</v>
+        <v>128986710</v>
       </c>
       <c r="B38" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519011</v>
+        <v>519088</v>
       </c>
       <c r="R38" t="n">
-        <v>6982694</v>
+        <v>6982506</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,10 +4304,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986710</v>
+        <v>128986713</v>
       </c>
       <c r="B39" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519088</v>
+        <v>519091</v>
       </c>
       <c r="R39" t="n">
-        <v>6982506</v>
+        <v>6982582</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4404,7 +4404,7 @@
         <v>128986457</v>
       </c>
       <c r="B40" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986502</v>
+        <v>128986722</v>
       </c>
       <c r="B41" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>519145</v>
+        <v>518975</v>
       </c>
       <c r="R41" t="n">
-        <v>6982681</v>
+        <v>6982829</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986499</v>
+        <v>128986708</v>
       </c>
       <c r="B42" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519106</v>
+        <v>518983</v>
       </c>
       <c r="R42" t="n">
-        <v>6982616</v>
+        <v>6982481</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
         <v>128986509</v>
       </c>
       <c r="B43" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986708</v>
+        <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518983</v>
+        <v>519106</v>
       </c>
       <c r="R44" t="n">
-        <v>6982481</v>
+        <v>6982616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986722</v>
+        <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518975</v>
+        <v>519145</v>
       </c>
       <c r="R45" t="n">
-        <v>6982829</v>
+        <v>6982681</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986474</v>
+        <v>128986482</v>
       </c>
       <c r="B46" t="n">
-        <v>80141</v>
+        <v>80144</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518955</v>
+        <v>519112</v>
       </c>
       <c r="R46" t="n">
-        <v>6982588</v>
+        <v>6982533</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5088,7 +5088,7 @@
         <v>128986465</v>
       </c>
       <c r="B47" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5187,10 +5187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986461</v>
+        <v>128986493</v>
       </c>
       <c r="B48" t="n">
-        <v>57723</v>
+        <v>80144</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519127</v>
+        <v>518940</v>
       </c>
       <c r="R48" t="n">
-        <v>6982642</v>
+        <v>6982481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5258,11 +5258,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5289,10 +5284,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986719</v>
+        <v>128986721</v>
       </c>
       <c r="B49" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5324,10 +5319,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519128</v>
+        <v>519110</v>
       </c>
       <c r="R49" t="n">
-        <v>6982688</v>
+        <v>6982770</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5386,10 +5381,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986493</v>
+        <v>128986719</v>
       </c>
       <c r="B50" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5421,10 +5416,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518940</v>
+        <v>519128</v>
       </c>
       <c r="R50" t="n">
-        <v>6982481</v>
+        <v>6982688</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5483,10 +5478,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986482</v>
+        <v>128986484</v>
       </c>
       <c r="B51" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5518,10 +5513,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519112</v>
+        <v>519153</v>
       </c>
       <c r="R51" t="n">
-        <v>6982533</v>
+        <v>6982677</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5580,10 +5575,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986721</v>
+        <v>128986474</v>
       </c>
       <c r="B52" t="n">
-        <v>80140</v>
+        <v>80145</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5591,21 +5586,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5615,10 +5610,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519110</v>
+        <v>518955</v>
       </c>
       <c r="R52" t="n">
-        <v>6982770</v>
+        <v>6982588</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5677,10 +5672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986484</v>
+        <v>128986461</v>
       </c>
       <c r="B53" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5683,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519153</v>
+        <v>519127</v>
       </c>
       <c r="R53" t="n">
-        <v>6982677</v>
+        <v>6982642</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5748,6 +5743,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5774,10 +5774,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128986490</v>
+        <v>128986717</v>
       </c>
       <c r="B54" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519080</v>
+        <v>519151</v>
       </c>
       <c r="R54" t="n">
-        <v>6982814</v>
+        <v>6982660</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5871,10 +5871,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128986717</v>
+        <v>128986490</v>
       </c>
       <c r="B55" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519151</v>
+        <v>519080</v>
       </c>
       <c r="R55" t="n">
-        <v>6982660</v>
+        <v>6982814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5971,7 +5971,7 @@
         <v>128986481</v>
       </c>
       <c r="B56" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986497</v>
       </c>
       <c r="B57" t="n">
-        <v>80175</v>
+        <v>98669</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>519074</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986486</v>
+        <v>128986496</v>
       </c>
       <c r="B58" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519058</v>
+        <v>518776</v>
       </c>
       <c r="R58" t="n">
-        <v>6982687</v>
+        <v>6982502</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986718</v>
+        <v>128986514</v>
       </c>
       <c r="B59" t="n">
-        <v>80140</v>
+        <v>80179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519135</v>
+        <v>519096</v>
       </c>
       <c r="R59" t="n">
-        <v>6982678</v>
+        <v>6982528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,10 +6356,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986715</v>
+        <v>128986724</v>
       </c>
       <c r="B60" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R60" t="n">
-        <v>6982624</v>
+        <v>6982673</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6427,6 +6427,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6453,10 +6458,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986724</v>
+        <v>128986715</v>
       </c>
       <c r="B61" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6488,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518998</v>
+        <v>519135</v>
       </c>
       <c r="R61" t="n">
-        <v>6982673</v>
+        <v>6982624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6524,11 +6529,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6558,7 +6558,7 @@
         <v>128986705</v>
       </c>
       <c r="B62" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6652,32 +6652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986477</v>
+        <v>128986718</v>
       </c>
       <c r="B63" t="n">
-        <v>75027</v>
+        <v>80144</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519000</v>
+        <v>519135</v>
       </c>
       <c r="R63" t="n">
-        <v>6982781</v>
+        <v>6982678</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986497</v>
+        <v>128986477</v>
       </c>
       <c r="B64" t="n">
-        <v>98659</v>
+        <v>75029</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519074</v>
+        <v>519000</v>
       </c>
       <c r="R64" t="n">
-        <v>6982512</v>
+        <v>6982781</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986496</v>
+        <v>128986486</v>
       </c>
       <c r="B65" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518776</v>
+        <v>519058</v>
       </c>
       <c r="R65" t="n">
-        <v>6982502</v>
+        <v>6982687</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986714</v>
+        <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>80140</v>
+        <v>79063</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519102</v>
+        <v>518960</v>
       </c>
       <c r="R66" t="n">
-        <v>6982627</v>
+        <v>6982834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,32 +7040,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986479</v>
+        <v>128986714</v>
       </c>
       <c r="B67" t="n">
-        <v>79059</v>
+        <v>80144</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518960</v>
+        <v>519102</v>
       </c>
       <c r="R67" t="n">
-        <v>6982834</v>
+        <v>6982627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7140,7 +7140,7 @@
         <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>57723</v>
+        <v>57725</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>128986511</v>
       </c>
       <c r="B71" t="n">
-        <v>56904</v>
+        <v>56906</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>128986472</v>
       </c>
       <c r="B72" t="n">
-        <v>57564</v>
+        <v>57566</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7831,32 +7831,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986480</v>
+        <v>128986503</v>
       </c>
       <c r="B75" t="n">
-        <v>80140</v>
+        <v>98669</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519008</v>
+        <v>519118</v>
       </c>
       <c r="R75" t="n">
-        <v>6982457</v>
+        <v>6982684</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986491</v>
+        <v>128986480</v>
       </c>
       <c r="B76" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518942</v>
+        <v>519008</v>
       </c>
       <c r="R76" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8025,32 +8025,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986503</v>
+        <v>128986491</v>
       </c>
       <c r="B77" t="n">
-        <v>98659</v>
+        <v>80144</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519118</v>
+        <v>518942</v>
       </c>
       <c r="R77" t="n">
-        <v>6982684</v>
+        <v>6982579</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8125,7 +8125,7 @@
         <v>128986712</v>
       </c>
       <c r="B78" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8222,7 +8222,7 @@
         <v>128986720</v>
       </c>
       <c r="B79" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8319,7 +8319,7 @@
         <v>128986725</v>
       </c>
       <c r="B80" t="n">
-        <v>78792</v>
+        <v>78796</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8416,7 +8416,7 @@
         <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>80140</v>
+        <v>80144</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98659</v>
+        <v>98669</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B83" t="n">
-        <v>78792</v>
+        <v>80144</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R83" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,6 +8678,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,32 +8709,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986464</v>
+        <v>128986517</v>
       </c>
       <c r="B84" t="n">
-        <v>57723</v>
+        <v>79295</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519152</v>
+        <v>518977</v>
       </c>
       <c r="R84" t="n">
-        <v>6982692</v>
+        <v>6982833</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8775,11 +8780,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8809,7 +8809,7 @@
         <v>128986476</v>
       </c>
       <c r="B85" t="n">
-        <v>80141</v>
+        <v>80145</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986703</v>
+        <v>128986464</v>
       </c>
       <c r="B86" t="n">
-        <v>80140</v>
+        <v>57725</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518965</v>
+        <v>519152</v>
       </c>
       <c r="R86" t="n">
-        <v>6982610</v>
+        <v>6982692</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Lunglav på 3 olika sälgar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9005,32 +9005,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986517</v>
+        <v>128986711</v>
       </c>
       <c r="B87" t="n">
-        <v>79291</v>
+        <v>80144</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9040,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518977</v>
+        <v>519123</v>
       </c>
       <c r="R87" t="n">
-        <v>6982833</v>
+        <v>6982555</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,10 +9102,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986711</v>
+        <v>128986727</v>
       </c>
       <c r="B88" t="n">
-        <v>80140</v>
+        <v>78796</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9113,21 +9113,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519123</v>
+        <v>519019</v>
       </c>
       <c r="R88" t="n">
-        <v>6982555</v>
+        <v>6982859</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9202,7 +9202,7 @@
         <v>128986699</v>
       </c>
       <c r="B89" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986729</v>
+        <v>128986732</v>
       </c>
       <c r="B20" t="n">
-        <v>78796</v>
+        <v>98669</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518952</v>
+        <v>519137</v>
       </c>
       <c r="R20" t="n">
-        <v>6982811</v>
+        <v>6982624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,7 +2548,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986732</v>
+        <v>128986505</v>
       </c>
       <c r="B21" t="n">
         <v>98669</v>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519137</v>
+        <v>519089</v>
       </c>
       <c r="R21" t="n">
-        <v>6982624</v>
+        <v>6982812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,7 +2645,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986505</v>
+        <v>128986730</v>
       </c>
       <c r="B22" t="n">
         <v>98669</v>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519089</v>
+        <v>518956</v>
       </c>
       <c r="R22" t="n">
-        <v>6982812</v>
+        <v>6982758</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986729</v>
       </c>
       <c r="B23" t="n">
-        <v>98669</v>
+        <v>78796</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>518952</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986700</v>
+        <v>128986716</v>
       </c>
       <c r="B24" t="n">
-        <v>91533</v>
+        <v>80144</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518969</v>
+        <v>519149</v>
       </c>
       <c r="R24" t="n">
-        <v>6982720</v>
+        <v>6982659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,7 +2936,7 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986716</v>
+        <v>128986489</v>
       </c>
       <c r="B25" t="n">
         <v>80144</v>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519149</v>
+        <v>519023</v>
       </c>
       <c r="R25" t="n">
-        <v>6982659</v>
+        <v>6982778</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986489</v>
+        <v>128986475</v>
       </c>
       <c r="B26" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519023</v>
+        <v>519074</v>
       </c>
       <c r="R26" t="n">
-        <v>6982778</v>
+        <v>6982503</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B27" t="n">
-        <v>80145</v>
+        <v>91533</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R27" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986500</v>
+        <v>128986492</v>
       </c>
       <c r="B28" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519090</v>
+        <v>518959</v>
       </c>
       <c r="R28" t="n">
-        <v>6982633</v>
+        <v>6982485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986501</v>
+        <v>128986510</v>
       </c>
       <c r="B29" t="n">
-        <v>98669</v>
+        <v>56906</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519091</v>
+        <v>519116</v>
       </c>
       <c r="R29" t="n">
-        <v>6982620</v>
+        <v>6982762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986492</v>
+        <v>128986500</v>
       </c>
       <c r="B30" t="n">
-        <v>80144</v>
+        <v>98669</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518959</v>
+        <v>519090</v>
       </c>
       <c r="R30" t="n">
-        <v>6982485</v>
+        <v>6982633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,32 +3518,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986726</v>
+        <v>128986501</v>
       </c>
       <c r="B31" t="n">
-        <v>78796</v>
+        <v>98669</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519089</v>
+        <v>519091</v>
       </c>
       <c r="R31" t="n">
-        <v>6982825</v>
+        <v>6982620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3615,10 +3615,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986463</v>
+        <v>128986726</v>
       </c>
       <c r="B32" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3626,21 +3626,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3650,10 +3650,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519129</v>
+        <v>519089</v>
       </c>
       <c r="R32" t="n">
-        <v>6982658</v>
+        <v>6982825</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3686,11 +3686,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3717,10 +3712,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986510</v>
+        <v>128986463</v>
       </c>
       <c r="B33" t="n">
-        <v>56906</v>
+        <v>57725</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,16 +3723,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3752,10 +3747,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519116</v>
+        <v>519129</v>
       </c>
       <c r="R33" t="n">
-        <v>6982762</v>
+        <v>6982658</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3788,6 +3783,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3814,32 +3814,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B34" t="n">
-        <v>78796</v>
+        <v>98669</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R34" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3911,10 +3911,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B35" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,21 +3922,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,11 +3982,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4008,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B36" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R36" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,6 +4079,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4110,7 +4110,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986723</v>
+        <v>128986713</v>
       </c>
       <c r="B37" t="n">
         <v>80144</v>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519011</v>
+        <v>519091</v>
       </c>
       <c r="R37" t="n">
-        <v>6982694</v>
+        <v>6982582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4207,7 +4207,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986710</v>
+        <v>128986723</v>
       </c>
       <c r="B38" t="n">
         <v>80144</v>
@@ -4242,10 +4242,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519088</v>
+        <v>519011</v>
       </c>
       <c r="R38" t="n">
-        <v>6982506</v>
+        <v>6982694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,7 +4304,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986713</v>
+        <v>128986710</v>
       </c>
       <c r="B39" t="n">
         <v>80144</v>
@@ -4339,10 +4339,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519091</v>
+        <v>519088</v>
       </c>
       <c r="R39" t="n">
-        <v>6982582</v>
+        <v>6982506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986497</v>
+        <v>128986715</v>
       </c>
       <c r="B57" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519074</v>
+        <v>519135</v>
       </c>
       <c r="R57" t="n">
-        <v>6982512</v>
+        <v>6982624</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986496</v>
+        <v>128986705</v>
       </c>
       <c r="B58" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518776</v>
+        <v>518809</v>
       </c>
       <c r="R58" t="n">
-        <v>6982502</v>
+        <v>6982489</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986514</v>
+        <v>128986718</v>
       </c>
       <c r="B59" t="n">
-        <v>80179</v>
+        <v>80144</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519096</v>
+        <v>519135</v>
       </c>
       <c r="R59" t="n">
-        <v>6982528</v>
+        <v>6982678</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,32 +6356,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986724</v>
+        <v>128986477</v>
       </c>
       <c r="B60" t="n">
-        <v>80144</v>
+        <v>75029</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518998</v>
+        <v>519000</v>
       </c>
       <c r="R60" t="n">
-        <v>6982673</v>
+        <v>6982781</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6427,11 +6427,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6458,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986715</v>
+        <v>128986486</v>
       </c>
       <c r="B61" t="n">
         <v>80144</v>
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519135</v>
+        <v>519058</v>
       </c>
       <c r="R61" t="n">
-        <v>6982624</v>
+        <v>6982687</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,32 +6550,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986705</v>
+        <v>128986497</v>
       </c>
       <c r="B62" t="n">
-        <v>80144</v>
+        <v>98669</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518809</v>
+        <v>519074</v>
       </c>
       <c r="R62" t="n">
-        <v>6982489</v>
+        <v>6982512</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,32 +6647,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986718</v>
+        <v>128986496</v>
       </c>
       <c r="B63" t="n">
-        <v>80144</v>
+        <v>98669</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6682,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519135</v>
+        <v>518776</v>
       </c>
       <c r="R63" t="n">
-        <v>6982678</v>
+        <v>6982502</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,10 +6744,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B64" t="n">
-        <v>75029</v>
+        <v>80179</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6760,21 +6755,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6779,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R64" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6846,7 +6841,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986486</v>
+        <v>128986724</v>
       </c>
       <c r="B65" t="n">
         <v>80144</v>
@@ -6881,10 +6876,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>519058</v>
+        <v>518998</v>
       </c>
       <c r="R65" t="n">
-        <v>6982687</v>
+        <v>6982673</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6917,6 +6912,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B66" t="n">
-        <v>79063</v>
+        <v>57725</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R66" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,6 +7014,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986714</v>
+        <v>128986466</v>
       </c>
       <c r="B67" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7080,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519102</v>
+        <v>519061</v>
       </c>
       <c r="R67" t="n">
-        <v>6982627</v>
+        <v>6982707</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,6 +7116,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7137,32 +7147,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>79063</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7172,10 +7182,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R68" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7208,11 +7218,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7244,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986466</v>
+        <v>128986714</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7255,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519061</v>
+        <v>519102</v>
       </c>
       <c r="R69" t="n">
-        <v>6982707</v>
+        <v>6982627</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7310,11 +7315,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8413,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128986709</v>
+        <v>128986734</v>
       </c>
       <c r="B81" t="n">
-        <v>80144</v>
+        <v>98669</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518996</v>
+        <v>518945</v>
       </c>
       <c r="R81" t="n">
-        <v>6982470</v>
+        <v>6982764</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,32 +8510,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128986734</v>
+        <v>128986709</v>
       </c>
       <c r="B82" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518945</v>
+        <v>518996</v>
       </c>
       <c r="R82" t="n">
-        <v>6982764</v>
+        <v>6982470</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986731</v>
+        <v>128986495</v>
       </c>
       <c r="B2" t="n">
-        <v>98669</v>
+        <v>57829</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>519104</v>
+        <v>518776</v>
       </c>
       <c r="R2" t="n">
-        <v>6982578</v>
+        <v>6982385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986495</v>
+        <v>128986455</v>
       </c>
       <c r="B3" t="n">
-        <v>57829</v>
+        <v>79629</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518776</v>
+        <v>518927</v>
       </c>
       <c r="R3" t="n">
-        <v>6982385</v>
+        <v>6982838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986455</v>
+        <v>128986731</v>
       </c>
       <c r="B4" t="n">
-        <v>79629</v>
+        <v>98676</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518927</v>
+        <v>519104</v>
       </c>
       <c r="R4" t="n">
-        <v>6982838</v>
+        <v>6982578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986513</v>
+        <v>128986498</v>
       </c>
       <c r="B7" t="n">
-        <v>92110</v>
+        <v>98676</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519097</v>
+        <v>519095</v>
       </c>
       <c r="R7" t="n">
-        <v>6982582</v>
+        <v>6982524</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986473</v>
+        <v>128986701</v>
       </c>
       <c r="B8" t="n">
-        <v>57566</v>
+        <v>80145</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518872</v>
+        <v>519098</v>
       </c>
       <c r="R8" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986706</v>
+        <v>128986513</v>
       </c>
       <c r="B9" t="n">
-        <v>80144</v>
+        <v>92117</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518979</v>
+        <v>519097</v>
       </c>
       <c r="R9" t="n">
-        <v>6982499</v>
+        <v>6982582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,7 +1461,7 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986488</v>
+        <v>128986706</v>
       </c>
       <c r="B10" t="n">
         <v>80144</v>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519036</v>
+        <v>518979</v>
       </c>
       <c r="R10" t="n">
-        <v>6982781</v>
+        <v>6982499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1553,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986701</v>
+        <v>128986488</v>
       </c>
       <c r="B11" t="n">
-        <v>80145</v>
+        <v>80144</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1564,21 +1569,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1588,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519098</v>
+        <v>519036</v>
       </c>
       <c r="R11" t="n">
-        <v>6982579</v>
+        <v>6982781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1624,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B12" t="n">
-        <v>57829</v>
+        <v>57566</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,16 +1666,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1690,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R12" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1726,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986498</v>
+        <v>128986494</v>
       </c>
       <c r="B13" t="n">
-        <v>98669</v>
+        <v>57829</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519095</v>
+        <v>519117</v>
       </c>
       <c r="R13" t="n">
-        <v>6982524</v>
+        <v>6982667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986485</v>
+        <v>128986515</v>
       </c>
       <c r="B15" t="n">
-        <v>80144</v>
+        <v>80179</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519104</v>
+        <v>519023</v>
       </c>
       <c r="R15" t="n">
-        <v>6982762</v>
+        <v>6982774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986458</v>
+        <v>128986485</v>
       </c>
       <c r="B16" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518751</v>
+        <v>519104</v>
       </c>
       <c r="R16" t="n">
-        <v>6982439</v>
+        <v>6982762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986468</v>
+        <v>128986478</v>
       </c>
       <c r="B17" t="n">
-        <v>57725</v>
+        <v>75141</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518944</v>
+        <v>518949</v>
       </c>
       <c r="R17" t="n">
-        <v>6982537</v>
+        <v>6982601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2221,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,32 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986515</v>
+        <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>80179</v>
+        <v>57725</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519023</v>
+        <v>518944</v>
       </c>
       <c r="R18" t="n">
-        <v>6982774</v>
+        <v>6982537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2313,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986478</v>
+        <v>128986458</v>
       </c>
       <c r="B19" t="n">
-        <v>75141</v>
+        <v>57725</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518949</v>
+        <v>518751</v>
       </c>
       <c r="R19" t="n">
-        <v>6982601</v>
+        <v>6982439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,6 +2415,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,10 +2446,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986732</v>
+        <v>128986505</v>
       </c>
       <c r="B20" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519137</v>
+        <v>519089</v>
       </c>
       <c r="R20" t="n">
-        <v>6982624</v>
+        <v>6982812</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2548,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986505</v>
+        <v>128986730</v>
       </c>
       <c r="B21" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2583,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519089</v>
+        <v>518956</v>
       </c>
       <c r="R21" t="n">
-        <v>6982812</v>
+        <v>6982758</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2645,32 +2640,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986730</v>
+        <v>128986729</v>
       </c>
       <c r="B22" t="n">
-        <v>98669</v>
+        <v>78796</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2680,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518956</v>
+        <v>518952</v>
       </c>
       <c r="R22" t="n">
-        <v>6982758</v>
+        <v>6982811</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,32 +2737,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986729</v>
+        <v>128986732</v>
       </c>
       <c r="B23" t="n">
-        <v>78796</v>
+        <v>98676</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518952</v>
+        <v>519137</v>
       </c>
       <c r="R23" t="n">
-        <v>6982811</v>
+        <v>6982624</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3133,7 +3133,7 @@
         <v>128986700</v>
       </c>
       <c r="B27" t="n">
-        <v>91533</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986492</v>
+        <v>128986500</v>
       </c>
       <c r="B28" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518959</v>
+        <v>519090</v>
       </c>
       <c r="R28" t="n">
-        <v>6982485</v>
+        <v>6982633</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986510</v>
+        <v>128986501</v>
       </c>
       <c r="B29" t="n">
-        <v>56906</v>
+        <v>98676</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519116</v>
+        <v>519091</v>
       </c>
       <c r="R29" t="n">
-        <v>6982762</v>
+        <v>6982620</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986500</v>
+        <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519090</v>
+        <v>519129</v>
       </c>
       <c r="R30" t="n">
-        <v>6982633</v>
+        <v>6982658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3518,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986501</v>
+        <v>128986492</v>
       </c>
       <c r="B31" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519091</v>
+        <v>518959</v>
       </c>
       <c r="R31" t="n">
-        <v>6982620</v>
+        <v>6982485</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3712,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986463</v>
+        <v>128986510</v>
       </c>
       <c r="B33" t="n">
-        <v>57725</v>
+        <v>56906</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3723,16 +3728,16 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
@@ -3747,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519129</v>
+        <v>519116</v>
       </c>
       <c r="R33" t="n">
-        <v>6982658</v>
+        <v>6982762</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3783,11 +3788,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -3814,32 +3814,32 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B34" t="n">
-        <v>98669</v>
+        <v>57725</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R34" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,6 +3885,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3911,32 +3916,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B35" t="n">
-        <v>78796</v>
+        <v>98676</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R35" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4008,10 +4013,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B36" t="n">
-        <v>57725</v>
+        <v>78796</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4019,21 +4024,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4043,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R36" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,11 +4084,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986713</v>
+        <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519091</v>
+        <v>518740</v>
       </c>
       <c r="R37" t="n">
-        <v>6982582</v>
+        <v>6982426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,6 +4181,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4207,7 +4212,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986723</v>
+        <v>128986713</v>
       </c>
       <c r="B38" t="n">
         <v>80144</v>
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519011</v>
+        <v>519091</v>
       </c>
       <c r="R38" t="n">
-        <v>6982694</v>
+        <v>6982582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,7 +4309,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986710</v>
+        <v>128986723</v>
       </c>
       <c r="B39" t="n">
         <v>80144</v>
@@ -4339,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519088</v>
+        <v>519011</v>
       </c>
       <c r="R39" t="n">
-        <v>6982506</v>
+        <v>6982694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4401,10 +4406,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986457</v>
+        <v>128986710</v>
       </c>
       <c r="B40" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,21 +4417,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518740</v>
+        <v>519088</v>
       </c>
       <c r="R40" t="n">
-        <v>6982426</v>
+        <v>6982506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4472,11 +4477,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4503,7 +4503,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986722</v>
+        <v>128986708</v>
       </c>
       <c r="B41" t="n">
         <v>80144</v>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518975</v>
+        <v>518983</v>
       </c>
       <c r="R41" t="n">
-        <v>6982829</v>
+        <v>6982481</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986708</v>
+        <v>128986722</v>
       </c>
       <c r="B42" t="n">
         <v>80144</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518983</v>
+        <v>518975</v>
       </c>
       <c r="R42" t="n">
-        <v>6982481</v>
+        <v>6982829</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
         <v>128986509</v>
       </c>
       <c r="B43" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986482</v>
+        <v>128986474</v>
       </c>
       <c r="B46" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519112</v>
+        <v>518955</v>
       </c>
       <c r="R46" t="n">
-        <v>6982533</v>
+        <v>6982588</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986465</v>
+        <v>128986461</v>
       </c>
       <c r="B47" t="n">
         <v>57725</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519109</v>
+        <v>519127</v>
       </c>
       <c r="R47" t="n">
-        <v>6982756</v>
+        <v>6982642</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986493</v>
+        <v>128986465</v>
       </c>
       <c r="B48" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5198,21 +5198,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518940</v>
+        <v>519109</v>
       </c>
       <c r="R48" t="n">
-        <v>6982481</v>
+        <v>6982756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5258,6 +5258,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5284,7 +5289,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986721</v>
+        <v>128986719</v>
       </c>
       <c r="B49" t="n">
         <v>80144</v>
@@ -5319,10 +5324,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519110</v>
+        <v>519128</v>
       </c>
       <c r="R49" t="n">
-        <v>6982770</v>
+        <v>6982688</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5381,7 +5386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986719</v>
+        <v>128986493</v>
       </c>
       <c r="B50" t="n">
         <v>80144</v>
@@ -5416,10 +5421,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519128</v>
+        <v>518940</v>
       </c>
       <c r="R50" t="n">
-        <v>6982688</v>
+        <v>6982481</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5478,7 +5483,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986484</v>
+        <v>128986482</v>
       </c>
       <c r="B51" t="n">
         <v>80144</v>
@@ -5513,10 +5518,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519153</v>
+        <v>519112</v>
       </c>
       <c r="R51" t="n">
-        <v>6982677</v>
+        <v>6982533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5575,10 +5580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986474</v>
+        <v>128986721</v>
       </c>
       <c r="B52" t="n">
-        <v>80145</v>
+        <v>80144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5586,21 +5591,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5610,10 +5615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>518955</v>
+        <v>519110</v>
       </c>
       <c r="R52" t="n">
-        <v>6982588</v>
+        <v>6982770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5672,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986461</v>
+        <v>128986484</v>
       </c>
       <c r="B53" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519127</v>
+        <v>519153</v>
       </c>
       <c r="R53" t="n">
-        <v>6982642</v>
+        <v>6982677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,11 +5748,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5774,7 +5774,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128986717</v>
+        <v>128986490</v>
       </c>
       <c r="B54" t="n">
         <v>80144</v>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519151</v>
+        <v>519080</v>
       </c>
       <c r="R54" t="n">
-        <v>6982660</v>
+        <v>6982814</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5871,7 +5871,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128986490</v>
+        <v>128986717</v>
       </c>
       <c r="B55" t="n">
         <v>80144</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519080</v>
+        <v>519151</v>
       </c>
       <c r="R55" t="n">
-        <v>6982814</v>
+        <v>6982660</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986715</v>
+        <v>128986497</v>
       </c>
       <c r="B57" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519135</v>
+        <v>519074</v>
       </c>
       <c r="R57" t="n">
-        <v>6982624</v>
+        <v>6982512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986705</v>
+        <v>128986496</v>
       </c>
       <c r="B58" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518809</v>
+        <v>518776</v>
       </c>
       <c r="R58" t="n">
-        <v>6982489</v>
+        <v>6982502</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986718</v>
+        <v>128986514</v>
       </c>
       <c r="B59" t="n">
-        <v>80144</v>
+        <v>80179</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519135</v>
+        <v>519096</v>
       </c>
       <c r="R59" t="n">
-        <v>6982678</v>
+        <v>6982528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6550,32 +6550,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986497</v>
+        <v>128986718</v>
       </c>
       <c r="B62" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519074</v>
+        <v>519135</v>
       </c>
       <c r="R62" t="n">
-        <v>6982512</v>
+        <v>6982678</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6647,32 +6647,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986496</v>
+        <v>128986715</v>
       </c>
       <c r="B63" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6682,10 +6682,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518776</v>
+        <v>519135</v>
       </c>
       <c r="R63" t="n">
-        <v>6982502</v>
+        <v>6982624</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6744,32 +6744,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986514</v>
+        <v>128986724</v>
       </c>
       <c r="B64" t="n">
-        <v>80179</v>
+        <v>80144</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6779,10 +6779,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519096</v>
+        <v>518998</v>
       </c>
       <c r="R64" t="n">
-        <v>6982528</v>
+        <v>6982673</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6815,6 +6815,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6841,7 +6846,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986724</v>
+        <v>128986705</v>
       </c>
       <c r="B65" t="n">
         <v>80144</v>
@@ -6876,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518998</v>
+        <v>518809</v>
       </c>
       <c r="R65" t="n">
-        <v>6982673</v>
+        <v>6982489</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6912,11 +6917,6 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>57725</v>
+        <v>79063</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R66" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986466</v>
+        <v>128986714</v>
       </c>
       <c r="B67" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519061</v>
+        <v>519102</v>
       </c>
       <c r="R67" t="n">
-        <v>6982707</v>
+        <v>6982627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7116,11 +7111,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7147,32 +7137,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986479</v>
+        <v>128986466</v>
       </c>
       <c r="B68" t="n">
-        <v>79063</v>
+        <v>57725</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7182,10 +7172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518960</v>
+        <v>519061</v>
       </c>
       <c r="R68" t="n">
-        <v>6982834</v>
+        <v>6982707</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7218,6 +7208,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7244,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986714</v>
+        <v>128986470</v>
       </c>
       <c r="B69" t="n">
-        <v>80144</v>
+        <v>57725</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7255,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519102</v>
+        <v>518794</v>
       </c>
       <c r="R69" t="n">
-        <v>6982627</v>
+        <v>6982445</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,6 +7310,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7834,7 +7834,7 @@
         <v>128986503</v>
       </c>
       <c r="B75" t="n">
-        <v>98669</v>
+        <v>98676</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8413,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128986734</v>
+        <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>98669</v>
+        <v>80144</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518945</v>
+        <v>518996</v>
       </c>
       <c r="R81" t="n">
-        <v>6982764</v>
+        <v>6982470</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,32 +8510,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128986709</v>
+        <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>80144</v>
+        <v>98676</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518996</v>
+        <v>518945</v>
       </c>
       <c r="R82" t="n">
-        <v>6982470</v>
+        <v>6982764</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986703</v>
+        <v>128986476</v>
       </c>
       <c r="B83" t="n">
-        <v>80144</v>
+        <v>80145</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518965</v>
+        <v>519017</v>
       </c>
       <c r="R83" t="n">
-        <v>6982610</v>
+        <v>6982756</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,11 +8678,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8709,32 +8704,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986517</v>
+        <v>128986464</v>
       </c>
       <c r="B84" t="n">
-        <v>79295</v>
+        <v>57725</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518977</v>
+        <v>519152</v>
       </c>
       <c r="R84" t="n">
-        <v>6982833</v>
+        <v>6982692</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8780,6 +8775,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8806,10 +8806,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986476</v>
+        <v>128986727</v>
       </c>
       <c r="B85" t="n">
-        <v>80145</v>
+        <v>78796</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8817,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519017</v>
+        <v>519019</v>
       </c>
       <c r="R85" t="n">
-        <v>6982756</v>
+        <v>6982859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986464</v>
+        <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>57725</v>
+        <v>80144</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519152</v>
+        <v>518965</v>
       </c>
       <c r="R86" t="n">
-        <v>6982692</v>
+        <v>6982610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8978,7 +8978,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9005,32 +9005,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986711</v>
+        <v>128986517</v>
       </c>
       <c r="B87" t="n">
-        <v>80144</v>
+        <v>79295</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9040,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>519123</v>
+        <v>518977</v>
       </c>
       <c r="R87" t="n">
-        <v>6982555</v>
+        <v>6982833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,10 +9102,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986727</v>
+        <v>128986711</v>
       </c>
       <c r="B88" t="n">
-        <v>78796</v>
+        <v>80144</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9113,21 +9113,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519019</v>
+        <v>519123</v>
       </c>
       <c r="R88" t="n">
-        <v>6982859</v>
+        <v>6982555</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128986495</v>
       </c>
       <c r="B2" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986455</v>
+        <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>79629</v>
+        <v>98678</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518927</v>
+        <v>519104</v>
       </c>
       <c r="R3" t="n">
-        <v>6982838</v>
+        <v>6982578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>98676</v>
+        <v>79631</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R4" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B5" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R6" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986498</v>
+        <v>128986701</v>
       </c>
       <c r="B7" t="n">
-        <v>98676</v>
+        <v>80147</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519095</v>
+        <v>519098</v>
       </c>
       <c r="R7" t="n">
-        <v>6982524</v>
+        <v>6982579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986701</v>
+        <v>128986513</v>
       </c>
       <c r="B8" t="n">
-        <v>80145</v>
+        <v>92119</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519098</v>
+        <v>519097</v>
       </c>
       <c r="R8" t="n">
-        <v>6982579</v>
+        <v>6982582</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,11 +1338,6 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986513</v>
+        <v>128986706</v>
       </c>
       <c r="B9" t="n">
-        <v>92117</v>
+        <v>80146</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519097</v>
+        <v>518979</v>
       </c>
       <c r="R9" t="n">
-        <v>6982582</v>
+        <v>6982499</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986706</v>
+        <v>128986488</v>
       </c>
       <c r="B10" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518979</v>
+        <v>519036</v>
       </c>
       <c r="R10" t="n">
-        <v>6982499</v>
+        <v>6982781</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986488</v>
+        <v>128986494</v>
       </c>
       <c r="B11" t="n">
-        <v>80144</v>
+        <v>57831</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519036</v>
+        <v>519117</v>
       </c>
       <c r="R11" t="n">
-        <v>6982781</v>
+        <v>6982667</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,6 +1629,11 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986473</v>
+        <v>128986498</v>
       </c>
       <c r="B12" t="n">
-        <v>57566</v>
+        <v>98678</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518872</v>
+        <v>519095</v>
       </c>
       <c r="R12" t="n">
-        <v>6982457</v>
+        <v>6982524</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B13" t="n">
-        <v>57829</v>
+        <v>57568</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,16 +1768,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R13" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1857,7 +1857,7 @@
         <v>128986707</v>
       </c>
       <c r="B14" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986515</v>
+        <v>128986478</v>
       </c>
       <c r="B15" t="n">
-        <v>80179</v>
+        <v>75143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>1460</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519023</v>
+        <v>518949</v>
       </c>
       <c r="R15" t="n">
-        <v>6982774</v>
+        <v>6982601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B16" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R16" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2150,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986478</v>
+        <v>128986468</v>
       </c>
       <c r="B17" t="n">
-        <v>75141</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2161,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518949</v>
+        <v>518944</v>
       </c>
       <c r="R17" t="n">
-        <v>6982601</v>
+        <v>6982537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2221,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,32 +2252,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986468</v>
+        <v>128986515</v>
       </c>
       <c r="B18" t="n">
-        <v>57725</v>
+        <v>80181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518944</v>
+        <v>519023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982537</v>
+        <v>6982774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2313,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986458</v>
+        <v>128986485</v>
       </c>
       <c r="B19" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518751</v>
+        <v>519104</v>
       </c>
       <c r="R19" t="n">
-        <v>6982439</v>
+        <v>6982762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986505</v>
+        <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>98676</v>
+        <v>78798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519089</v>
+        <v>518952</v>
       </c>
       <c r="R20" t="n">
-        <v>6982812</v>
+        <v>6982811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986730</v>
+        <v>128986732</v>
       </c>
       <c r="B21" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518956</v>
+        <v>519137</v>
       </c>
       <c r="R21" t="n">
-        <v>6982758</v>
+        <v>6982624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2640,32 +2645,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986729</v>
+        <v>128986505</v>
       </c>
       <c r="B22" t="n">
-        <v>78796</v>
+        <v>98678</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518952</v>
+        <v>519089</v>
       </c>
       <c r="R22" t="n">
-        <v>6982811</v>
+        <v>6982812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2737,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986732</v>
+        <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519137</v>
+        <v>518956</v>
       </c>
       <c r="R23" t="n">
-        <v>6982624</v>
+        <v>6982758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2813,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986716</v>
+        <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>80144</v>
+        <v>80147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519149</v>
+        <v>519074</v>
       </c>
       <c r="R24" t="n">
-        <v>6982659</v>
+        <v>6982503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986489</v>
+        <v>128986700</v>
       </c>
       <c r="B25" t="n">
-        <v>80144</v>
+        <v>91542</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519023</v>
+        <v>518969</v>
       </c>
       <c r="R25" t="n">
-        <v>6982778</v>
+        <v>6982720</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986475</v>
+        <v>128986716</v>
       </c>
       <c r="B26" t="n">
-        <v>80145</v>
+        <v>80146</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519074</v>
+        <v>519149</v>
       </c>
       <c r="R26" t="n">
-        <v>6982503</v>
+        <v>6982659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986700</v>
+        <v>128986489</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518969</v>
+        <v>519023</v>
       </c>
       <c r="R27" t="n">
-        <v>6982720</v>
+        <v>6982778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,32 +3227,32 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986500</v>
+        <v>128986463</v>
       </c>
       <c r="B28" t="n">
-        <v>98676</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519090</v>
+        <v>519129</v>
       </c>
       <c r="R28" t="n">
-        <v>6982633</v>
+        <v>6982658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,32 +3329,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986501</v>
+        <v>128986492</v>
       </c>
       <c r="B29" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519091</v>
+        <v>518959</v>
       </c>
       <c r="R29" t="n">
-        <v>6982620</v>
+        <v>6982485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986463</v>
+        <v>128986500</v>
       </c>
       <c r="B30" t="n">
-        <v>57725</v>
+        <v>98678</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519129</v>
+        <v>519090</v>
       </c>
       <c r="R30" t="n">
-        <v>6982658</v>
+        <v>6982633</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,11 +3497,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986492</v>
+        <v>128986501</v>
       </c>
       <c r="B31" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>518959</v>
+        <v>519091</v>
       </c>
       <c r="R31" t="n">
-        <v>6982485</v>
+        <v>6982620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3623,7 +3623,7 @@
         <v>128986726</v>
       </c>
       <c r="B32" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>128986510</v>
       </c>
       <c r="B33" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3817,7 +3817,7 @@
         <v>128986467</v>
       </c>
       <c r="B34" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3919,7 +3919,7 @@
         <v>128986508</v>
       </c>
       <c r="B35" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>128986728</v>
       </c>
       <c r="B36" t="n">
-        <v>78796</v>
+        <v>78798</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986457</v>
+        <v>128986713</v>
       </c>
       <c r="B37" t="n">
-        <v>57725</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518740</v>
+        <v>519091</v>
       </c>
       <c r="R37" t="n">
-        <v>6982426</v>
+        <v>6982582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,11 +4181,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4212,10 +4207,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986713</v>
+        <v>128986723</v>
       </c>
       <c r="B38" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519091</v>
+        <v>519011</v>
       </c>
       <c r="R38" t="n">
-        <v>6982582</v>
+        <v>6982694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,10 +4304,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986723</v>
+        <v>128986710</v>
       </c>
       <c r="B39" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4344,10 +4339,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519011</v>
+        <v>519088</v>
       </c>
       <c r="R39" t="n">
-        <v>6982694</v>
+        <v>6982506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4406,10 +4401,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986710</v>
+        <v>128986457</v>
       </c>
       <c r="B40" t="n">
-        <v>80144</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4417,21 +4412,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4441,10 +4436,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519088</v>
+        <v>518740</v>
       </c>
       <c r="R40" t="n">
-        <v>6982506</v>
+        <v>6982426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,6 +4472,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4506,7 +4506,7 @@
         <v>128986708</v>
       </c>
       <c r="B41" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4603,7 +4603,7 @@
         <v>128986722</v>
       </c>
       <c r="B42" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4700,7 +4700,7 @@
         <v>128986509</v>
       </c>
       <c r="B43" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4991,7 +4991,7 @@
         <v>128986474</v>
       </c>
       <c r="B46" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986461</v>
+        <v>128986465</v>
       </c>
       <c r="B47" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519127</v>
+        <v>519109</v>
       </c>
       <c r="R47" t="n">
-        <v>6982642</v>
+        <v>6982756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5160,7 +5160,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5187,10 +5187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986465</v>
+        <v>128986461</v>
       </c>
       <c r="B48" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5222,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519109</v>
+        <v>519127</v>
       </c>
       <c r="R48" t="n">
-        <v>6982756</v>
+        <v>6982642</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5262,7 +5262,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5292,7 +5292,7 @@
         <v>128986719</v>
       </c>
       <c r="B49" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5389,7 +5389,7 @@
         <v>128986493</v>
       </c>
       <c r="B50" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5486,7 +5486,7 @@
         <v>128986482</v>
       </c>
       <c r="B51" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         <v>128986721</v>
       </c>
       <c r="B52" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5680,7 +5680,7 @@
         <v>128986484</v>
       </c>
       <c r="B53" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5777,7 +5777,7 @@
         <v>128986490</v>
       </c>
       <c r="B54" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>128986717</v>
       </c>
       <c r="B55" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128986481</v>
       </c>
       <c r="B56" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986497</v>
+        <v>128986477</v>
       </c>
       <c r="B57" t="n">
-        <v>98676</v>
+        <v>75031</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519074</v>
+        <v>519000</v>
       </c>
       <c r="R57" t="n">
-        <v>6982512</v>
+        <v>6982781</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986496</v>
+        <v>128986514</v>
       </c>
       <c r="B58" t="n">
-        <v>98676</v>
+        <v>80181</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518776</v>
+        <v>519096</v>
       </c>
       <c r="R58" t="n">
-        <v>6982502</v>
+        <v>6982528</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986514</v>
+        <v>128986486</v>
       </c>
       <c r="B59" t="n">
-        <v>80179</v>
+        <v>80146</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519096</v>
+        <v>519058</v>
       </c>
       <c r="R59" t="n">
-        <v>6982528</v>
+        <v>6982687</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,32 +6356,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986477</v>
+        <v>128986718</v>
       </c>
       <c r="B60" t="n">
-        <v>75029</v>
+        <v>80146</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519000</v>
+        <v>519135</v>
       </c>
       <c r="R60" t="n">
-        <v>6982781</v>
+        <v>6982678</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986486</v>
+        <v>128986715</v>
       </c>
       <c r="B61" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519058</v>
+        <v>519135</v>
       </c>
       <c r="R61" t="n">
-        <v>6982687</v>
+        <v>6982624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6550,10 +6550,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986718</v>
+        <v>128986724</v>
       </c>
       <c r="B62" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R62" t="n">
-        <v>6982678</v>
+        <v>6982673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,6 +6621,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6647,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986715</v>
+        <v>128986705</v>
       </c>
       <c r="B63" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6682,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519135</v>
+        <v>518809</v>
       </c>
       <c r="R63" t="n">
-        <v>6982624</v>
+        <v>6982489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6744,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986724</v>
+        <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6779,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518998</v>
+        <v>519074</v>
       </c>
       <c r="R64" t="n">
-        <v>6982673</v>
+        <v>6982512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6815,11 +6820,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986705</v>
+        <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518809</v>
+        <v>518776</v>
       </c>
       <c r="R65" t="n">
-        <v>6982489</v>
+        <v>6982502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986479</v>
+        <v>128986714</v>
       </c>
       <c r="B66" t="n">
-        <v>79063</v>
+        <v>80146</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518960</v>
+        <v>519102</v>
       </c>
       <c r="R66" t="n">
-        <v>6982834</v>
+        <v>6982627</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,32 +7040,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986714</v>
+        <v>128986479</v>
       </c>
       <c r="B67" t="n">
-        <v>80144</v>
+        <v>79065</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519102</v>
+        <v>518960</v>
       </c>
       <c r="R67" t="n">
-        <v>6982627</v>
+        <v>6982834</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7137,10 +7137,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986466</v>
+        <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7172,10 +7172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519061</v>
+        <v>518794</v>
       </c>
       <c r="R68" t="n">
-        <v>6982707</v>
+        <v>6982445</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,7 +7212,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986470</v>
+        <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7274,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>518794</v>
+        <v>519061</v>
       </c>
       <c r="R69" t="n">
-        <v>6982445</v>
+        <v>6982707</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7314,7 +7314,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7344,7 +7344,7 @@
         <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>57725</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7446,7 +7446,7 @@
         <v>128986511</v>
       </c>
       <c r="B71" t="n">
-        <v>56906</v>
+        <v>56908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7543,7 +7543,7 @@
         <v>128986472</v>
       </c>
       <c r="B72" t="n">
-        <v>57566</v>
+        <v>57568</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7737,7 +7737,7 @@
         <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>80145</v>
+        <v>80147</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7831,32 +7831,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986503</v>
+        <v>128986480</v>
       </c>
       <c r="B75" t="n">
-        <v>98676</v>
+        <v>80146</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519118</v>
+        <v>519008</v>
       </c>
       <c r="R75" t="n">
-        <v>6982684</v>
+        <v>6982457</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986480</v>
+        <v>128986491</v>
       </c>
       <c r="B76" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519008</v>
+        <v>518942</v>
       </c>
       <c r="R76" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8025,32 +8025,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986491</v>
+        <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>80144</v>
+        <v>98678</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518942</v>
+        <v>519118</v>
       </c>
       <c r="R77" t="n">
-        <v>6982579</v>
+        <v>6982684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128986712</v>
+        <v>128986725</v>
       </c>
       <c r="B78" t="n">
-        <v>80144</v>
+        <v>78798</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519121</v>
+        <v>519052</v>
       </c>
       <c r="R78" t="n">
-        <v>6982559</v>
+        <v>6982433</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986720</v>
+        <v>128986712</v>
       </c>
       <c r="B79" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519130</v>
+        <v>519121</v>
       </c>
       <c r="R79" t="n">
-        <v>6982756</v>
+        <v>6982559</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986725</v>
+        <v>128986720</v>
       </c>
       <c r="B80" t="n">
-        <v>78796</v>
+        <v>80146</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519052</v>
+        <v>519130</v>
       </c>
       <c r="R80" t="n">
-        <v>6982433</v>
+        <v>6982756</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8416,7 +8416,7 @@
         <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98676</v>
+        <v>98678</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986476</v>
+        <v>128986727</v>
       </c>
       <c r="B83" t="n">
-        <v>80145</v>
+        <v>78798</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519017</v>
+        <v>519019</v>
       </c>
       <c r="R83" t="n">
-        <v>6982756</v>
+        <v>6982859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986464</v>
+        <v>128986476</v>
       </c>
       <c r="B84" t="n">
-        <v>57725</v>
+        <v>80147</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519152</v>
+        <v>519017</v>
       </c>
       <c r="R84" t="n">
-        <v>6982692</v>
+        <v>6982756</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8775,11 +8775,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8806,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986727</v>
+        <v>128986464</v>
       </c>
       <c r="B85" t="n">
-        <v>78796</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519019</v>
+        <v>519152</v>
       </c>
       <c r="R85" t="n">
-        <v>6982859</v>
+        <v>6982692</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8877,6 +8872,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8906,7 +8906,7 @@
         <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9008,7 +9008,7 @@
         <v>128986517</v>
       </c>
       <c r="B87" t="n">
-        <v>79295</v>
+        <v>79297</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>128986711</v>
       </c>
       <c r="B88" t="n">
-        <v>80144</v>
+        <v>80146</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9202,7 +9202,7 @@
         <v>128986699</v>
       </c>
       <c r="B89" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B5" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R5" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98678</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R6" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986701</v>
+        <v>128986513</v>
       </c>
       <c r="B7" t="n">
-        <v>80147</v>
+        <v>92119</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519098</v>
+        <v>519097</v>
       </c>
       <c r="R7" t="n">
-        <v>6982579</v>
+        <v>6982582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986513</v>
+        <v>128986706</v>
       </c>
       <c r="B8" t="n">
-        <v>92119</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519097</v>
+        <v>518979</v>
       </c>
       <c r="R8" t="n">
-        <v>6982582</v>
+        <v>6982499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,7 +1359,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986706</v>
+        <v>128986488</v>
       </c>
       <c r="B9" t="n">
         <v>80146</v>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518979</v>
+        <v>519036</v>
       </c>
       <c r="R9" t="n">
-        <v>6982499</v>
+        <v>6982781</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,10 +1456,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986488</v>
+        <v>128986701</v>
       </c>
       <c r="B10" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,21 +1467,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519036</v>
+        <v>519098</v>
       </c>
       <c r="R10" t="n">
-        <v>6982781</v>
+        <v>6982579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1527,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,10 +1558,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B11" t="n">
-        <v>57831</v>
+        <v>57568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,16 +1569,16 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R11" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1629,11 +1629,6 @@
       <c r="AA11" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986498</v>
+        <v>128986494</v>
       </c>
       <c r="B12" t="n">
-        <v>98678</v>
+        <v>57831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519095</v>
+        <v>519117</v>
       </c>
       <c r="R12" t="n">
-        <v>6982524</v>
+        <v>6982667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986473</v>
+        <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>57568</v>
+        <v>98678</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518872</v>
+        <v>519095</v>
       </c>
       <c r="R13" t="n">
-        <v>6982457</v>
+        <v>6982524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986478</v>
+        <v>128986515</v>
       </c>
       <c r="B15" t="n">
-        <v>75143</v>
+        <v>80181</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1460</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518949</v>
+        <v>519023</v>
       </c>
       <c r="R15" t="n">
-        <v>6982601</v>
+        <v>6982774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986458</v>
+        <v>128986485</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518751</v>
+        <v>519104</v>
       </c>
       <c r="R16" t="n">
-        <v>6982439</v>
+        <v>6982762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986468</v>
+        <v>128986478</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>75143</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518944</v>
+        <v>518949</v>
       </c>
       <c r="R17" t="n">
-        <v>6982537</v>
+        <v>6982601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2221,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,32 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986515</v>
+        <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519023</v>
+        <v>518944</v>
       </c>
       <c r="R18" t="n">
-        <v>6982774</v>
+        <v>6982537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2313,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B19" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R19" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,6 +2415,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>80147</v>
+        <v>91542</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R24" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>91542</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986463</v>
+        <v>128986492</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519129</v>
+        <v>518959</v>
       </c>
       <c r="R28" t="n">
-        <v>6982658</v>
+        <v>6982485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986492</v>
+        <v>128986726</v>
       </c>
       <c r="B29" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518959</v>
+        <v>519089</v>
       </c>
       <c r="R29" t="n">
-        <v>6982485</v>
+        <v>6982825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3426,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986500</v>
+        <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519090</v>
+        <v>519129</v>
       </c>
       <c r="R30" t="n">
-        <v>6982633</v>
+        <v>6982658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3497,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986501</v>
+        <v>128986510</v>
       </c>
       <c r="B31" t="n">
-        <v>98678</v>
+        <v>56908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519091</v>
+        <v>519116</v>
       </c>
       <c r="R31" t="n">
-        <v>6982620</v>
+        <v>6982762</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,32 +3620,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986726</v>
+        <v>128986500</v>
       </c>
       <c r="B32" t="n">
-        <v>78798</v>
+        <v>98678</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519089</v>
+        <v>519090</v>
       </c>
       <c r="R32" t="n">
-        <v>6982825</v>
+        <v>6982633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,32 +3717,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986510</v>
+        <v>128986501</v>
       </c>
       <c r="B33" t="n">
-        <v>56908</v>
+        <v>98678</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519116</v>
+        <v>519091</v>
       </c>
       <c r="R33" t="n">
-        <v>6982762</v>
+        <v>6982620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>78798</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R34" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3916,32 +3911,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3951,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>78798</v>
+        <v>98678</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R36" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986474</v>
+        <v>128986719</v>
       </c>
       <c r="B46" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518955</v>
+        <v>519128</v>
       </c>
       <c r="R46" t="n">
-        <v>6982588</v>
+        <v>6982688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986465</v>
+        <v>128986493</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519109</v>
+        <v>518940</v>
       </c>
       <c r="R47" t="n">
-        <v>6982756</v>
+        <v>6982481</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,11 +5156,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5187,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986461</v>
+        <v>128986482</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5198,21 +5193,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519127</v>
+        <v>519112</v>
       </c>
       <c r="R48" t="n">
-        <v>6982642</v>
+        <v>6982533</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5258,11 +5253,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5289,7 +5279,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986719</v>
+        <v>128986721</v>
       </c>
       <c r="B49" t="n">
         <v>80146</v>
@@ -5324,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519128</v>
+        <v>519110</v>
       </c>
       <c r="R49" t="n">
-        <v>6982688</v>
+        <v>6982770</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5386,7 +5376,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986493</v>
+        <v>128986484</v>
       </c>
       <c r="B50" t="n">
         <v>80146</v>
@@ -5421,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518940</v>
+        <v>519153</v>
       </c>
       <c r="R50" t="n">
-        <v>6982481</v>
+        <v>6982677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5483,10 +5473,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986482</v>
+        <v>128986474</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5494,21 +5484,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5518,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519112</v>
+        <v>518955</v>
       </c>
       <c r="R51" t="n">
-        <v>6982533</v>
+        <v>6982588</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5580,10 +5570,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986721</v>
+        <v>128986465</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5591,21 +5581,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519110</v>
+        <v>519109</v>
       </c>
       <c r="R52" t="n">
-        <v>6982770</v>
+        <v>6982756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5651,6 +5641,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5677,10 +5672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986484</v>
+        <v>128986461</v>
       </c>
       <c r="B53" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5683,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519153</v>
+        <v>519127</v>
       </c>
       <c r="R53" t="n">
-        <v>6982677</v>
+        <v>6982642</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5748,6 +5743,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B57" t="n">
-        <v>75031</v>
+        <v>80181</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R57" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986514</v>
+        <v>128986486</v>
       </c>
       <c r="B58" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519096</v>
+        <v>519058</v>
       </c>
       <c r="R58" t="n">
-        <v>6982528</v>
+        <v>6982687</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986486</v>
+        <v>128986718</v>
       </c>
       <c r="B59" t="n">
         <v>80146</v>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519058</v>
+        <v>519135</v>
       </c>
       <c r="R59" t="n">
-        <v>6982687</v>
+        <v>6982678</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986718</v>
+        <v>128986715</v>
       </c>
       <c r="B60" t="n">
         <v>80146</v>
@@ -6394,7 +6394,7 @@
         <v>519135</v>
       </c>
       <c r="R60" t="n">
-        <v>6982678</v>
+        <v>6982624</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986715</v>
+        <v>128986724</v>
       </c>
       <c r="B61" t="n">
         <v>80146</v>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R61" t="n">
-        <v>6982624</v>
+        <v>6982673</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6524,6 +6524,11 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6550,7 +6555,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986724</v>
+        <v>128986705</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518998</v>
+        <v>518809</v>
       </c>
       <c r="R62" t="n">
-        <v>6982673</v>
+        <v>6982489</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,11 +6626,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,32 +6652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986705</v>
+        <v>128986477</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>75031</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518809</v>
+        <v>519000</v>
       </c>
       <c r="R63" t="n">
-        <v>6982489</v>
+        <v>6982781</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986460</v>
+        <v>128986511</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7352,16 +7352,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519008</v>
+        <v>518948</v>
       </c>
       <c r="R70" t="n">
-        <v>6982491</v>
+        <v>6982848</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,11 +7412,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7443,10 +7438,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986511</v>
+        <v>128986460</v>
       </c>
       <c r="B71" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7454,16 +7449,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518948</v>
+        <v>519008</v>
       </c>
       <c r="R71" t="n">
-        <v>6982848</v>
+        <v>6982491</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7514,6 +7509,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7734,10 +7734,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986702</v>
+        <v>128986480</v>
       </c>
       <c r="B74" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7745,21 +7745,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519099</v>
+        <v>519008</v>
       </c>
       <c r="R74" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986480</v>
+        <v>128986491</v>
       </c>
       <c r="B75" t="n">
         <v>80146</v>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519008</v>
+        <v>518942</v>
       </c>
       <c r="R75" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986491</v>
+        <v>128986702</v>
       </c>
       <c r="B76" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7963,7 +7963,7 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518942</v>
+        <v>519099</v>
       </c>
       <c r="R76" t="n">
         <v>6982579</v>
@@ -8122,10 +8122,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128986725</v>
+        <v>128986712</v>
       </c>
       <c r="B78" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8133,21 +8133,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519052</v>
+        <v>519121</v>
       </c>
       <c r="R78" t="n">
-        <v>6982433</v>
+        <v>6982559</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986712</v>
+        <v>128986720</v>
       </c>
       <c r="B79" t="n">
         <v>80146</v>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519121</v>
+        <v>519130</v>
       </c>
       <c r="R79" t="n">
-        <v>6982559</v>
+        <v>6982756</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986720</v>
+        <v>128986725</v>
       </c>
       <c r="B80" t="n">
-        <v>80146</v>
+        <v>78798</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519130</v>
+        <v>519052</v>
       </c>
       <c r="R80" t="n">
-        <v>6982756</v>
+        <v>6982433</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B83" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R83" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,6 +8678,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,32 +8709,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986476</v>
+        <v>128986517</v>
       </c>
       <c r="B84" t="n">
-        <v>80147</v>
+        <v>79297</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>6459</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519017</v>
+        <v>518977</v>
       </c>
       <c r="R84" t="n">
-        <v>6982756</v>
+        <v>6982833</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,10 +8806,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986464</v>
+        <v>128986711</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8817,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519152</v>
+        <v>519123</v>
       </c>
       <c r="R85" t="n">
-        <v>6982692</v>
+        <v>6982555</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8872,11 +8877,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986703</v>
+        <v>128986476</v>
       </c>
       <c r="B86" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518965</v>
+        <v>519017</v>
       </c>
       <c r="R86" t="n">
-        <v>6982610</v>
+        <v>6982756</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,11 +8974,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9005,32 +9000,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986517</v>
+        <v>128986727</v>
       </c>
       <c r="B87" t="n">
-        <v>79297</v>
+        <v>78798</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>6446</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9040,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518977</v>
+        <v>519019</v>
       </c>
       <c r="R87" t="n">
-        <v>6982833</v>
+        <v>6982859</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,10 +9097,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986711</v>
+        <v>128986464</v>
       </c>
       <c r="B88" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9113,21 +9108,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519123</v>
+        <v>519152</v>
       </c>
       <c r="R88" t="n">
-        <v>6982555</v>
+        <v>6982692</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9173,6 +9168,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986716</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>519149</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986716</v>
+        <v>128986489</v>
       </c>
       <c r="B26" t="n">
         <v>80146</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519149</v>
+        <v>519023</v>
       </c>
       <c r="R26" t="n">
-        <v>6982659</v>
+        <v>6982778</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986489</v>
+        <v>128986475</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519023</v>
+        <v>519074</v>
       </c>
       <c r="R27" t="n">
-        <v>6982778</v>
+        <v>6982503</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -7341,32 +7341,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986511</v>
+        <v>128986504</v>
       </c>
       <c r="B70" t="n">
-        <v>56908</v>
+        <v>98678</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518948</v>
+        <v>519130</v>
       </c>
       <c r="R70" t="n">
-        <v>6982848</v>
+        <v>6982767</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7438,10 +7438,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986460</v>
+        <v>128986511</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7449,16 +7449,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519008</v>
+        <v>518948</v>
       </c>
       <c r="R71" t="n">
-        <v>6982491</v>
+        <v>6982848</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,11 +7509,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7540,27 +7535,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986472</v>
+        <v>128986460</v>
       </c>
       <c r="B72" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7575,10 +7570,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519067</v>
+        <v>519008</v>
       </c>
       <c r="R72" t="n">
-        <v>6982817</v>
+        <v>6982491</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7611,6 +7606,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7637,32 +7637,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128986504</v>
+        <v>128986472</v>
       </c>
       <c r="B73" t="n">
-        <v>98678</v>
+        <v>57568</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519130</v>
+        <v>519067</v>
       </c>
       <c r="R73" t="n">
-        <v>6982767</v>
+        <v>6982817</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986703</v>
+        <v>128986476</v>
       </c>
       <c r="B83" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518965</v>
+        <v>519017</v>
       </c>
       <c r="R83" t="n">
-        <v>6982610</v>
+        <v>6982756</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,11 +8678,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8709,32 +8704,32 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986517</v>
+        <v>128986727</v>
       </c>
       <c r="B84" t="n">
-        <v>79297</v>
+        <v>78798</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6459</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518977</v>
+        <v>519019</v>
       </c>
       <c r="R84" t="n">
-        <v>6982833</v>
+        <v>6982859</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8806,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986711</v>
+        <v>128986464</v>
       </c>
       <c r="B85" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519123</v>
+        <v>519152</v>
       </c>
       <c r="R85" t="n">
-        <v>6982555</v>
+        <v>6982692</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8877,6 +8872,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986476</v>
+        <v>128986699</v>
       </c>
       <c r="B86" t="n">
-        <v>80147</v>
+        <v>79631</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519017</v>
+        <v>518952</v>
       </c>
       <c r="R86" t="n">
-        <v>6982756</v>
+        <v>6982811</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9000,10 +9000,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B87" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9011,21 +9011,21 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R87" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9071,6 +9071,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9097,32 +9102,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986464</v>
+        <v>128986517</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>79297</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9132,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519152</v>
+        <v>518977</v>
       </c>
       <c r="R88" t="n">
-        <v>6982692</v>
+        <v>6982833</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9168,11 +9173,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9199,10 +9199,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986699</v>
+        <v>128986711</v>
       </c>
       <c r="B89" t="n">
-        <v>79631</v>
+        <v>80146</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518952</v>
+        <v>519123</v>
       </c>
       <c r="R89" t="n">
-        <v>6982811</v>
+        <v>6982555</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -1071,7 +1071,7 @@
         <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1168,7 +1168,7 @@
         <v>128986513</v>
       </c>
       <c r="B7" t="n">
-        <v>92119</v>
+        <v>92134</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986706</v>
+        <v>128986488</v>
       </c>
       <c r="B8" t="n">
         <v>80146</v>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518979</v>
+        <v>519036</v>
       </c>
       <c r="R8" t="n">
-        <v>6982499</v>
+        <v>6982781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986488</v>
+        <v>128986494</v>
       </c>
       <c r="B9" t="n">
-        <v>80146</v>
+        <v>57831</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519036</v>
+        <v>519117</v>
       </c>
       <c r="R9" t="n">
-        <v>6982781</v>
+        <v>6982667</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986473</v>
+        <v>128986706</v>
       </c>
       <c r="B11" t="n">
-        <v>57568</v>
+        <v>80146</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518872</v>
+        <v>518979</v>
       </c>
       <c r="R11" t="n">
-        <v>6982457</v>
+        <v>6982499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,10 +1660,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
+        <v>57568</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1666,16 +1671,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R12" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1760,7 +1760,7 @@
         <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986478</v>
+        <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>75143</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518949</v>
+        <v>518751</v>
       </c>
       <c r="R17" t="n">
-        <v>6982601</v>
+        <v>6982439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986458</v>
+        <v>128986478</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>75143</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518751</v>
+        <v>518949</v>
       </c>
       <c r="R19" t="n">
-        <v>6982439</v>
+        <v>6982601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2546,7 +2546,7 @@
         <v>128986732</v>
       </c>
       <c r="B21" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>128986505</v>
       </c>
       <c r="B22" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>91542</v>
+        <v>80147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R24" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B27" t="n">
-        <v>80147</v>
+        <v>91540</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R27" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3623,7 +3623,7 @@
         <v>128986500</v>
       </c>
       <c r="B32" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3720,7 +3720,7 @@
         <v>128986501</v>
       </c>
       <c r="B33" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4016,7 +4016,7 @@
         <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986713</v>
+        <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519091</v>
+        <v>518740</v>
       </c>
       <c r="R37" t="n">
-        <v>6982582</v>
+        <v>6982426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,6 +4181,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4207,7 +4212,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986723</v>
+        <v>128986713</v>
       </c>
       <c r="B38" t="n">
         <v>80146</v>
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519011</v>
+        <v>519091</v>
       </c>
       <c r="R38" t="n">
-        <v>6982694</v>
+        <v>6982582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,7 +4309,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986710</v>
+        <v>128986723</v>
       </c>
       <c r="B39" t="n">
         <v>80146</v>
@@ -4339,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519088</v>
+        <v>519011</v>
       </c>
       <c r="R39" t="n">
-        <v>6982506</v>
+        <v>6982694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4401,10 +4406,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986457</v>
+        <v>128986710</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,21 +4417,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518740</v>
+        <v>519088</v>
       </c>
       <c r="R40" t="n">
-        <v>6982426</v>
+        <v>6982506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4472,11 +4477,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4700,7 +4700,7 @@
         <v>128986509</v>
       </c>
       <c r="B43" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4797,7 +4797,7 @@
         <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4894,7 +4894,7 @@
         <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986719</v>
+        <v>128986484</v>
       </c>
       <c r="B46" t="n">
         <v>80146</v>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519128</v>
+        <v>519153</v>
       </c>
       <c r="R46" t="n">
-        <v>6982688</v>
+        <v>6982677</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986493</v>
+        <v>128986465</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518940</v>
+        <v>519109</v>
       </c>
       <c r="R47" t="n">
-        <v>6982481</v>
+        <v>6982756</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,6 +5156,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5182,10 +5187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986482</v>
+        <v>128986461</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519112</v>
+        <v>519127</v>
       </c>
       <c r="R48" t="n">
-        <v>6982533</v>
+        <v>6982642</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5253,6 +5258,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5279,7 +5289,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986721</v>
+        <v>128986719</v>
       </c>
       <c r="B49" t="n">
         <v>80146</v>
@@ -5314,10 +5324,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519110</v>
+        <v>519128</v>
       </c>
       <c r="R49" t="n">
-        <v>6982770</v>
+        <v>6982688</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,7 +5386,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986484</v>
+        <v>128986493</v>
       </c>
       <c r="B50" t="n">
         <v>80146</v>
@@ -5411,10 +5421,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519153</v>
+        <v>518940</v>
       </c>
       <c r="R50" t="n">
-        <v>6982677</v>
+        <v>6982481</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,10 +5483,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986474</v>
+        <v>128986482</v>
       </c>
       <c r="B51" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5494,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5518,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518955</v>
+        <v>519112</v>
       </c>
       <c r="R51" t="n">
-        <v>6982588</v>
+        <v>6982533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5570,10 +5580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986465</v>
+        <v>128986721</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5581,21 +5591,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5605,10 +5615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519109</v>
+        <v>519110</v>
       </c>
       <c r="R52" t="n">
-        <v>6982756</v>
+        <v>6982770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5641,11 +5651,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5672,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986461</v>
+        <v>128986474</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519127</v>
+        <v>518955</v>
       </c>
       <c r="R53" t="n">
-        <v>6982642</v>
+        <v>6982588</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,11 +5748,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5774,7 +5774,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128986490</v>
+        <v>128986717</v>
       </c>
       <c r="B54" t="n">
         <v>80146</v>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519080</v>
+        <v>519151</v>
       </c>
       <c r="R54" t="n">
-        <v>6982814</v>
+        <v>6982660</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5871,7 +5871,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128986717</v>
+        <v>128986490</v>
       </c>
       <c r="B55" t="n">
         <v>80146</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519151</v>
+        <v>519080</v>
       </c>
       <c r="R55" t="n">
-        <v>6982660</v>
+        <v>6982814</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986477</v>
       </c>
       <c r="B57" t="n">
-        <v>80181</v>
+        <v>75031</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>6428</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>519000</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982781</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6356,7 +6356,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986715</v>
+        <v>128986724</v>
       </c>
       <c r="B60" t="n">
         <v>80146</v>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R60" t="n">
-        <v>6982624</v>
+        <v>6982673</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6427,6 +6427,11 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6453,32 +6458,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986724</v>
+        <v>128986514</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>80181</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6488,10 +6493,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>518998</v>
+        <v>519096</v>
       </c>
       <c r="R61" t="n">
-        <v>6982673</v>
+        <v>6982528</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6524,11 +6529,6 @@
       <c r="AA61" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6555,7 +6555,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986705</v>
+        <v>128986715</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -6590,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518809</v>
+        <v>519135</v>
       </c>
       <c r="R62" t="n">
-        <v>6982489</v>
+        <v>6982624</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6652,32 +6652,32 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986477</v>
+        <v>128986705</v>
       </c>
       <c r="B63" t="n">
-        <v>75031</v>
+        <v>80146</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519000</v>
+        <v>518809</v>
       </c>
       <c r="R63" t="n">
-        <v>6982781</v>
+        <v>6982489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6752,7 +6752,7 @@
         <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986714</v>
+        <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>80146</v>
+        <v>79065</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519102</v>
+        <v>518960</v>
       </c>
       <c r="R66" t="n">
-        <v>6982627</v>
+        <v>6982834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7040,32 +7040,32 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B67" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R67" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,6 +7111,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7137,7 +7142,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986470</v>
+        <v>128986466</v>
       </c>
       <c r="B68" t="n">
         <v>57727</v>
@@ -7172,10 +7177,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518794</v>
+        <v>519061</v>
       </c>
       <c r="R68" t="n">
-        <v>6982445</v>
+        <v>6982707</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7212,7 +7217,7 @@
       </c>
       <c r="AC68" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7244,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986466</v>
+        <v>128986714</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7255,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519061</v>
+        <v>519102</v>
       </c>
       <c r="R69" t="n">
-        <v>6982707</v>
+        <v>6982627</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7310,11 +7315,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,32 +7341,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986504</v>
+        <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>98678</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519130</v>
+        <v>519008</v>
       </c>
       <c r="R70" t="n">
-        <v>6982767</v>
+        <v>6982491</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,6 +7412,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7535,27 +7540,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986460</v>
+        <v>128986472</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7570,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519008</v>
+        <v>519067</v>
       </c>
       <c r="R72" t="n">
-        <v>6982491</v>
+        <v>6982817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7606,11 +7611,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7637,32 +7637,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128986472</v>
+        <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>57568</v>
+        <v>98704</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519067</v>
+        <v>519130</v>
       </c>
       <c r="R73" t="n">
-        <v>6982817</v>
+        <v>6982767</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7734,7 +7734,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986480</v>
+        <v>128986491</v>
       </c>
       <c r="B74" t="n">
         <v>80146</v>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519008</v>
+        <v>518942</v>
       </c>
       <c r="R74" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,10 +7831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986491</v>
+        <v>128986702</v>
       </c>
       <c r="B75" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7842,21 +7842,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,7 +7866,7 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>518942</v>
+        <v>519099</v>
       </c>
       <c r="R75" t="n">
         <v>6982579</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986702</v>
+        <v>128986480</v>
       </c>
       <c r="B76" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7939,21 +7939,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519099</v>
+        <v>519008</v>
       </c>
       <c r="R76" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8028,7 +8028,7 @@
         <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98678</v>
+        <v>98704</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986476</v>
+        <v>128986464</v>
       </c>
       <c r="B83" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519017</v>
+        <v>519152</v>
       </c>
       <c r="R83" t="n">
-        <v>6982756</v>
+        <v>6982692</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,6 +8678,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,10 +8709,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986727</v>
+        <v>128986476</v>
       </c>
       <c r="B84" t="n">
-        <v>78798</v>
+        <v>80147</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8720,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519019</v>
+        <v>519017</v>
       </c>
       <c r="R84" t="n">
-        <v>6982859</v>
+        <v>6982756</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,10 +8806,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986464</v>
+        <v>128986699</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>79631</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8817,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519152</v>
+        <v>518952</v>
       </c>
       <c r="R85" t="n">
-        <v>6982692</v>
+        <v>6982811</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8872,11 +8877,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986699</v>
+        <v>128986727</v>
       </c>
       <c r="B86" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518952</v>
+        <v>519019</v>
       </c>
       <c r="R86" t="n">
-        <v>6982811</v>
+        <v>6982859</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B3" t="n">
-        <v>98704</v>
+        <v>79631</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R3" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986455</v>
+        <v>128986731</v>
       </c>
       <c r="B4" t="n">
-        <v>79631</v>
+        <v>98705</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518927</v>
+        <v>519104</v>
       </c>
       <c r="R4" t="n">
-        <v>6982838</v>
+        <v>6982578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986513</v>
+        <v>128986488</v>
       </c>
       <c r="B7" t="n">
-        <v>92134</v>
+        <v>80146</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519097</v>
+        <v>519036</v>
       </c>
       <c r="R7" t="n">
-        <v>6982582</v>
+        <v>6982781</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1262,10 +1262,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986488</v>
+        <v>128986701</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519036</v>
+        <v>519098</v>
       </c>
       <c r="R8" t="n">
-        <v>6982781</v>
+        <v>6982579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1333,6 +1333,11 @@
       <c r="AA8" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B9" t="n">
-        <v>57831</v>
+        <v>57568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,16 +1375,16 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R9" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986701</v>
+        <v>128986498</v>
       </c>
       <c r="B10" t="n">
-        <v>80147</v>
+        <v>98705</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519098</v>
+        <v>519095</v>
       </c>
       <c r="R10" t="n">
-        <v>6982579</v>
+        <v>6982524</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1660,10 +1655,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986473</v>
+        <v>128986494</v>
       </c>
       <c r="B12" t="n">
-        <v>57568</v>
+        <v>57831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1671,16 +1666,16 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>102621</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>518872</v>
+        <v>519117</v>
       </c>
       <c r="R12" t="n">
-        <v>6982457</v>
+        <v>6982667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986498</v>
+        <v>128986513</v>
       </c>
       <c r="B13" t="n">
-        <v>98704</v>
+        <v>92135</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519095</v>
+        <v>519097</v>
       </c>
       <c r="R13" t="n">
-        <v>6982524</v>
+        <v>6982582</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986515</v>
+        <v>128986485</v>
       </c>
       <c r="B15" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519023</v>
+        <v>519104</v>
       </c>
       <c r="R15" t="n">
-        <v>6982774</v>
+        <v>6982762</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B16" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R16" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2119,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,7 +2150,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986458</v>
+        <v>128986468</v>
       </c>
       <c r="B17" t="n">
         <v>57727</v>
@@ -2180,10 +2185,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518751</v>
+        <v>518944</v>
       </c>
       <c r="R17" t="n">
-        <v>6982439</v>
+        <v>6982537</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2220,7 +2225,7 @@
       </c>
       <c r="AC17" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986468</v>
+        <v>128986478</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>75143</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518944</v>
+        <v>518949</v>
       </c>
       <c r="R18" t="n">
-        <v>6982537</v>
+        <v>6982601</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,32 +2349,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986478</v>
+        <v>128986515</v>
       </c>
       <c r="B19" t="n">
-        <v>75143</v>
+        <v>80181</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1460</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518949</v>
+        <v>519023</v>
       </c>
       <c r="R19" t="n">
-        <v>6982601</v>
+        <v>6982774</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986729</v>
+        <v>128986730</v>
       </c>
       <c r="B20" t="n">
-        <v>78798</v>
+        <v>98705</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518952</v>
+        <v>518956</v>
       </c>
       <c r="R20" t="n">
-        <v>6982811</v>
+        <v>6982758</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986732</v>
+        <v>128986505</v>
       </c>
       <c r="B21" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519137</v>
+        <v>519089</v>
       </c>
       <c r="R21" t="n">
-        <v>6982624</v>
+        <v>6982812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2614,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2640,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986505</v>
+        <v>128986732</v>
       </c>
       <c r="B22" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519089</v>
+        <v>519137</v>
       </c>
       <c r="R22" t="n">
-        <v>6982812</v>
+        <v>6982624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986729</v>
       </c>
       <c r="B23" t="n">
-        <v>98704</v>
+        <v>78798</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>518952</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>80147</v>
+        <v>91540</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R24" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986716</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519149</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982659</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,7 +3033,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986489</v>
+        <v>128986716</v>
       </c>
       <c r="B26" t="n">
         <v>80146</v>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519023</v>
+        <v>519149</v>
       </c>
       <c r="R26" t="n">
-        <v>6982778</v>
+        <v>6982659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3130,10 +3130,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986700</v>
+        <v>128986489</v>
       </c>
       <c r="B27" t="n">
-        <v>91540</v>
+        <v>80146</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3141,21 +3141,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3165,10 +3165,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>518969</v>
+        <v>519023</v>
       </c>
       <c r="R27" t="n">
-        <v>6982720</v>
+        <v>6982778</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986492</v>
+        <v>128986463</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518959</v>
+        <v>519129</v>
       </c>
       <c r="R28" t="n">
-        <v>6982485</v>
+        <v>6982658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986726</v>
+        <v>128986510</v>
       </c>
       <c r="B29" t="n">
-        <v>78798</v>
+        <v>56908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519089</v>
+        <v>519116</v>
       </c>
       <c r="R29" t="n">
-        <v>6982825</v>
+        <v>6982762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,32 +3426,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986463</v>
+        <v>128986501</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98705</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519129</v>
+        <v>519091</v>
       </c>
       <c r="R30" t="n">
-        <v>6982658</v>
+        <v>6982620</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,11 +3497,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986510</v>
+        <v>128986500</v>
       </c>
       <c r="B31" t="n">
-        <v>56908</v>
+        <v>98705</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519116</v>
+        <v>519090</v>
       </c>
       <c r="R31" t="n">
-        <v>6982762</v>
+        <v>6982633</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,32 +3620,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986500</v>
+        <v>128986726</v>
       </c>
       <c r="B32" t="n">
-        <v>98704</v>
+        <v>78798</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519090</v>
+        <v>519089</v>
       </c>
       <c r="R32" t="n">
-        <v>6982633</v>
+        <v>6982825</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,32 +3717,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986501</v>
+        <v>128986492</v>
       </c>
       <c r="B33" t="n">
-        <v>98704</v>
+        <v>80146</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519091</v>
+        <v>518959</v>
       </c>
       <c r="R33" t="n">
-        <v>6982620</v>
+        <v>6982485</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4016,7 +4016,7 @@
         <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4309,7 +4309,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986723</v>
+        <v>128986710</v>
       </c>
       <c r="B39" t="n">
         <v>80146</v>
@@ -4344,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519011</v>
+        <v>519088</v>
       </c>
       <c r="R39" t="n">
-        <v>6982694</v>
+        <v>6982506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4406,7 +4406,7 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986710</v>
+        <v>128986723</v>
       </c>
       <c r="B40" t="n">
         <v>80146</v>
@@ -4441,10 +4441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519088</v>
+        <v>519011</v>
       </c>
       <c r="R40" t="n">
-        <v>6982506</v>
+        <v>6982694</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986509</v>
+        <v>128986502</v>
       </c>
       <c r="B43" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518970</v>
+        <v>519145</v>
       </c>
       <c r="R43" t="n">
-        <v>6982749</v>
+        <v>6982681</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4797,7 +4797,7 @@
         <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4891,10 +4891,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986502</v>
+        <v>128986509</v>
       </c>
       <c r="B45" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519145</v>
+        <v>518970</v>
       </c>
       <c r="R45" t="n">
-        <v>6982681</v>
+        <v>6982749</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,7 +4988,7 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986484</v>
+        <v>128986719</v>
       </c>
       <c r="B46" t="n">
         <v>80146</v>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519153</v>
+        <v>519128</v>
       </c>
       <c r="R46" t="n">
-        <v>6982677</v>
+        <v>6982688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986465</v>
+        <v>128986493</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519109</v>
+        <v>518940</v>
       </c>
       <c r="R47" t="n">
-        <v>6982756</v>
+        <v>6982481</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,11 +5156,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5187,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986461</v>
+        <v>128986482</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5198,21 +5193,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519127</v>
+        <v>519112</v>
       </c>
       <c r="R48" t="n">
-        <v>6982642</v>
+        <v>6982533</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5258,11 +5253,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5289,7 +5279,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986719</v>
+        <v>128986721</v>
       </c>
       <c r="B49" t="n">
         <v>80146</v>
@@ -5324,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519128</v>
+        <v>519110</v>
       </c>
       <c r="R49" t="n">
-        <v>6982688</v>
+        <v>6982770</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5386,7 +5376,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986493</v>
+        <v>128986484</v>
       </c>
       <c r="B50" t="n">
         <v>80146</v>
@@ -5421,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518940</v>
+        <v>519153</v>
       </c>
       <c r="R50" t="n">
-        <v>6982481</v>
+        <v>6982677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5483,10 +5473,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986482</v>
+        <v>128986474</v>
       </c>
       <c r="B51" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5494,21 +5484,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5518,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519112</v>
+        <v>518955</v>
       </c>
       <c r="R51" t="n">
-        <v>6982533</v>
+        <v>6982588</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5580,10 +5570,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986721</v>
+        <v>128986465</v>
       </c>
       <c r="B52" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5591,21 +5581,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519110</v>
+        <v>519109</v>
       </c>
       <c r="R52" t="n">
-        <v>6982770</v>
+        <v>6982756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5651,6 +5641,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5677,10 +5672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986474</v>
+        <v>128986461</v>
       </c>
       <c r="B53" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5683,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518955</v>
+        <v>519127</v>
       </c>
       <c r="R53" t="n">
-        <v>6982588</v>
+        <v>6982642</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5748,6 +5743,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5774,7 +5774,7 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128986717</v>
+        <v>128986490</v>
       </c>
       <c r="B54" t="n">
         <v>80146</v>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519151</v>
+        <v>519080</v>
       </c>
       <c r="R54" t="n">
-        <v>6982660</v>
+        <v>6982814</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5871,7 +5871,7 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128986490</v>
+        <v>128986717</v>
       </c>
       <c r="B55" t="n">
         <v>80146</v>
@@ -5906,10 +5906,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519080</v>
+        <v>519151</v>
       </c>
       <c r="R55" t="n">
-        <v>6982814</v>
+        <v>6982660</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -6065,10 +6065,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B57" t="n">
-        <v>75031</v>
+        <v>80181</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6076,21 +6076,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R57" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,7 +6162,7 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986486</v>
+        <v>128986718</v>
       </c>
       <c r="B58" t="n">
         <v>80146</v>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519058</v>
+        <v>519135</v>
       </c>
       <c r="R58" t="n">
-        <v>6982687</v>
+        <v>6982678</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,7 +6259,7 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986718</v>
+        <v>128986715</v>
       </c>
       <c r="B59" t="n">
         <v>80146</v>
@@ -6297,7 +6297,7 @@
         <v>519135</v>
       </c>
       <c r="R59" t="n">
-        <v>6982678</v>
+        <v>6982624</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,32 +6356,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986724</v>
+        <v>128986477</v>
       </c>
       <c r="B60" t="n">
-        <v>80146</v>
+        <v>75031</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>518998</v>
+        <v>519000</v>
       </c>
       <c r="R60" t="n">
-        <v>6982673</v>
+        <v>6982781</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6427,11 +6427,6 @@
       <c r="AA60" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6458,32 +6453,32 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986514</v>
+        <v>128986486</v>
       </c>
       <c r="B61" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6493,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519096</v>
+        <v>519058</v>
       </c>
       <c r="R61" t="n">
-        <v>6982528</v>
+        <v>6982687</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6555,7 +6550,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986715</v>
+        <v>128986724</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -6590,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R62" t="n">
-        <v>6982624</v>
+        <v>6982673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6626,6 +6621,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6752,7 +6752,7 @@
         <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B66" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R66" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,6 +7014,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7040,7 +7045,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986470</v>
+        <v>128986466</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7075,10 +7080,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518794</v>
+        <v>519061</v>
       </c>
       <c r="R67" t="n">
-        <v>6982445</v>
+        <v>6982707</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7115,7 +7120,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7142,32 +7147,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986466</v>
+        <v>128986479</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79065</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7177,10 +7182,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>519061</v>
+        <v>518960</v>
       </c>
       <c r="R68" t="n">
-        <v>6982707</v>
+        <v>6982834</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7213,11 +7218,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7831,32 +7831,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986702</v>
+        <v>128986503</v>
       </c>
       <c r="B75" t="n">
-        <v>80147</v>
+        <v>98705</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519099</v>
+        <v>519118</v>
       </c>
       <c r="R75" t="n">
-        <v>6982579</v>
+        <v>6982684</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8025,32 +8025,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986503</v>
+        <v>128986702</v>
       </c>
       <c r="B77" t="n">
-        <v>98704</v>
+        <v>80147</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519118</v>
+        <v>519099</v>
       </c>
       <c r="R77" t="n">
-        <v>6982684</v>
+        <v>6982579</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8122,7 +8122,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128986712</v>
+        <v>128986720</v>
       </c>
       <c r="B78" t="n">
         <v>80146</v>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519121</v>
+        <v>519130</v>
       </c>
       <c r="R78" t="n">
-        <v>6982559</v>
+        <v>6982756</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8219,7 +8219,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986720</v>
+        <v>128986712</v>
       </c>
       <c r="B79" t="n">
         <v>80146</v>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519130</v>
+        <v>519121</v>
       </c>
       <c r="R79" t="n">
-        <v>6982756</v>
+        <v>6982559</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98704</v>
+        <v>98705</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,32 +8607,32 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986464</v>
+        <v>128986517</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>79297</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519152</v>
+        <v>518977</v>
       </c>
       <c r="R83" t="n">
-        <v>6982692</v>
+        <v>6982833</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,11 +8678,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8709,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986476</v>
+        <v>128986699</v>
       </c>
       <c r="B84" t="n">
-        <v>80147</v>
+        <v>79631</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8720,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519017</v>
+        <v>518952</v>
       </c>
       <c r="R84" t="n">
-        <v>6982756</v>
+        <v>6982811</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8806,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986699</v>
+        <v>128986727</v>
       </c>
       <c r="B85" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518952</v>
+        <v>519019</v>
       </c>
       <c r="R85" t="n">
-        <v>6982811</v>
+        <v>6982859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8903,10 +8898,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8909,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R86" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,6 +8969,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9000,7 +9000,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986703</v>
+        <v>128986711</v>
       </c>
       <c r="B87" t="n">
         <v>80146</v>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518965</v>
+        <v>519123</v>
       </c>
       <c r="R87" t="n">
-        <v>6982610</v>
+        <v>6982555</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9071,11 +9071,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9102,32 +9097,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986517</v>
+        <v>128986464</v>
       </c>
       <c r="B88" t="n">
-        <v>79297</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6459</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518977</v>
+        <v>519152</v>
       </c>
       <c r="R88" t="n">
-        <v>6982833</v>
+        <v>6982692</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9173,6 +9168,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9199,10 +9199,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986711</v>
+        <v>128986476</v>
       </c>
       <c r="B89" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519123</v>
+        <v>519017</v>
       </c>
       <c r="R89" t="n">
-        <v>6982555</v>
+        <v>6982756</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986495</v>
+        <v>128986455</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>79631</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518776</v>
+        <v>518927</v>
       </c>
       <c r="R2" t="n">
-        <v>6982385</v>
+        <v>6982838</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986455</v>
+        <v>128986495</v>
       </c>
       <c r="B3" t="n">
-        <v>79631</v>
+        <v>57831</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518927</v>
+        <v>518776</v>
       </c>
       <c r="R3" t="n">
-        <v>6982838</v>
+        <v>6982385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,12 +857,12 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
@@ -872,7 +872,7 @@
         <v>128986731</v>
       </c>
       <c r="B4" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -954,12 +954,12 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
@@ -1056,12 +1056,12 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
@@ -1071,7 +1071,7 @@
         <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,19 +1153,19 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986488</v>
+        <v>128986706</v>
       </c>
       <c r="B7" t="n">
         <v>80146</v>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519036</v>
+        <v>518979</v>
       </c>
       <c r="R7" t="n">
-        <v>6982781</v>
+        <v>6982499</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1250,22 +1250,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986701</v>
+        <v>128986488</v>
       </c>
       <c r="B8" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1273,21 +1273,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519098</v>
+        <v>519036</v>
       </c>
       <c r="R8" t="n">
-        <v>6982579</v>
+        <v>6982781</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1335,11 +1335,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1352,44 +1347,44 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986473</v>
+        <v>128986498</v>
       </c>
       <c r="B9" t="n">
-        <v>57568</v>
+        <v>98706</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518872</v>
+        <v>519095</v>
       </c>
       <c r="R9" t="n">
-        <v>6982457</v>
+        <v>6982524</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,44 +1444,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986498</v>
+        <v>128986701</v>
       </c>
       <c r="B10" t="n">
-        <v>98705</v>
+        <v>80147</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519095</v>
+        <v>519098</v>
       </c>
       <c r="R10" t="n">
-        <v>6982524</v>
+        <v>6982579</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1534,6 +1529,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD10" t="b">
         <v>0</v>
       </c>
@@ -1546,44 +1546,44 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986706</v>
+        <v>128986473</v>
       </c>
       <c r="B11" t="n">
-        <v>80146</v>
+        <v>57568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518979</v>
+        <v>518872</v>
       </c>
       <c r="R11" t="n">
-        <v>6982499</v>
+        <v>6982457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,12 +1643,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1745,12 +1745,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -1842,12 +1842,12 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
@@ -1939,22 +1939,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986485</v>
+        <v>128986478</v>
       </c>
       <c r="B15" t="n">
-        <v>80146</v>
+        <v>75143</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519104</v>
+        <v>518949</v>
       </c>
       <c r="R15" t="n">
-        <v>6982762</v>
+        <v>6982601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,12 +2036,12 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
@@ -2138,12 +2138,12 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
@@ -2240,44 +2240,44 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986478</v>
+        <v>128986515</v>
       </c>
       <c r="B18" t="n">
-        <v>75143</v>
+        <v>80181</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1460</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518949</v>
+        <v>519023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982601</v>
+        <v>6982774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2337,44 +2337,44 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986515</v>
+        <v>128986485</v>
       </c>
       <c r="B19" t="n">
-        <v>80181</v>
+        <v>80146</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519023</v>
+        <v>519104</v>
       </c>
       <c r="R19" t="n">
-        <v>6982774</v>
+        <v>6982762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,44 +2434,44 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986730</v>
+        <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>98705</v>
+        <v>78798</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518956</v>
+        <v>518952</v>
       </c>
       <c r="R20" t="n">
-        <v>6982758</v>
+        <v>6982811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,22 +2531,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986505</v>
+        <v>128986732</v>
       </c>
       <c r="B21" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519089</v>
+        <v>519137</v>
       </c>
       <c r="R21" t="n">
-        <v>6982812</v>
+        <v>6982624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2616,6 +2616,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
+        </is>
+      </c>
       <c r="AD21" t="b">
         <v>0</v>
       </c>
@@ -2628,22 +2633,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986732</v>
+        <v>128986505</v>
       </c>
       <c r="B22" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2675,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519137</v>
+        <v>519089</v>
       </c>
       <c r="R22" t="n">
-        <v>6982624</v>
+        <v>6982812</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,11 +2718,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2730,44 +2730,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986729</v>
+        <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>78798</v>
+        <v>98706</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518952</v>
+        <v>518956</v>
       </c>
       <c r="R23" t="n">
-        <v>6982811</v>
+        <v>6982758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,22 +2827,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>91540</v>
+        <v>80147</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R24" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,22 +2924,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B25" t="n">
-        <v>80147</v>
+        <v>91540</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,12 +3021,12 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
@@ -3118,12 +3118,12 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
@@ -3215,22 +3215,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986463</v>
+        <v>128986492</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519129</v>
+        <v>518959</v>
       </c>
       <c r="R28" t="n">
-        <v>6982658</v>
+        <v>6982485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3300,11 +3300,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD28" t="b">
         <v>0</v>
       </c>
@@ -3317,22 +3312,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986510</v>
+        <v>128986726</v>
       </c>
       <c r="B29" t="n">
-        <v>56908</v>
+        <v>78798</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519116</v>
+        <v>519089</v>
       </c>
       <c r="R29" t="n">
-        <v>6982762</v>
+        <v>6982825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3414,44 +3409,44 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986501</v>
+        <v>128986510</v>
       </c>
       <c r="B30" t="n">
-        <v>98705</v>
+        <v>56908</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519091</v>
+        <v>519116</v>
       </c>
       <c r="R30" t="n">
-        <v>6982620</v>
+        <v>6982762</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3511,44 +3506,44 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986500</v>
+        <v>128986463</v>
       </c>
       <c r="B31" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519090</v>
+        <v>519129</v>
       </c>
       <c r="R31" t="n">
-        <v>6982633</v>
+        <v>6982658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3596,6 +3591,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD31" t="b">
         <v>0</v>
       </c>
@@ -3608,44 +3608,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986726</v>
+        <v>128986501</v>
       </c>
       <c r="B32" t="n">
-        <v>78798</v>
+        <v>98706</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519089</v>
+        <v>519091</v>
       </c>
       <c r="R32" t="n">
-        <v>6982825</v>
+        <v>6982620</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,44 +3705,44 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986492</v>
+        <v>128986500</v>
       </c>
       <c r="B33" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>518959</v>
+        <v>519090</v>
       </c>
       <c r="R33" t="n">
-        <v>6982485</v>
+        <v>6982633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,12 +3802,12 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
@@ -3899,44 +3899,44 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986508</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>98706</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>518986</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3984,11 +3984,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD35" t="b">
         <v>0</v>
       </c>
@@ -4001,44 +3996,44 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B36" t="n">
-        <v>98705</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R36" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4086,6 +4081,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD36" t="b">
         <v>0</v>
       </c>
@@ -4098,22 +4098,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986457</v>
+        <v>128986713</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518740</v>
+        <v>519091</v>
       </c>
       <c r="R37" t="n">
-        <v>6982426</v>
+        <v>6982582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4183,11 +4183,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD37" t="b">
         <v>0</v>
       </c>
@@ -4200,19 +4195,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986713</v>
+        <v>128986723</v>
       </c>
       <c r="B38" t="n">
         <v>80146</v>
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519091</v>
+        <v>519011</v>
       </c>
       <c r="R38" t="n">
-        <v>6982582</v>
+        <v>6982694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4297,12 +4292,12 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
@@ -4394,22 +4389,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986723</v>
+        <v>128986457</v>
       </c>
       <c r="B40" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4417,21 +4412,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4441,10 +4436,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519011</v>
+        <v>518740</v>
       </c>
       <c r="R40" t="n">
-        <v>6982694</v>
+        <v>6982426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4479,6 +4474,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD40" t="b">
         <v>0</v>
       </c>
@@ -4491,44 +4491,44 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986708</v>
+        <v>128986509</v>
       </c>
       <c r="B41" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518983</v>
+        <v>518970</v>
       </c>
       <c r="R41" t="n">
-        <v>6982481</v>
+        <v>6982749</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4588,19 +4588,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986722</v>
+        <v>128986708</v>
       </c>
       <c r="B42" t="n">
         <v>80146</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518975</v>
+        <v>518983</v>
       </c>
       <c r="R42" t="n">
-        <v>6982829</v>
+        <v>6982481</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4685,44 +4685,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986502</v>
+        <v>128986722</v>
       </c>
       <c r="B43" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519145</v>
+        <v>518975</v>
       </c>
       <c r="R43" t="n">
-        <v>6982681</v>
+        <v>6982829</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4782,12 +4782,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -4797,7 +4797,7 @@
         <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4879,22 +4879,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986509</v>
+        <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518970</v>
+        <v>519145</v>
       </c>
       <c r="R45" t="n">
-        <v>6982749</v>
+        <v>6982681</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4976,12 +4976,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5073,12 +5073,12 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
@@ -5170,12 +5170,12 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
@@ -5267,12 +5267,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -5364,12 +5364,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5461,22 +5461,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986474</v>
+        <v>128986465</v>
       </c>
       <c r="B51" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>518955</v>
+        <v>519109</v>
       </c>
       <c r="R51" t="n">
-        <v>6982588</v>
+        <v>6982756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5546,6 +5546,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD51" t="b">
         <v>0</v>
       </c>
@@ -5558,19 +5563,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986465</v>
+        <v>128986461</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5605,10 +5610,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519109</v>
+        <v>519127</v>
       </c>
       <c r="R52" t="n">
-        <v>6982756</v>
+        <v>6982642</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5645,7 +5650,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5660,22 +5665,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986461</v>
+        <v>128986474</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80147</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519127</v>
+        <v>518955</v>
       </c>
       <c r="R53" t="n">
-        <v>6982642</v>
+        <v>6982588</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5745,11 +5750,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5762,12 +5762,12 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
@@ -5859,12 +5859,12 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
@@ -5956,12 +5956,12 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
@@ -6053,44 +6053,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986496</v>
       </c>
       <c r="B57" t="n">
-        <v>80181</v>
+        <v>98706</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>518776</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982502</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6150,44 +6150,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986718</v>
+        <v>128986497</v>
       </c>
       <c r="B58" t="n">
-        <v>80146</v>
+        <v>98706</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519135</v>
+        <v>519074</v>
       </c>
       <c r="R58" t="n">
-        <v>6982678</v>
+        <v>6982512</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6247,44 +6247,44 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986715</v>
+        <v>128986477</v>
       </c>
       <c r="B59" t="n">
-        <v>80146</v>
+        <v>75031</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519135</v>
+        <v>519000</v>
       </c>
       <c r="R59" t="n">
-        <v>6982624</v>
+        <v>6982781</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6344,22 +6344,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986477</v>
+        <v>128986514</v>
       </c>
       <c r="B60" t="n">
-        <v>75031</v>
+        <v>80181</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6367,21 +6367,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6428</v>
+        <v>6463</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519000</v>
+        <v>519096</v>
       </c>
       <c r="R60" t="n">
-        <v>6982781</v>
+        <v>6982528</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6441,12 +6441,12 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
@@ -6538,19 +6538,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986724</v>
+        <v>128986718</v>
       </c>
       <c r="B62" t="n">
         <v>80146</v>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518998</v>
+        <v>519135</v>
       </c>
       <c r="R62" t="n">
-        <v>6982673</v>
+        <v>6982678</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6623,11 +6623,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På asp</t>
-        </is>
-      </c>
       <c r="AD62" t="b">
         <v>0</v>
       </c>
@@ -6640,19 +6635,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986705</v>
+        <v>128986715</v>
       </c>
       <c r="B63" t="n">
         <v>80146</v>
@@ -6687,10 +6682,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518809</v>
+        <v>519135</v>
       </c>
       <c r="R63" t="n">
-        <v>6982489</v>
+        <v>6982624</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6737,44 +6732,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986497</v>
+        <v>128986724</v>
       </c>
       <c r="B64" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6779,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519074</v>
+        <v>518998</v>
       </c>
       <c r="R64" t="n">
-        <v>6982512</v>
+        <v>6982673</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,6 +6817,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -6834,44 +6834,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986496</v>
+        <v>128986705</v>
       </c>
       <c r="B65" t="n">
-        <v>98705</v>
+        <v>80146</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518776</v>
+        <v>518809</v>
       </c>
       <c r="R65" t="n">
-        <v>6982502</v>
+        <v>6982489</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6931,44 +6931,44 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>79065</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R66" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7016,11 +7016,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
-        </is>
-      </c>
       <c r="AD66" t="b">
         <v>0</v>
       </c>
@@ -7033,22 +7028,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986466</v>
+        <v>128986714</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>80146</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519061</v>
+        <v>519102</v>
       </c>
       <c r="R67" t="n">
-        <v>6982707</v>
+        <v>6982627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7118,11 +7113,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
-        </is>
-      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7135,44 +7125,44 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>79065</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7182,10 +7172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R68" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7220,6 +7210,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -7232,22 +7227,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986714</v>
+        <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7255,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519102</v>
+        <v>519061</v>
       </c>
       <c r="R69" t="n">
-        <v>6982627</v>
+        <v>6982707</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7317,6 +7312,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7329,12 +7329,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7431,12 +7431,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -7528,12 +7528,12 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
@@ -7625,12 +7625,12 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7722,22 +7722,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986491</v>
+        <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>80146</v>
+        <v>80147</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7745,21 +7745,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,7 +7769,7 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>518942</v>
+        <v>519099</v>
       </c>
       <c r="R74" t="n">
         <v>6982579</v>
@@ -7819,12 +7819,12 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
@@ -7834,7 +7834,7 @@
         <v>128986503</v>
       </c>
       <c r="B75" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7916,12 +7916,12 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
@@ -8013,22 +8013,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986702</v>
+        <v>128986491</v>
       </c>
       <c r="B77" t="n">
-        <v>80147</v>
+        <v>80146</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8036,21 +8036,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519099</v>
+        <v>518942</v>
       </c>
       <c r="R77" t="n">
         <v>6982579</v>
@@ -8110,19 +8110,19 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128986720</v>
+        <v>128986712</v>
       </c>
       <c r="B78" t="n">
         <v>80146</v>
@@ -8157,10 +8157,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519130</v>
+        <v>519121</v>
       </c>
       <c r="R78" t="n">
-        <v>6982756</v>
+        <v>6982559</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8207,19 +8207,19 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986712</v>
+        <v>128986720</v>
       </c>
       <c r="B79" t="n">
         <v>80146</v>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519121</v>
+        <v>519130</v>
       </c>
       <c r="R79" t="n">
-        <v>6982559</v>
+        <v>6982756</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8304,12 +8304,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -8401,12 +8401,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -8498,12 +8498,12 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98705</v>
+        <v>98706</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8595,44 +8595,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986517</v>
+        <v>128986476</v>
       </c>
       <c r="B83" t="n">
-        <v>79297</v>
+        <v>80147</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6459</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518977</v>
+        <v>519017</v>
       </c>
       <c r="R83" t="n">
-        <v>6982833</v>
+        <v>6982756</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8692,22 +8692,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986699</v>
+        <v>128986727</v>
       </c>
       <c r="B84" t="n">
-        <v>79631</v>
+        <v>78798</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518952</v>
+        <v>519019</v>
       </c>
       <c r="R84" t="n">
-        <v>6982811</v>
+        <v>6982859</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8789,22 +8789,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B85" t="n">
-        <v>78798</v>
+        <v>80146</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R85" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8874,6 +8874,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -8886,44 +8891,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986703</v>
+        <v>128986517</v>
       </c>
       <c r="B86" t="n">
-        <v>80146</v>
+        <v>79297</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8933,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518965</v>
+        <v>518977</v>
       </c>
       <c r="R86" t="n">
-        <v>6982610</v>
+        <v>6982833</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8971,11 +8976,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
-        </is>
-      </c>
       <c r="AD86" t="b">
         <v>0</v>
       </c>
@@ -8988,12 +8988,12 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
@@ -9085,12 +9085,12 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
@@ -9187,22 +9187,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986476</v>
+        <v>128986699</v>
       </c>
       <c r="B89" t="n">
-        <v>80147</v>
+        <v>79631</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519017</v>
+        <v>518952</v>
       </c>
       <c r="R89" t="n">
-        <v>6982756</v>
+        <v>6982811</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9284,12 +9284,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Löthman</t>
+          <t>Marielle Andersson</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986455</v>
+        <v>128986495</v>
       </c>
       <c r="B2" t="n">
-        <v>79631</v>
+        <v>57831</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>103031</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518927</v>
+        <v>518776</v>
       </c>
       <c r="R2" t="n">
-        <v>6982838</v>
+        <v>6982385</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986495</v>
+        <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>57831</v>
+        <v>98710</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518776</v>
+        <v>519104</v>
       </c>
       <c r="R3" t="n">
-        <v>6982385</v>
+        <v>6982578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>98706</v>
+        <v>79633</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R4" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,10 +1165,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986706</v>
+        <v>128986701</v>
       </c>
       <c r="B7" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1176,21 +1176,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>518979</v>
+        <v>519098</v>
       </c>
       <c r="R7" t="n">
-        <v>6982499</v>
+        <v>6982579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986488</v>
+        <v>128986473</v>
       </c>
       <c r="B8" t="n">
-        <v>80146</v>
+        <v>57568</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519036</v>
+        <v>518872</v>
       </c>
       <c r="R8" t="n">
-        <v>6982781</v>
+        <v>6982457</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986498</v>
+        <v>128986513</v>
       </c>
       <c r="B9" t="n">
-        <v>98706</v>
+        <v>92138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519095</v>
+        <v>519097</v>
       </c>
       <c r="R9" t="n">
-        <v>6982524</v>
+        <v>6982582</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1456,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986701</v>
+        <v>128986706</v>
       </c>
       <c r="B10" t="n">
-        <v>80147</v>
+        <v>80148</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1467,21 +1472,21 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1491,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519098</v>
+        <v>518979</v>
       </c>
       <c r="R10" t="n">
-        <v>6982579</v>
+        <v>6982499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1527,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986473</v>
+        <v>128986488</v>
       </c>
       <c r="B11" t="n">
-        <v>57568</v>
+        <v>80148</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518872</v>
+        <v>519036</v>
       </c>
       <c r="R11" t="n">
-        <v>6982457</v>
+        <v>6982781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986513</v>
+        <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>92135</v>
+        <v>98710</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519097</v>
+        <v>519095</v>
       </c>
       <c r="R13" t="n">
-        <v>6982582</v>
+        <v>6982524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1857,7 +1857,7 @@
         <v>128986707</v>
       </c>
       <c r="B14" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1954,7 +1954,7 @@
         <v>128986478</v>
       </c>
       <c r="B15" t="n">
-        <v>75143</v>
+        <v>75145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2048,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80183</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R16" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2150,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986468</v>
+        <v>128986485</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2161,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2185,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518944</v>
+        <v>519104</v>
       </c>
       <c r="R17" t="n">
-        <v>6982537</v>
+        <v>6982762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2221,11 +2216,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,32 +2242,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986515</v>
+        <v>128986458</v>
       </c>
       <c r="B18" t="n">
-        <v>80181</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519023</v>
+        <v>518751</v>
       </c>
       <c r="R18" t="n">
-        <v>6982774</v>
+        <v>6982439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2313,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986485</v>
+        <v>128986468</v>
       </c>
       <c r="B19" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519104</v>
+        <v>518944</v>
       </c>
       <c r="R19" t="n">
-        <v>6982762</v>
+        <v>6982537</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,6 +2415,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2449,7 +2449,7 @@
         <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2546,7 +2546,7 @@
         <v>128986732</v>
       </c>
       <c r="B21" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2648,7 +2648,7 @@
         <v>128986505</v>
       </c>
       <c r="B22" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2745,7 +2745,7 @@
         <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2842,7 +2842,7 @@
         <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>80147</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986700</v>
+        <v>128986716</v>
       </c>
       <c r="B25" t="n">
-        <v>91540</v>
+        <v>80148</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518969</v>
+        <v>519149</v>
       </c>
       <c r="R25" t="n">
-        <v>6982720</v>
+        <v>6982659</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986716</v>
+        <v>128986700</v>
       </c>
       <c r="B26" t="n">
-        <v>80146</v>
+        <v>91543</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519149</v>
+        <v>518969</v>
       </c>
       <c r="R26" t="n">
-        <v>6982659</v>
+        <v>6982720</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3133,7 +3133,7 @@
         <v>128986489</v>
       </c>
       <c r="B27" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986492</v>
+        <v>128986510</v>
       </c>
       <c r="B28" t="n">
-        <v>80146</v>
+        <v>56908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518959</v>
+        <v>519116</v>
       </c>
       <c r="R28" t="n">
-        <v>6982485</v>
+        <v>6982762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986726</v>
+        <v>128986492</v>
       </c>
       <c r="B29" t="n">
-        <v>78798</v>
+        <v>80148</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519089</v>
+        <v>518959</v>
       </c>
       <c r="R29" t="n">
-        <v>6982825</v>
+        <v>6982485</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986510</v>
+        <v>128986726</v>
       </c>
       <c r="B30" t="n">
-        <v>56908</v>
+        <v>78800</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519116</v>
+        <v>519089</v>
       </c>
       <c r="R30" t="n">
-        <v>6982762</v>
+        <v>6982825</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986501</v>
+        <v>128986500</v>
       </c>
       <c r="B32" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519091</v>
+        <v>519090</v>
       </c>
       <c r="R32" t="n">
-        <v>6982620</v>
+        <v>6982633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986500</v>
+        <v>128986501</v>
       </c>
       <c r="B33" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519090</v>
+        <v>519091</v>
       </c>
       <c r="R33" t="n">
-        <v>6982633</v>
+        <v>6982620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3817,7 +3817,7 @@
         <v>128986728</v>
       </c>
       <c r="B34" t="n">
-        <v>78798</v>
+        <v>78800</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>98706</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4008,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986467</v>
+        <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4043,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518933</v>
+        <v>518986</v>
       </c>
       <c r="R36" t="n">
-        <v>6982538</v>
+        <v>6982827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,11 +4084,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4113,7 +4113,7 @@
         <v>128986713</v>
       </c>
       <c r="B37" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4210,7 +4210,7 @@
         <v>128986723</v>
       </c>
       <c r="B38" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4307,7 +4307,7 @@
         <v>128986710</v>
       </c>
       <c r="B39" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4506,7 +4506,7 @@
         <v>128986509</v>
       </c>
       <c r="B41" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986708</v>
+        <v>128986499</v>
       </c>
       <c r="B42" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518983</v>
+        <v>519106</v>
       </c>
       <c r="R42" t="n">
-        <v>6982481</v>
+        <v>6982616</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,32 +4697,32 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986722</v>
+        <v>128986502</v>
       </c>
       <c r="B43" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518975</v>
+        <v>519145</v>
       </c>
       <c r="R43" t="n">
-        <v>6982829</v>
+        <v>6982681</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986499</v>
+        <v>128986708</v>
       </c>
       <c r="B44" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519106</v>
+        <v>518983</v>
       </c>
       <c r="R44" t="n">
-        <v>6982616</v>
+        <v>6982481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986502</v>
+        <v>128986722</v>
       </c>
       <c r="B45" t="n">
-        <v>98706</v>
+        <v>80148</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519145</v>
+        <v>518975</v>
       </c>
       <c r="R45" t="n">
-        <v>6982681</v>
+        <v>6982829</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986719</v>
+        <v>128986474</v>
       </c>
       <c r="B46" t="n">
-        <v>80146</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519128</v>
+        <v>518955</v>
       </c>
       <c r="R46" t="n">
-        <v>6982688</v>
+        <v>6982588</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986493</v>
+        <v>128986482</v>
       </c>
       <c r="B47" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518940</v>
+        <v>519112</v>
       </c>
       <c r="R47" t="n">
-        <v>6982481</v>
+        <v>6982533</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986482</v>
+        <v>128986721</v>
       </c>
       <c r="B48" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519112</v>
+        <v>519110</v>
       </c>
       <c r="R48" t="n">
-        <v>6982533</v>
+        <v>6982770</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,10 +5279,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986721</v>
+        <v>128986719</v>
       </c>
       <c r="B49" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519110</v>
+        <v>519128</v>
       </c>
       <c r="R49" t="n">
-        <v>6982770</v>
+        <v>6982688</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986484</v>
+        <v>128986493</v>
       </c>
       <c r="B50" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519153</v>
+        <v>518940</v>
       </c>
       <c r="R50" t="n">
-        <v>6982677</v>
+        <v>6982481</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986465</v>
+        <v>128986484</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519109</v>
+        <v>519153</v>
       </c>
       <c r="R51" t="n">
-        <v>6982756</v>
+        <v>6982677</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,11 +5544,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5575,7 +5570,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986461</v>
+        <v>128986465</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5610,10 +5605,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519127</v>
+        <v>519109</v>
       </c>
       <c r="R52" t="n">
-        <v>6982642</v>
+        <v>6982756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5650,7 +5645,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5677,10 +5672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986474</v>
+        <v>128986461</v>
       </c>
       <c r="B53" t="n">
-        <v>80147</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5683,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518955</v>
+        <v>519127</v>
       </c>
       <c r="R53" t="n">
-        <v>6982588</v>
+        <v>6982642</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5748,6 +5743,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -5777,7 +5777,7 @@
         <v>128986490</v>
       </c>
       <c r="B54" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>128986717</v>
       </c>
       <c r="B55" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128986481</v>
       </c>
       <c r="B56" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986496</v>
+        <v>128986514</v>
       </c>
       <c r="B57" t="n">
-        <v>98706</v>
+        <v>80183</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>518776</v>
+        <v>519096</v>
       </c>
       <c r="R57" t="n">
-        <v>6982502</v>
+        <v>6982528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986497</v>
+        <v>128986477</v>
       </c>
       <c r="B58" t="n">
-        <v>98706</v>
+        <v>75033</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519074</v>
+        <v>519000</v>
       </c>
       <c r="R58" t="n">
-        <v>6982512</v>
+        <v>6982781</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986477</v>
+        <v>128986486</v>
       </c>
       <c r="B59" t="n">
-        <v>75031</v>
+        <v>80148</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519000</v>
+        <v>519058</v>
       </c>
       <c r="R59" t="n">
-        <v>6982781</v>
+        <v>6982687</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,32 +6356,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986514</v>
+        <v>128986718</v>
       </c>
       <c r="B60" t="n">
-        <v>80181</v>
+        <v>80148</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519096</v>
+        <v>519135</v>
       </c>
       <c r="R60" t="n">
-        <v>6982528</v>
+        <v>6982678</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,10 +6453,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986486</v>
+        <v>128986715</v>
       </c>
       <c r="B61" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519058</v>
+        <v>519135</v>
       </c>
       <c r="R61" t="n">
-        <v>6982687</v>
+        <v>6982624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6550,10 +6550,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986718</v>
+        <v>128986724</v>
       </c>
       <c r="B62" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R62" t="n">
-        <v>6982678</v>
+        <v>6982673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,6 +6621,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6647,10 +6652,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986715</v>
+        <v>128986705</v>
       </c>
       <c r="B63" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6682,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519135</v>
+        <v>518809</v>
       </c>
       <c r="R63" t="n">
-        <v>6982624</v>
+        <v>6982489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6744,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986724</v>
+        <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6779,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518998</v>
+        <v>519074</v>
       </c>
       <c r="R64" t="n">
-        <v>6982673</v>
+        <v>6982512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6815,11 +6820,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986705</v>
+        <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>80146</v>
+        <v>98710</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518809</v>
+        <v>518776</v>
       </c>
       <c r="R65" t="n">
-        <v>6982489</v>
+        <v>6982502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6946,7 +6946,7 @@
         <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>79065</v>
+        <v>79067</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7043,7 +7043,7 @@
         <v>128986714</v>
       </c>
       <c r="B67" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7341,10 +7341,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986460</v>
+        <v>128986511</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7352,16 +7352,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519008</v>
+        <v>518948</v>
       </c>
       <c r="R70" t="n">
-        <v>6982491</v>
+        <v>6982848</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,11 +7412,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7443,10 +7438,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986511</v>
+        <v>128986460</v>
       </c>
       <c r="B71" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7454,16 +7449,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518948</v>
+        <v>519008</v>
       </c>
       <c r="R71" t="n">
-        <v>6982848</v>
+        <v>6982491</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7514,6 +7509,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7540,32 +7540,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986472</v>
+        <v>128986504</v>
       </c>
       <c r="B72" t="n">
-        <v>57568</v>
+        <v>98710</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519067</v>
+        <v>519130</v>
       </c>
       <c r="R72" t="n">
-        <v>6982817</v>
+        <v>6982767</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7637,32 +7637,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128986504</v>
+        <v>128986472</v>
       </c>
       <c r="B73" t="n">
-        <v>98706</v>
+        <v>57568</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519130</v>
+        <v>519067</v>
       </c>
       <c r="R73" t="n">
-        <v>6982767</v>
+        <v>6982817</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986702</v>
+        <v>128986503</v>
       </c>
       <c r="B74" t="n">
-        <v>80147</v>
+        <v>98710</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519099</v>
+        <v>519118</v>
       </c>
       <c r="R74" t="n">
-        <v>6982579</v>
+        <v>6982684</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,32 +7831,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986503</v>
+        <v>128986702</v>
       </c>
       <c r="B75" t="n">
-        <v>98706</v>
+        <v>80149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519118</v>
+        <v>519099</v>
       </c>
       <c r="R75" t="n">
-        <v>6982684</v>
+        <v>6982579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,10 +7928,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986480</v>
+        <v>128986491</v>
       </c>
       <c r="B76" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519008</v>
+        <v>518942</v>
       </c>
       <c r="R76" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8025,10 +8025,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986491</v>
+        <v>128986480</v>
       </c>
       <c r="B77" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518942</v>
+        <v>519008</v>
       </c>
       <c r="R77" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8125,7 +8125,7 @@
         <v>128986712</v>
       </c>
       <c r="B78" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986720</v>
+        <v>128986725</v>
       </c>
       <c r="B79" t="n">
-        <v>80146</v>
+        <v>78800</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519130</v>
+        <v>519052</v>
       </c>
       <c r="R79" t="n">
-        <v>6982756</v>
+        <v>6982433</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986725</v>
+        <v>128986720</v>
       </c>
       <c r="B80" t="n">
-        <v>78798</v>
+        <v>80148</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519052</v>
+        <v>519130</v>
       </c>
       <c r="R80" t="n">
-        <v>6982433</v>
+        <v>6982756</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8416,7 +8416,7 @@
         <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98706</v>
+        <v>98710</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986476</v>
+        <v>128986727</v>
       </c>
       <c r="B83" t="n">
-        <v>80147</v>
+        <v>78800</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519017</v>
+        <v>519019</v>
       </c>
       <c r="R83" t="n">
-        <v>6982756</v>
+        <v>6982859</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986727</v>
+        <v>128986711</v>
       </c>
       <c r="B84" t="n">
-        <v>78798</v>
+        <v>80148</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519019</v>
+        <v>519123</v>
       </c>
       <c r="R84" t="n">
-        <v>6982859</v>
+        <v>6982555</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986703</v>
+        <v>128986464</v>
       </c>
       <c r="B85" t="n">
-        <v>80146</v>
+        <v>57727</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518965</v>
+        <v>519152</v>
       </c>
       <c r="R85" t="n">
-        <v>6982610</v>
+        <v>6982692</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8876,7 +8876,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Lunglav på 3 olika sälgar</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986517</v>
+        <v>128986476</v>
       </c>
       <c r="B86" t="n">
-        <v>79297</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6459</v>
+        <v>2081</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518977</v>
+        <v>519017</v>
       </c>
       <c r="R86" t="n">
-        <v>6982833</v>
+        <v>6982756</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9000,10 +9000,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986711</v>
+        <v>128986703</v>
       </c>
       <c r="B87" t="n">
-        <v>80146</v>
+        <v>80148</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>519123</v>
+        <v>518965</v>
       </c>
       <c r="R87" t="n">
-        <v>6982555</v>
+        <v>6982610</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9071,6 +9071,11 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9097,32 +9102,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986464</v>
+        <v>128986517</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>79299</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6459</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9132,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519152</v>
+        <v>518977</v>
       </c>
       <c r="R88" t="n">
-        <v>6982692</v>
+        <v>6982833</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9168,11 +9173,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9202,7 +9202,7 @@
         <v>128986699</v>
       </c>
       <c r="B89" t="n">
-        <v>79631</v>
+        <v>79633</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -1267,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986473</v>
+        <v>128986706</v>
       </c>
       <c r="B8" t="n">
-        <v>57568</v>
+        <v>80148</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518872</v>
+        <v>518979</v>
       </c>
       <c r="R8" t="n">
-        <v>6982457</v>
+        <v>6982499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1364,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986513</v>
+        <v>128986473</v>
       </c>
       <c r="B9" t="n">
-        <v>92138</v>
+        <v>57568</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>760</v>
+        <v>102621</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519097</v>
+        <v>518872</v>
       </c>
       <c r="R9" t="n">
-        <v>6982582</v>
+        <v>6982457</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986706</v>
+        <v>128986494</v>
       </c>
       <c r="B10" t="n">
-        <v>80148</v>
+        <v>57831</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518979</v>
+        <v>519117</v>
       </c>
       <c r="R10" t="n">
-        <v>6982499</v>
+        <v>6982667</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,6 +1532,11 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1558,32 +1563,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986488</v>
+        <v>128986498</v>
       </c>
       <c r="B11" t="n">
-        <v>80148</v>
+        <v>98710</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519036</v>
+        <v>519095</v>
       </c>
       <c r="R11" t="n">
-        <v>6982781</v>
+        <v>6982524</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1655,32 +1660,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986494</v>
+        <v>128986488</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
+        <v>80148</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1695,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519117</v>
+        <v>519036</v>
       </c>
       <c r="R12" t="n">
-        <v>6982667</v>
+        <v>6982781</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1726,11 +1731,6 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986498</v>
+        <v>128986513</v>
       </c>
       <c r="B13" t="n">
-        <v>98710</v>
+        <v>92138</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519095</v>
+        <v>519097</v>
       </c>
       <c r="R13" t="n">
-        <v>6982524</v>
+        <v>6982582</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>91543</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R24" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986716</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519149</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982659</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986700</v>
+        <v>128986716</v>
       </c>
       <c r="B26" t="n">
-        <v>91543</v>
+        <v>80148</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518969</v>
+        <v>519149</v>
       </c>
       <c r="R26" t="n">
-        <v>6982720</v>
+        <v>6982659</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986474</v>
+        <v>128986482</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80148</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518955</v>
+        <v>519112</v>
       </c>
       <c r="R46" t="n">
-        <v>6982588</v>
+        <v>6982533</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986482</v>
+        <v>128986721</v>
       </c>
       <c r="B47" t="n">
         <v>80148</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519112</v>
+        <v>519110</v>
       </c>
       <c r="R47" t="n">
-        <v>6982533</v>
+        <v>6982770</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5182,7 +5182,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986721</v>
+        <v>128986719</v>
       </c>
       <c r="B48" t="n">
         <v>80148</v>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519110</v>
+        <v>519128</v>
       </c>
       <c r="R48" t="n">
-        <v>6982770</v>
+        <v>6982688</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986719</v>
+        <v>128986493</v>
       </c>
       <c r="B49" t="n">
         <v>80148</v>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519128</v>
+        <v>518940</v>
       </c>
       <c r="R49" t="n">
-        <v>6982688</v>
+        <v>6982481</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,7 +5376,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986493</v>
+        <v>128986484</v>
       </c>
       <c r="B50" t="n">
         <v>80148</v>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518940</v>
+        <v>519153</v>
       </c>
       <c r="R50" t="n">
-        <v>6982481</v>
+        <v>6982677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,10 +5473,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986484</v>
+        <v>128986465</v>
       </c>
       <c r="B51" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5484,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519153</v>
+        <v>519109</v>
       </c>
       <c r="R51" t="n">
-        <v>6982677</v>
+        <v>6982756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,6 +5544,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5570,7 +5575,7 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986465</v>
+        <v>128986461</v>
       </c>
       <c r="B52" t="n">
         <v>57727</v>
@@ -5605,10 +5610,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519109</v>
+        <v>519127</v>
       </c>
       <c r="R52" t="n">
-        <v>6982756</v>
+        <v>6982642</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5645,7 +5650,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5672,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986461</v>
+        <v>128986474</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519127</v>
+        <v>518955</v>
       </c>
       <c r="R53" t="n">
-        <v>6982642</v>
+        <v>6982588</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,11 +5748,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -7438,32 +7438,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986460</v>
+        <v>128986504</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>98710</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7473,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519008</v>
+        <v>519130</v>
       </c>
       <c r="R71" t="n">
-        <v>6982491</v>
+        <v>6982767</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,11 +7509,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7540,32 +7535,32 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986504</v>
+        <v>128986460</v>
       </c>
       <c r="B72" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7575,10 +7570,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519130</v>
+        <v>519008</v>
       </c>
       <c r="R72" t="n">
-        <v>6982767</v>
+        <v>6982491</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7611,6 +7606,11 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>79633</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>98710</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R6" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986701</v>
+        <v>128986513</v>
       </c>
       <c r="B7" t="n">
-        <v>80149</v>
+        <v>92140</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2081</v>
+        <v>760</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519098</v>
+        <v>519097</v>
       </c>
       <c r="R7" t="n">
-        <v>6982579</v>
+        <v>6982582</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986706</v>
+        <v>128986498</v>
       </c>
       <c r="B8" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518979</v>
+        <v>519095</v>
       </c>
       <c r="R8" t="n">
-        <v>6982499</v>
+        <v>6982524</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1364,32 +1359,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986473</v>
+        <v>128986701</v>
       </c>
       <c r="B9" t="n">
-        <v>57568</v>
+        <v>80150</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>102621</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>518872</v>
+        <v>519098</v>
       </c>
       <c r="R9" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1435,6 +1430,11 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,10 +1461,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B10" t="n">
-        <v>57831</v>
+        <v>57568</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1472,16 +1472,16 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R10" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1532,11 +1532,6 @@
       <c r="AA10" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1563,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986498</v>
+        <v>128986706</v>
       </c>
       <c r="B11" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519095</v>
+        <v>518979</v>
       </c>
       <c r="R11" t="n">
-        <v>6982524</v>
+        <v>6982499</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1663,7 +1658,7 @@
         <v>128986488</v>
       </c>
       <c r="B12" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1757,32 +1752,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986513</v>
+        <v>128986494</v>
       </c>
       <c r="B13" t="n">
-        <v>92138</v>
+        <v>57831</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>103031</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1787,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519097</v>
+        <v>519117</v>
       </c>
       <c r="R13" t="n">
-        <v>6982582</v>
+        <v>6982667</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1828,6 +1823,11 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1857,7 +1857,7 @@
         <v>128986707</v>
       </c>
       <c r="B14" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986478</v>
+        <v>128986468</v>
       </c>
       <c r="B15" t="n">
-        <v>75145</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518949</v>
+        <v>518944</v>
       </c>
       <c r="R15" t="n">
-        <v>6982601</v>
+        <v>6982537</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,6 +2022,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,32 +2053,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986515</v>
+        <v>128986458</v>
       </c>
       <c r="B16" t="n">
-        <v>80183</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519023</v>
+        <v>518751</v>
       </c>
       <c r="R16" t="n">
-        <v>6982774</v>
+        <v>6982439</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,10 +2155,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986485</v>
+        <v>128986478</v>
       </c>
       <c r="B17" t="n">
-        <v>80148</v>
+        <v>75145</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2166,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519104</v>
+        <v>518949</v>
       </c>
       <c r="R17" t="n">
-        <v>6982762</v>
+        <v>6982601</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2242,32 +2252,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2277,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R18" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2313,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986468</v>
+        <v>128986485</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518944</v>
+        <v>519104</v>
       </c>
       <c r="R19" t="n">
-        <v>6982537</v>
+        <v>6982762</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2449,7 +2449,7 @@
         <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>78800</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986732</v>
+        <v>128986730</v>
       </c>
       <c r="B21" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519137</v>
+        <v>518956</v>
       </c>
       <c r="R21" t="n">
-        <v>6982624</v>
+        <v>6982758</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2614,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2648,7 +2643,7 @@
         <v>128986505</v>
       </c>
       <c r="B22" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2742,10 +2737,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986732</v>
       </c>
       <c r="B23" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2777,10 +2772,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>519137</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982624</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2813,6 +2808,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>91543</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R24" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B25" t="n">
-        <v>80149</v>
+        <v>91545</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3036,7 +3036,7 @@
         <v>128986716</v>
       </c>
       <c r="B26" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3133,7 +3133,7 @@
         <v>128986489</v>
       </c>
       <c r="B27" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986510</v>
+        <v>128986463</v>
       </c>
       <c r="B28" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,16 +3238,16 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519116</v>
+        <v>519129</v>
       </c>
       <c r="R28" t="n">
-        <v>6982762</v>
+        <v>6982658</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,6 +3298,11 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3324,10 +3329,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986492</v>
+        <v>128986510</v>
       </c>
       <c r="B29" t="n">
-        <v>80148</v>
+        <v>56908</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3340,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3364,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>518959</v>
+        <v>519116</v>
       </c>
       <c r="R29" t="n">
-        <v>6982485</v>
+        <v>6982762</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,10 +3426,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986726</v>
+        <v>128986492</v>
       </c>
       <c r="B30" t="n">
-        <v>78800</v>
+        <v>80149</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3437,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3461,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519089</v>
+        <v>518959</v>
       </c>
       <c r="R30" t="n">
-        <v>6982825</v>
+        <v>6982485</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3518,10 +3523,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986463</v>
+        <v>128986726</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3529,21 +3534,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519129</v>
+        <v>519089</v>
       </c>
       <c r="R31" t="n">
-        <v>6982658</v>
+        <v>6982825</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,11 +3594,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3620,10 +3620,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986500</v>
+        <v>128986501</v>
       </c>
       <c r="B32" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519090</v>
+        <v>519091</v>
       </c>
       <c r="R32" t="n">
-        <v>6982633</v>
+        <v>6982620</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986501</v>
+        <v>128986500</v>
       </c>
       <c r="B33" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519091</v>
+        <v>519090</v>
       </c>
       <c r="R33" t="n">
-        <v>6982620</v>
+        <v>6982633</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986728</v>
+        <v>128986467</v>
       </c>
       <c r="B34" t="n">
-        <v>78800</v>
+        <v>57727</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518928</v>
+        <v>518933</v>
       </c>
       <c r="R34" t="n">
-        <v>6982835</v>
+        <v>6982538</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,6 +3885,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3911,32 +3916,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986508</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>98712</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3951,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>518986</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,11 +3987,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986508</v>
+        <v>128986728</v>
       </c>
       <c r="B36" t="n">
-        <v>98710</v>
+        <v>78801</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518986</v>
+        <v>518928</v>
       </c>
       <c r="R36" t="n">
-        <v>6982827</v>
+        <v>6982835</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986713</v>
+        <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519091</v>
+        <v>518740</v>
       </c>
       <c r="R37" t="n">
-        <v>6982582</v>
+        <v>6982426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,6 +4181,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4207,10 +4212,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986723</v>
+        <v>128986713</v>
       </c>
       <c r="B38" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519011</v>
+        <v>519091</v>
       </c>
       <c r="R38" t="n">
-        <v>6982694</v>
+        <v>6982582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,10 +4309,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986710</v>
+        <v>128986723</v>
       </c>
       <c r="B39" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4339,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519088</v>
+        <v>519011</v>
       </c>
       <c r="R39" t="n">
-        <v>6982506</v>
+        <v>6982694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4401,10 +4406,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986457</v>
+        <v>128986710</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,21 +4417,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518740</v>
+        <v>519088</v>
       </c>
       <c r="R40" t="n">
-        <v>6982426</v>
+        <v>6982506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4472,11 +4477,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986509</v>
+        <v>128986708</v>
       </c>
       <c r="B41" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518970</v>
+        <v>518983</v>
       </c>
       <c r="R41" t="n">
-        <v>6982749</v>
+        <v>6982481</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986499</v>
+        <v>128986722</v>
       </c>
       <c r="B42" t="n">
-        <v>98710</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519106</v>
+        <v>518975</v>
       </c>
       <c r="R42" t="n">
-        <v>6982616</v>
+        <v>6982829</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
         <v>128986502</v>
       </c>
       <c r="B43" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986708</v>
+        <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518983</v>
+        <v>519106</v>
       </c>
       <c r="R44" t="n">
-        <v>6982481</v>
+        <v>6982616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986722</v>
+        <v>128986509</v>
       </c>
       <c r="B45" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518975</v>
+        <v>518970</v>
       </c>
       <c r="R45" t="n">
-        <v>6982829</v>
+        <v>6982749</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986482</v>
+        <v>128986474</v>
       </c>
       <c r="B46" t="n">
-        <v>80148</v>
+        <v>80150</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519112</v>
+        <v>518955</v>
       </c>
       <c r="R46" t="n">
-        <v>6982533</v>
+        <v>6982588</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986721</v>
+        <v>128986461</v>
       </c>
       <c r="B47" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519110</v>
+        <v>519127</v>
       </c>
       <c r="R47" t="n">
-        <v>6982770</v>
+        <v>6982642</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,6 +5156,11 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5182,10 +5187,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986719</v>
+        <v>128986465</v>
       </c>
       <c r="B48" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5193,21 +5198,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5222,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519128</v>
+        <v>519109</v>
       </c>
       <c r="R48" t="n">
-        <v>6982688</v>
+        <v>6982756</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5253,6 +5258,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5279,10 +5289,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986493</v>
+        <v>128986719</v>
       </c>
       <c r="B49" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5314,10 +5324,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>518940</v>
+        <v>519128</v>
       </c>
       <c r="R49" t="n">
-        <v>6982481</v>
+        <v>6982688</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,10 +5386,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986484</v>
+        <v>128986493</v>
       </c>
       <c r="B50" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5411,10 +5421,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519153</v>
+        <v>518940</v>
       </c>
       <c r="R50" t="n">
-        <v>6982677</v>
+        <v>6982481</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5473,10 +5483,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986465</v>
+        <v>128986482</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5494,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5518,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519109</v>
+        <v>519112</v>
       </c>
       <c r="R51" t="n">
-        <v>6982756</v>
+        <v>6982533</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,11 +5554,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5575,10 +5580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986461</v>
+        <v>128986721</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5586,21 +5591,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5610,10 +5615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519127</v>
+        <v>519110</v>
       </c>
       <c r="R52" t="n">
-        <v>6982642</v>
+        <v>6982770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5646,11 +5651,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5677,7 +5677,7 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986474</v>
+        <v>128986484</v>
       </c>
       <c r="B53" t="n">
         <v>80149</v>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518955</v>
+        <v>519153</v>
       </c>
       <c r="R53" t="n">
-        <v>6982588</v>
+        <v>6982677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5777,7 +5777,7 @@
         <v>128986490</v>
       </c>
       <c r="B54" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5874,7 +5874,7 @@
         <v>128986717</v>
       </c>
       <c r="B55" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5971,7 +5971,7 @@
         <v>128986481</v>
       </c>
       <c r="B56" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6068,7 +6068,7 @@
         <v>128986514</v>
       </c>
       <c r="B57" t="n">
-        <v>80183</v>
+        <v>80184</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6262,7 +6262,7 @@
         <v>128986486</v>
       </c>
       <c r="B59" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6359,7 +6359,7 @@
         <v>128986718</v>
       </c>
       <c r="B60" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6456,7 +6456,7 @@
         <v>128986715</v>
       </c>
       <c r="B61" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6553,7 +6553,7 @@
         <v>128986724</v>
       </c>
       <c r="B62" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6655,7 +6655,7 @@
         <v>128986705</v>
       </c>
       <c r="B63" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6752,7 +6752,7 @@
         <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6849,7 +6849,7 @@
         <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986479</v>
+        <v>128986466</v>
       </c>
       <c r="B66" t="n">
-        <v>79067</v>
+        <v>57727</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518960</v>
+        <v>519061</v>
       </c>
       <c r="R66" t="n">
-        <v>6982834</v>
+        <v>6982707</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,6 +7014,11 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7040,10 +7045,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986714</v>
+        <v>128986470</v>
       </c>
       <c r="B67" t="n">
-        <v>80148</v>
+        <v>57727</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7056,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7080,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519102</v>
+        <v>518794</v>
       </c>
       <c r="R67" t="n">
-        <v>6982627</v>
+        <v>6982445</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7111,6 +7116,11 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7137,32 +7147,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7172,10 +7182,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R68" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7208,11 +7218,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7244,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986466</v>
+        <v>128986714</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,21 +7255,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7274,10 +7279,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519061</v>
+        <v>519102</v>
       </c>
       <c r="R69" t="n">
-        <v>6982707</v>
+        <v>6982627</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7310,11 +7315,6 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,10 +7341,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986511</v>
+        <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7352,16 +7352,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>518948</v>
+        <v>519008</v>
       </c>
       <c r="R70" t="n">
-        <v>6982848</v>
+        <v>6982491</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,6 +7412,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7438,32 +7443,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986504</v>
+        <v>128986511</v>
       </c>
       <c r="B71" t="n">
-        <v>98710</v>
+        <v>56908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7473,10 +7478,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519130</v>
+        <v>518948</v>
       </c>
       <c r="R71" t="n">
-        <v>6982767</v>
+        <v>6982848</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7535,27 +7540,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986460</v>
+        <v>128986472</v>
       </c>
       <c r="B72" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7570,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519008</v>
+        <v>519067</v>
       </c>
       <c r="R72" t="n">
-        <v>6982491</v>
+        <v>6982817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7606,11 +7611,6 @@
       <c r="AA72" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -7637,32 +7637,32 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128986472</v>
+        <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>57568</v>
+        <v>98712</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -7672,10 +7672,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519067</v>
+        <v>519130</v>
       </c>
       <c r="R73" t="n">
-        <v>6982817</v>
+        <v>6982767</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986503</v>
+        <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>98710</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519118</v>
+        <v>519099</v>
       </c>
       <c r="R74" t="n">
-        <v>6982684</v>
+        <v>6982579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,7 +7831,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986702</v>
+        <v>128986480</v>
       </c>
       <c r="B75" t="n">
         <v>80149</v>
@@ -7842,21 +7842,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519099</v>
+        <v>519008</v>
       </c>
       <c r="R75" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7931,7 +7931,7 @@
         <v>128986491</v>
       </c>
       <c r="B76" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8025,32 +8025,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986480</v>
+        <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>80148</v>
+        <v>98712</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519008</v>
+        <v>519118</v>
       </c>
       <c r="R77" t="n">
-        <v>6982457</v>
+        <v>6982684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8125,7 +8125,7 @@
         <v>128986712</v>
       </c>
       <c r="B78" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8219,10 +8219,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986725</v>
+        <v>128986720</v>
       </c>
       <c r="B79" t="n">
-        <v>78800</v>
+        <v>80149</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8230,21 +8230,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8254,10 +8254,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>519052</v>
+        <v>519130</v>
       </c>
       <c r="R79" t="n">
-        <v>6982433</v>
+        <v>6982756</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8316,10 +8316,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986720</v>
+        <v>128986725</v>
       </c>
       <c r="B80" t="n">
-        <v>80148</v>
+        <v>78801</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -8327,21 +8327,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8351,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519130</v>
+        <v>519052</v>
       </c>
       <c r="R80" t="n">
-        <v>6982756</v>
+        <v>6982433</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8416,7 +8416,7 @@
         <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98710</v>
+        <v>98712</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986727</v>
+        <v>128986464</v>
       </c>
       <c r="B83" t="n">
-        <v>78800</v>
+        <v>57727</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519019</v>
+        <v>519152</v>
       </c>
       <c r="R83" t="n">
-        <v>6982859</v>
+        <v>6982692</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,6 +8678,11 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8704,10 +8709,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986711</v>
+        <v>128986699</v>
       </c>
       <c r="B84" t="n">
-        <v>80148</v>
+        <v>79634</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8720,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519123</v>
+        <v>518952</v>
       </c>
       <c r="R84" t="n">
-        <v>6982555</v>
+        <v>6982811</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,10 +8806,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986464</v>
+        <v>128986476</v>
       </c>
       <c r="B85" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8817,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519152</v>
+        <v>519017</v>
       </c>
       <c r="R85" t="n">
-        <v>6982692</v>
+        <v>6982756</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8872,11 +8877,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986476</v>
+        <v>128986727</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519017</v>
+        <v>519019</v>
       </c>
       <c r="R86" t="n">
-        <v>6982756</v>
+        <v>6982859</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9003,7 +9003,7 @@
         <v>128986703</v>
       </c>
       <c r="B87" t="n">
-        <v>80148</v>
+        <v>80149</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9105,7 +9105,7 @@
         <v>128986517</v>
       </c>
       <c r="B88" t="n">
-        <v>79299</v>
+        <v>79300</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9199,10 +9199,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986699</v>
+        <v>128986711</v>
       </c>
       <c r="B89" t="n">
-        <v>79633</v>
+        <v>80149</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518952</v>
+        <v>519123</v>
       </c>
       <c r="R89" t="n">
-        <v>6982811</v>
+        <v>6982555</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B5" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R5" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,6 +1037,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1063,32 +1068,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>98716</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R6" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1139,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986513</v>
+        <v>128986494</v>
       </c>
       <c r="B7" t="n">
-        <v>92140</v>
+        <v>57831</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>760</v>
+        <v>103031</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519097</v>
+        <v>519117</v>
       </c>
       <c r="R7" t="n">
-        <v>6982582</v>
+        <v>6982667</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1265,7 +1270,7 @@
         <v>128986498</v>
       </c>
       <c r="B8" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1461,32 +1466,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986473</v>
+        <v>128986513</v>
       </c>
       <c r="B10" t="n">
-        <v>57568</v>
+        <v>92144</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>102621</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1501,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518872</v>
+        <v>519097</v>
       </c>
       <c r="R10" t="n">
-        <v>6982457</v>
+        <v>6982582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1752,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986494</v>
+        <v>128986473</v>
       </c>
       <c r="B13" t="n">
-        <v>57831</v>
+        <v>57568</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1763,16 +1768,16 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>103031</v>
+        <v>102621</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -1787,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519117</v>
+        <v>518872</v>
       </c>
       <c r="R13" t="n">
-        <v>6982667</v>
+        <v>6982457</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1823,11 +1828,6 @@
       <c r="AA13" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986468</v>
+        <v>128986515</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518944</v>
+        <v>519023</v>
       </c>
       <c r="R15" t="n">
-        <v>6982537</v>
+        <v>6982774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,10 +2048,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986458</v>
+        <v>128986485</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2064,21 +2059,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518751</v>
+        <v>519104</v>
       </c>
       <c r="R16" t="n">
-        <v>6982439</v>
+        <v>6982762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986478</v>
+        <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>75145</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2166,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518949</v>
+        <v>518751</v>
       </c>
       <c r="R17" t="n">
-        <v>6982601</v>
+        <v>6982439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2226,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2252,32 +2247,32 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986515</v>
+        <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519023</v>
+        <v>518944</v>
       </c>
       <c r="R18" t="n">
-        <v>6982774</v>
+        <v>6982537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2318,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986485</v>
+        <v>128986478</v>
       </c>
       <c r="B19" t="n">
-        <v>80149</v>
+        <v>75145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>1460</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>519104</v>
+        <v>518949</v>
       </c>
       <c r="R19" t="n">
-        <v>6982762</v>
+        <v>6982601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2543,10 +2543,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986730</v>
+        <v>128986732</v>
       </c>
       <c r="B21" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2578,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>518956</v>
+        <v>519137</v>
       </c>
       <c r="R21" t="n">
-        <v>6982758</v>
+        <v>6982624</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,6 +2614,11 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2643,7 +2648,7 @@
         <v>128986505</v>
       </c>
       <c r="B22" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2737,10 +2742,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986732</v>
+        <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2772,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>519137</v>
+        <v>518956</v>
       </c>
       <c r="R23" t="n">
-        <v>6982624</v>
+        <v>6982758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2808,11 +2813,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -2939,7 +2939,7 @@
         <v>128986700</v>
       </c>
       <c r="B25" t="n">
-        <v>91545</v>
+        <v>91549</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986463</v>
+        <v>128986492</v>
       </c>
       <c r="B28" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519129</v>
+        <v>518959</v>
       </c>
       <c r="R28" t="n">
-        <v>6982658</v>
+        <v>6982485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3298,11 +3298,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3329,10 +3324,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986510</v>
+        <v>128986726</v>
       </c>
       <c r="B29" t="n">
-        <v>56908</v>
+        <v>78801</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3340,21 +3335,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3364,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519116</v>
+        <v>519089</v>
       </c>
       <c r="R29" t="n">
-        <v>6982762</v>
+        <v>6982825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3426,10 +3421,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986492</v>
+        <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3437,21 +3432,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3461,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>518959</v>
+        <v>519129</v>
       </c>
       <c r="R30" t="n">
-        <v>6982485</v>
+        <v>6982658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3497,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,10 +3523,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986726</v>
+        <v>128986510</v>
       </c>
       <c r="B31" t="n">
-        <v>78801</v>
+        <v>56908</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,21 +3534,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519089</v>
+        <v>519116</v>
       </c>
       <c r="R31" t="n">
-        <v>6982825</v>
+        <v>6982762</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3620,10 +3620,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986501</v>
+        <v>128986500</v>
       </c>
       <c r="B32" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519091</v>
+        <v>519090</v>
       </c>
       <c r="R32" t="n">
-        <v>6982620</v>
+        <v>6982633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986500</v>
+        <v>128986501</v>
       </c>
       <c r="B33" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519090</v>
+        <v>519091</v>
       </c>
       <c r="R33" t="n">
-        <v>6982633</v>
+        <v>6982620</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3814,10 +3814,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986467</v>
+        <v>128986728</v>
       </c>
       <c r="B34" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3825,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3849,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518933</v>
+        <v>518928</v>
       </c>
       <c r="R34" t="n">
-        <v>6982538</v>
+        <v>6982835</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3885,11 +3885,6 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -3916,32 +3911,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>98712</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3951,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3987,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986728</v>
+        <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>78801</v>
+        <v>98716</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518928</v>
+        <v>518986</v>
       </c>
       <c r="R36" t="n">
-        <v>6982835</v>
+        <v>6982827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986708</v>
+        <v>128986509</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518983</v>
+        <v>518970</v>
       </c>
       <c r="R41" t="n">
-        <v>6982481</v>
+        <v>6982749</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986722</v>
+        <v>128986499</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>98716</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518975</v>
+        <v>519106</v>
       </c>
       <c r="R42" t="n">
-        <v>6982829</v>
+        <v>6982616</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4700,7 +4700,7 @@
         <v>128986502</v>
       </c>
       <c r="B43" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986499</v>
+        <v>128986708</v>
       </c>
       <c r="B44" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519106</v>
+        <v>518983</v>
       </c>
       <c r="R44" t="n">
-        <v>6982616</v>
+        <v>6982481</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986509</v>
+        <v>128986722</v>
       </c>
       <c r="B45" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518970</v>
+        <v>518975</v>
       </c>
       <c r="R45" t="n">
-        <v>6982749</v>
+        <v>6982829</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5085,10 +5085,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986461</v>
+        <v>128986719</v>
       </c>
       <c r="B47" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5096,21 +5096,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519127</v>
+        <v>519128</v>
       </c>
       <c r="R47" t="n">
-        <v>6982642</v>
+        <v>6982688</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5156,11 +5156,6 @@
       <c r="AA47" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC47" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5187,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986465</v>
+        <v>128986493</v>
       </c>
       <c r="B48" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5198,21 +5193,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5222,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519109</v>
+        <v>518940</v>
       </c>
       <c r="R48" t="n">
-        <v>6982756</v>
+        <v>6982481</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5258,11 +5253,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5289,7 +5279,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986719</v>
+        <v>128986482</v>
       </c>
       <c r="B49" t="n">
         <v>80149</v>
@@ -5324,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519128</v>
+        <v>519112</v>
       </c>
       <c r="R49" t="n">
-        <v>6982688</v>
+        <v>6982533</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5386,7 +5376,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986493</v>
+        <v>128986721</v>
       </c>
       <c r="B50" t="n">
         <v>80149</v>
@@ -5421,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>518940</v>
+        <v>519110</v>
       </c>
       <c r="R50" t="n">
-        <v>6982481</v>
+        <v>6982770</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5483,7 +5473,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986482</v>
+        <v>128986484</v>
       </c>
       <c r="B51" t="n">
         <v>80149</v>
@@ -5518,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519112</v>
+        <v>519153</v>
       </c>
       <c r="R51" t="n">
-        <v>6982533</v>
+        <v>6982677</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5580,10 +5570,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986721</v>
+        <v>128986465</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5591,21 +5581,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5615,10 +5605,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519110</v>
+        <v>519109</v>
       </c>
       <c r="R52" t="n">
-        <v>6982770</v>
+        <v>6982756</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5651,6 +5641,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5677,10 +5672,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986484</v>
+        <v>128986461</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5683,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5707,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519153</v>
+        <v>519127</v>
       </c>
       <c r="R53" t="n">
-        <v>6982677</v>
+        <v>6982642</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5748,6 +5743,11 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986497</v>
       </c>
       <c r="B57" t="n">
-        <v>80184</v>
+        <v>98716</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>220787</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>519074</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982512</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986477</v>
+        <v>128986496</v>
       </c>
       <c r="B58" t="n">
-        <v>75033</v>
+        <v>98716</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6428</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519000</v>
+        <v>518776</v>
       </c>
       <c r="R58" t="n">
-        <v>6982781</v>
+        <v>6982502</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986486</v>
+        <v>128986514</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>80184</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6463</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519058</v>
+        <v>519096</v>
       </c>
       <c r="R59" t="n">
-        <v>6982687</v>
+        <v>6982528</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,32 +6356,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986718</v>
+        <v>128986477</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>75033</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>6428</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519135</v>
+        <v>519000</v>
       </c>
       <c r="R60" t="n">
-        <v>6982678</v>
+        <v>6982781</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986715</v>
+        <v>128986486</v>
       </c>
       <c r="B61" t="n">
         <v>80149</v>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519135</v>
+        <v>519058</v>
       </c>
       <c r="R61" t="n">
-        <v>6982624</v>
+        <v>6982687</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986724</v>
+        <v>128986718</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518998</v>
+        <v>519135</v>
       </c>
       <c r="R62" t="n">
-        <v>6982673</v>
+        <v>6982678</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,11 +6621,6 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC62" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6652,7 +6647,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986705</v>
+        <v>128986715</v>
       </c>
       <c r="B63" t="n">
         <v>80149</v>
@@ -6687,10 +6682,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518809</v>
+        <v>519135</v>
       </c>
       <c r="R63" t="n">
-        <v>6982489</v>
+        <v>6982624</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6749,32 +6744,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986497</v>
+        <v>128986724</v>
       </c>
       <c r="B64" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6779,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519074</v>
+        <v>518998</v>
       </c>
       <c r="R64" t="n">
-        <v>6982512</v>
+        <v>6982673</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6820,6 +6815,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986496</v>
+        <v>128986705</v>
       </c>
       <c r="B65" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518776</v>
+        <v>518809</v>
       </c>
       <c r="R65" t="n">
-        <v>6982502</v>
+        <v>6982489</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6943,7 +6943,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986466</v>
+        <v>128986470</v>
       </c>
       <c r="B66" t="n">
         <v>57727</v>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>519061</v>
+        <v>518794</v>
       </c>
       <c r="R66" t="n">
-        <v>6982707</v>
+        <v>6982445</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,7 +7045,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986470</v>
+        <v>128986466</v>
       </c>
       <c r="B67" t="n">
         <v>57727</v>
@@ -7080,10 +7080,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>518794</v>
+        <v>519061</v>
       </c>
       <c r="R67" t="n">
-        <v>6982445</v>
+        <v>6982707</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7120,7 +7120,7 @@
       </c>
       <c r="AC67" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986702</v>
+        <v>128986503</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>98716</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519099</v>
+        <v>519118</v>
       </c>
       <c r="R74" t="n">
-        <v>6982579</v>
+        <v>6982684</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,10 +7831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986480</v>
+        <v>128986702</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7842,21 +7842,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519008</v>
+        <v>519099</v>
       </c>
       <c r="R75" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986491</v>
+        <v>128986480</v>
       </c>
       <c r="B76" t="n">
         <v>80149</v>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518942</v>
+        <v>519008</v>
       </c>
       <c r="R76" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8025,32 +8025,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986503</v>
+        <v>128986491</v>
       </c>
       <c r="B77" t="n">
-        <v>98712</v>
+        <v>80149</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519118</v>
+        <v>518942</v>
       </c>
       <c r="R77" t="n">
-        <v>6982684</v>
+        <v>6982579</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8513,7 +8513,7 @@
         <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>98712</v>
+        <v>98716</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8709,10 +8709,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986699</v>
+        <v>128986476</v>
       </c>
       <c r="B84" t="n">
-        <v>79634</v>
+        <v>80150</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8720,21 +8720,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>229821</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8744,10 +8744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>518952</v>
+        <v>519017</v>
       </c>
       <c r="R84" t="n">
-        <v>6982811</v>
+        <v>6982756</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8806,10 +8806,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986476</v>
+        <v>128986727</v>
       </c>
       <c r="B85" t="n">
-        <v>80150</v>
+        <v>78801</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8817,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>2081</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519017</v>
+        <v>519019</v>
       </c>
       <c r="R85" t="n">
-        <v>6982756</v>
+        <v>6982859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8903,10 +8903,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>78801</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8914,21 +8914,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R86" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,6 +8974,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9000,32 +9005,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986703</v>
+        <v>128986517</v>
       </c>
       <c r="B87" t="n">
-        <v>80149</v>
+        <v>79300</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518965</v>
+        <v>518977</v>
       </c>
       <c r="R87" t="n">
-        <v>6982610</v>
+        <v>6982833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9071,11 +9076,6 @@
       <c r="AA87" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9102,32 +9102,32 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986517</v>
+        <v>128986711</v>
       </c>
       <c r="B88" t="n">
-        <v>79300</v>
+        <v>80149</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>518977</v>
+        <v>519123</v>
       </c>
       <c r="R88" t="n">
-        <v>6982833</v>
+        <v>6982555</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9199,10 +9199,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986711</v>
+        <v>128986699</v>
       </c>
       <c r="B89" t="n">
-        <v>80149</v>
+        <v>79634</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519123</v>
+        <v>518952</v>
       </c>
       <c r="R89" t="n">
-        <v>6982555</v>
+        <v>6982811</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B3" t="n">
-        <v>98716</v>
+        <v>79634</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R3" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986455</v>
+        <v>128986731</v>
       </c>
       <c r="B4" t="n">
-        <v>79634</v>
+        <v>98724</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518927</v>
+        <v>519104</v>
       </c>
       <c r="R4" t="n">
-        <v>6982838</v>
+        <v>6982578</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1071,7 +1071,7 @@
         <v>128986506</v>
       </c>
       <c r="B6" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986494</v>
+        <v>128986498</v>
       </c>
       <c r="B7" t="n">
-        <v>57831</v>
+        <v>98724</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>103031</v>
+        <v>220787</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519117</v>
+        <v>519095</v>
       </c>
       <c r="R7" t="n">
-        <v>6982667</v>
+        <v>6982524</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,11 +1236,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>3st</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1267,32 +1262,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986498</v>
+        <v>128986473</v>
       </c>
       <c r="B8" t="n">
-        <v>98716</v>
+        <v>57568</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>102621</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1297,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>519095</v>
+        <v>518872</v>
       </c>
       <c r="R8" t="n">
-        <v>6982524</v>
+        <v>6982457</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1466,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986513</v>
+        <v>128986706</v>
       </c>
       <c r="B10" t="n">
-        <v>92144</v>
+        <v>80149</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6458</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1501,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519097</v>
+        <v>518979</v>
       </c>
       <c r="R10" t="n">
-        <v>6982582</v>
+        <v>6982499</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1563,7 +1558,7 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986706</v>
+        <v>128986488</v>
       </c>
       <c r="B11" t="n">
         <v>80149</v>
@@ -1598,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518979</v>
+        <v>519036</v>
       </c>
       <c r="R11" t="n">
-        <v>6982499</v>
+        <v>6982781</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1660,32 +1655,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986488</v>
+        <v>128986494</v>
       </c>
       <c r="B12" t="n">
-        <v>80149</v>
+        <v>57831</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>103031</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1695,10 +1690,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519036</v>
+        <v>519117</v>
       </c>
       <c r="R12" t="n">
-        <v>6982781</v>
+        <v>6982667</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1731,6 +1726,11 @@
       <c r="AA12" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1757,32 +1757,32 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986473</v>
+        <v>128986513</v>
       </c>
       <c r="B13" t="n">
-        <v>57568</v>
+        <v>92145</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>102621</v>
+        <v>760</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>518872</v>
+        <v>519097</v>
       </c>
       <c r="R13" t="n">
-        <v>6982457</v>
+        <v>6982582</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986515</v>
+        <v>128986458</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>57727</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519023</v>
+        <v>518751</v>
       </c>
       <c r="R15" t="n">
-        <v>6982774</v>
+        <v>6982439</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,6 +2022,11 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2048,10 +2053,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986485</v>
+        <v>128986468</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2064,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2088,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519104</v>
+        <v>518944</v>
       </c>
       <c r="R16" t="n">
-        <v>6982762</v>
+        <v>6982537</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2119,6 +2124,11 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2145,32 +2155,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986458</v>
+        <v>128986515</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2190,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518751</v>
+        <v>519023</v>
       </c>
       <c r="R17" t="n">
-        <v>6982439</v>
+        <v>6982774</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,11 +2226,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,10 +2252,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986468</v>
+        <v>128986485</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2263,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2287,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518944</v>
+        <v>519104</v>
       </c>
       <c r="R18" t="n">
-        <v>6982537</v>
+        <v>6982762</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,11 +2323,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986729</v>
+        <v>128986732</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>98724</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518952</v>
+        <v>519137</v>
       </c>
       <c r="R20" t="n">
-        <v>6982811</v>
+        <v>6982624</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,6 +2517,11 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2543,10 +2548,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986732</v>
+        <v>128986505</v>
       </c>
       <c r="B21" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2578,10 +2583,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519137</v>
+        <v>519089</v>
       </c>
       <c r="R21" t="n">
-        <v>6982624</v>
+        <v>6982812</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2614,11 +2619,6 @@
       <c r="AA21" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2645,10 +2645,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986505</v>
+        <v>128986730</v>
       </c>
       <c r="B22" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2680,10 +2680,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519089</v>
+        <v>518956</v>
       </c>
       <c r="R22" t="n">
-        <v>6982812</v>
+        <v>6982758</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986729</v>
       </c>
       <c r="B23" t="n">
-        <v>98716</v>
+        <v>78801</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>518952</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982811</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>91550</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R24" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>91549</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986492</v>
+        <v>128986510</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>56908</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6458</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518959</v>
+        <v>519116</v>
       </c>
       <c r="R28" t="n">
-        <v>6982485</v>
+        <v>6982762</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986726</v>
+        <v>128986500</v>
       </c>
       <c r="B29" t="n">
-        <v>78801</v>
+        <v>98724</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519089</v>
+        <v>519090</v>
       </c>
       <c r="R29" t="n">
-        <v>6982825</v>
+        <v>6982633</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986463</v>
+        <v>128986501</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519129</v>
+        <v>519091</v>
       </c>
       <c r="R30" t="n">
-        <v>6982658</v>
+        <v>6982620</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,11 +3492,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,10 +3518,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986510</v>
+        <v>128986463</v>
       </c>
       <c r="B31" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3534,16 +3529,16 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
@@ -3558,10 +3553,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519116</v>
+        <v>519129</v>
       </c>
       <c r="R31" t="n">
-        <v>6982762</v>
+        <v>6982658</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3594,6 +3589,11 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3620,32 +3620,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986500</v>
+        <v>128986492</v>
       </c>
       <c r="B32" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519090</v>
+        <v>518959</v>
       </c>
       <c r="R32" t="n">
-        <v>6982633</v>
+        <v>6982485</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,32 +3717,32 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986501</v>
+        <v>128986726</v>
       </c>
       <c r="B33" t="n">
-        <v>98716</v>
+        <v>78801</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519091</v>
+        <v>519089</v>
       </c>
       <c r="R33" t="n">
-        <v>6982620</v>
+        <v>6982825</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986508</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>518986</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982827</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,11 +3982,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +4008,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B36" t="n">
-        <v>98716</v>
+        <v>57727</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4043,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R36" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4084,6 +4079,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4503,32 +4503,32 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986509</v>
+        <v>128986722</v>
       </c>
       <c r="B41" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518970</v>
+        <v>518975</v>
       </c>
       <c r="R41" t="n">
-        <v>6982749</v>
+        <v>6982829</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,32 +4600,32 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986499</v>
+        <v>128986708</v>
       </c>
       <c r="B42" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>519106</v>
+        <v>518983</v>
       </c>
       <c r="R42" t="n">
-        <v>6982616</v>
+        <v>6982481</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,10 +4697,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986502</v>
+        <v>128986509</v>
       </c>
       <c r="B43" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519145</v>
+        <v>518970</v>
       </c>
       <c r="R43" t="n">
-        <v>6982681</v>
+        <v>6982749</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4794,32 +4794,32 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986708</v>
+        <v>128986499</v>
       </c>
       <c r="B44" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4829,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>518983</v>
+        <v>519106</v>
       </c>
       <c r="R44" t="n">
-        <v>6982481</v>
+        <v>6982616</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4891,32 +4891,32 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986722</v>
+        <v>128986502</v>
       </c>
       <c r="B45" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518975</v>
+        <v>519145</v>
       </c>
       <c r="R45" t="n">
-        <v>6982829</v>
+        <v>6982681</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4988,10 +4988,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986474</v>
+        <v>128986719</v>
       </c>
       <c r="B46" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4999,21 +4999,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5023,10 +5023,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>518955</v>
+        <v>519128</v>
       </c>
       <c r="R46" t="n">
-        <v>6982588</v>
+        <v>6982688</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5085,7 +5085,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986719</v>
+        <v>128986493</v>
       </c>
       <c r="B47" t="n">
         <v>80149</v>
@@ -5120,10 +5120,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>519128</v>
+        <v>518940</v>
       </c>
       <c r="R47" t="n">
-        <v>6982688</v>
+        <v>6982481</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986493</v>
+        <v>128986474</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5193,21 +5193,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518940</v>
+        <v>518955</v>
       </c>
       <c r="R48" t="n">
-        <v>6982481</v>
+        <v>6982588</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986721</v>
+        <v>128986465</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519110</v>
+        <v>519109</v>
       </c>
       <c r="R50" t="n">
-        <v>6982770</v>
+        <v>6982756</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5447,6 +5447,11 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5473,10 +5478,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986484</v>
+        <v>128986461</v>
       </c>
       <c r="B51" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5484,21 +5489,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5513,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519153</v>
+        <v>519127</v>
       </c>
       <c r="R51" t="n">
-        <v>6982677</v>
+        <v>6982642</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,6 +5549,11 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5570,10 +5580,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986465</v>
+        <v>128986721</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5581,21 +5591,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5605,10 +5615,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519109</v>
+        <v>519110</v>
       </c>
       <c r="R52" t="n">
-        <v>6982756</v>
+        <v>6982770</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5641,11 +5651,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5672,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986461</v>
+        <v>128986484</v>
       </c>
       <c r="B53" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5683,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5707,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519127</v>
+        <v>519153</v>
       </c>
       <c r="R53" t="n">
-        <v>6982642</v>
+        <v>6982677</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5743,11 +5748,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6065,32 +6065,32 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986497</v>
+        <v>128986514</v>
       </c>
       <c r="B57" t="n">
-        <v>98716</v>
+        <v>80184</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>220787</v>
+        <v>6463</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6100,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519074</v>
+        <v>519096</v>
       </c>
       <c r="R57" t="n">
-        <v>6982512</v>
+        <v>6982528</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6162,32 +6162,32 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986496</v>
+        <v>128986477</v>
       </c>
       <c r="B58" t="n">
-        <v>98716</v>
+        <v>75033</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6428</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6197,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>518776</v>
+        <v>519000</v>
       </c>
       <c r="R58" t="n">
-        <v>6982502</v>
+        <v>6982781</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6259,32 +6259,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986514</v>
+        <v>128986486</v>
       </c>
       <c r="B59" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6294,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519096</v>
+        <v>519058</v>
       </c>
       <c r="R59" t="n">
-        <v>6982528</v>
+        <v>6982687</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6356,32 +6356,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986477</v>
+        <v>128986718</v>
       </c>
       <c r="B60" t="n">
-        <v>75033</v>
+        <v>80149</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6428</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6391,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519000</v>
+        <v>519135</v>
       </c>
       <c r="R60" t="n">
-        <v>6982781</v>
+        <v>6982678</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6453,7 +6453,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986486</v>
+        <v>128986715</v>
       </c>
       <c r="B61" t="n">
         <v>80149</v>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519058</v>
+        <v>519135</v>
       </c>
       <c r="R61" t="n">
-        <v>6982687</v>
+        <v>6982624</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6550,7 +6550,7 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986718</v>
+        <v>128986724</v>
       </c>
       <c r="B62" t="n">
         <v>80149</v>
@@ -6585,10 +6585,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>519135</v>
+        <v>518998</v>
       </c>
       <c r="R62" t="n">
-        <v>6982678</v>
+        <v>6982673</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6621,6 +6621,11 @@
       <c r="AA62" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>På asp</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6647,7 +6652,7 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986715</v>
+        <v>128986705</v>
       </c>
       <c r="B63" t="n">
         <v>80149</v>
@@ -6682,10 +6687,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>519135</v>
+        <v>518809</v>
       </c>
       <c r="R63" t="n">
-        <v>6982624</v>
+        <v>6982489</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6744,32 +6749,32 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986724</v>
+        <v>128986497</v>
       </c>
       <c r="B64" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6779,10 +6784,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>518998</v>
+        <v>519074</v>
       </c>
       <c r="R64" t="n">
-        <v>6982673</v>
+        <v>6982512</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6815,11 +6820,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På asp</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -6846,32 +6846,32 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986705</v>
+        <v>128986496</v>
       </c>
       <c r="B65" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6881,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518809</v>
+        <v>518776</v>
       </c>
       <c r="R65" t="n">
-        <v>6982489</v>
+        <v>6982502</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7341,27 +7341,27 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986460</v>
+        <v>128986472</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>57568</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519008</v>
+        <v>519067</v>
       </c>
       <c r="R70" t="n">
-        <v>6982491</v>
+        <v>6982817</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,11 +7412,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7443,10 +7438,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986511</v>
+        <v>128986460</v>
       </c>
       <c r="B71" t="n">
-        <v>56908</v>
+        <v>57727</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7454,16 +7449,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7478,10 +7473,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518948</v>
+        <v>519008</v>
       </c>
       <c r="R71" t="n">
-        <v>6982848</v>
+        <v>6982491</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7514,6 +7509,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7540,27 +7540,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986472</v>
+        <v>128986511</v>
       </c>
       <c r="B72" t="n">
-        <v>57568</v>
+        <v>56908</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102621</v>
+        <v>102612</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519067</v>
+        <v>518948</v>
       </c>
       <c r="R72" t="n">
-        <v>6982817</v>
+        <v>6982848</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7640,7 +7640,7 @@
         <v>128986504</v>
       </c>
       <c r="B73" t="n">
-        <v>98716</v>
+        <v>98724</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7734,32 +7734,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986503</v>
+        <v>128986702</v>
       </c>
       <c r="B74" t="n">
-        <v>98716</v>
+        <v>80150</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7769,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519118</v>
+        <v>519099</v>
       </c>
       <c r="R74" t="n">
-        <v>6982684</v>
+        <v>6982579</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7831,10 +7831,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986702</v>
+        <v>128986480</v>
       </c>
       <c r="B75" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7842,21 +7842,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7866,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519099</v>
+        <v>519008</v>
       </c>
       <c r="R75" t="n">
-        <v>6982579</v>
+        <v>6982457</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7928,7 +7928,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986480</v>
+        <v>128986491</v>
       </c>
       <c r="B76" t="n">
         <v>80149</v>
@@ -7963,10 +7963,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>519008</v>
+        <v>518942</v>
       </c>
       <c r="R76" t="n">
-        <v>6982457</v>
+        <v>6982579</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8025,32 +8025,32 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986491</v>
+        <v>128986503</v>
       </c>
       <c r="B77" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>518942</v>
+        <v>519118</v>
       </c>
       <c r="R77" t="n">
-        <v>6982579</v>
+        <v>6982684</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8413,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128986709</v>
+        <v>128986734</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518996</v>
+        <v>518945</v>
       </c>
       <c r="R81" t="n">
-        <v>6982470</v>
+        <v>6982764</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,32 +8510,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128986734</v>
+        <v>128986709</v>
       </c>
       <c r="B82" t="n">
-        <v>98716</v>
+        <v>80149</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518945</v>
+        <v>518996</v>
       </c>
       <c r="R82" t="n">
-        <v>6982764</v>
+        <v>6982470</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986464</v>
+        <v>128986476</v>
       </c>
       <c r="B83" t="n">
-        <v>57727</v>
+        <v>80150</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519152</v>
+        <v>519017</v>
       </c>
       <c r="R83" t="n">
-        <v>6982692</v>
+        <v>6982756</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8678,11 +8678,6 @@
       <c r="AA83" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -8709,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986476</v>
+        <v>128986464</v>
       </c>
       <c r="B84" t="n">
-        <v>80150</v>
+        <v>57727</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8720,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8744,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519017</v>
+        <v>519152</v>
       </c>
       <c r="R84" t="n">
-        <v>6982756</v>
+        <v>6982692</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8780,6 +8775,11 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986455</v>
+        <v>128986731</v>
       </c>
       <c r="B3" t="n">
-        <v>79634</v>
+        <v>98724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>518927</v>
+        <v>519104</v>
       </c>
       <c r="R3" t="n">
-        <v>6982838</v>
+        <v>6982578</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -869,32 +869,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986731</v>
+        <v>128986455</v>
       </c>
       <c r="B4" t="n">
-        <v>98724</v>
+        <v>79634</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>519104</v>
+        <v>518927</v>
       </c>
       <c r="R4" t="n">
-        <v>6982578</v>
+        <v>6982838</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,32 +966,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986459</v>
+        <v>128986506</v>
       </c>
       <c r="B5" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>518814</v>
+        <v>519021</v>
       </c>
       <c r="R5" t="n">
-        <v>6982487</v>
+        <v>6982805</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1037,11 +1037,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1068,32 +1063,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986506</v>
+        <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1103,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>519021</v>
+        <v>518814</v>
       </c>
       <c r="R6" t="n">
-        <v>6982805</v>
+        <v>6982487</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1139,6 +1134,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,32 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986498</v>
+        <v>128986701</v>
       </c>
       <c r="B7" t="n">
-        <v>98724</v>
+        <v>80150</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1200,10 +1200,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519095</v>
+        <v>519098</v>
       </c>
       <c r="R7" t="n">
-        <v>6982524</v>
+        <v>6982579</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1236,6 +1236,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>På gran</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1262,32 +1267,32 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986473</v>
+        <v>128986706</v>
       </c>
       <c r="B8" t="n">
-        <v>57568</v>
+        <v>80149</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>102621</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1297,10 +1302,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518872</v>
+        <v>518979</v>
       </c>
       <c r="R8" t="n">
-        <v>6982457</v>
+        <v>6982499</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1359,10 +1364,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986701</v>
+        <v>128986488</v>
       </c>
       <c r="B9" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1370,21 +1375,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1394,10 +1399,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519098</v>
+        <v>519036</v>
       </c>
       <c r="R9" t="n">
-        <v>6982579</v>
+        <v>6982781</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1430,11 +1435,6 @@
       <c r="AA9" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>På gran</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1461,32 +1461,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986706</v>
+        <v>128986513</v>
       </c>
       <c r="B10" t="n">
-        <v>80149</v>
+        <v>92145</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6458</v>
+        <v>760</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>518979</v>
+        <v>519097</v>
       </c>
       <c r="R10" t="n">
-        <v>6982499</v>
+        <v>6982582</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1558,32 +1558,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986488</v>
+        <v>128986473</v>
       </c>
       <c r="B11" t="n">
-        <v>80149</v>
+        <v>57568</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1593,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>519036</v>
+        <v>518872</v>
       </c>
       <c r="R11" t="n">
-        <v>6982781</v>
+        <v>6982457</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1757,10 +1757,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986513</v>
+        <v>128986498</v>
       </c>
       <c r="B13" t="n">
-        <v>92145</v>
+        <v>98724</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1768,21 +1768,21 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>760</v>
+        <v>220787</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1792,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519097</v>
+        <v>519095</v>
       </c>
       <c r="R13" t="n">
-        <v>6982582</v>
+        <v>6982524</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1951,10 +1951,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986458</v>
+        <v>128986478</v>
       </c>
       <c r="B15" t="n">
-        <v>57727</v>
+        <v>75145</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1962,21 +1962,21 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518751</v>
+        <v>518949</v>
       </c>
       <c r="R15" t="n">
-        <v>6982439</v>
+        <v>6982601</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2022,11 +2022,6 @@
       <c r="AA15" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2053,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986468</v>
+        <v>128986515</v>
       </c>
       <c r="B16" t="n">
-        <v>57727</v>
+        <v>80184</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2088,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>518944</v>
+        <v>519023</v>
       </c>
       <c r="R16" t="n">
-        <v>6982537</v>
+        <v>6982774</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2124,11 +2119,6 @@
       <c r="AA16" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2155,32 +2145,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986515</v>
+        <v>128986485</v>
       </c>
       <c r="B17" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2190,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519023</v>
+        <v>519104</v>
       </c>
       <c r="R17" t="n">
-        <v>6982774</v>
+        <v>6982762</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2252,10 +2242,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B18" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2263,21 +2253,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2287,10 +2277,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R18" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2323,6 +2313,11 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2344,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986478</v>
+        <v>128986468</v>
       </c>
       <c r="B19" t="n">
-        <v>75145</v>
+        <v>57727</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2355,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1460</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2379,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518949</v>
+        <v>518944</v>
       </c>
       <c r="R19" t="n">
-        <v>6982601</v>
+        <v>6982537</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2420,6 +2415,11 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2446,32 +2446,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986732</v>
+        <v>128986729</v>
       </c>
       <c r="B20" t="n">
-        <v>98724</v>
+        <v>78801</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2481,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>519137</v>
+        <v>518952</v>
       </c>
       <c r="R20" t="n">
-        <v>6982624</v>
+        <v>6982811</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2517,11 +2517,6 @@
       <c r="AA20" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2645,7 +2640,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986730</v>
+        <v>128986732</v>
       </c>
       <c r="B22" t="n">
         <v>98724</v>
@@ -2680,10 +2675,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>518956</v>
+        <v>519137</v>
       </c>
       <c r="R22" t="n">
-        <v>6982758</v>
+        <v>6982624</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2716,6 +2711,11 @@
       <c r="AA22" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr">
+        <is>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2742,32 +2742,32 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986729</v>
+        <v>128986730</v>
       </c>
       <c r="B23" t="n">
-        <v>78801</v>
+        <v>98724</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2777,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518952</v>
+        <v>518956</v>
       </c>
       <c r="R23" t="n">
-        <v>6982811</v>
+        <v>6982758</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B24" t="n">
-        <v>91550</v>
+        <v>80150</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R24" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986700</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>91550</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>518969</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982720</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3227,10 +3227,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986510</v>
+        <v>128986492</v>
       </c>
       <c r="B28" t="n">
-        <v>56908</v>
+        <v>80149</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3238,21 +3238,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3262,10 +3262,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>519116</v>
+        <v>518959</v>
       </c>
       <c r="R28" t="n">
-        <v>6982762</v>
+        <v>6982485</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3324,32 +3324,32 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986500</v>
+        <v>128986726</v>
       </c>
       <c r="B29" t="n">
-        <v>98724</v>
+        <v>78801</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3359,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519090</v>
+        <v>519089</v>
       </c>
       <c r="R29" t="n">
-        <v>6982633</v>
+        <v>6982825</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3421,32 +3421,32 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986501</v>
+        <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3456,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519091</v>
+        <v>519129</v>
       </c>
       <c r="R30" t="n">
-        <v>6982620</v>
+        <v>6982658</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,6 +3492,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3518,32 +3523,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986463</v>
+        <v>128986501</v>
       </c>
       <c r="B31" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3553,10 +3558,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519129</v>
+        <v>519091</v>
       </c>
       <c r="R31" t="n">
-        <v>6982658</v>
+        <v>6982620</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3589,11 +3594,6 @@
       <c r="AA31" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3620,32 +3620,32 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986492</v>
+        <v>128986500</v>
       </c>
       <c r="B32" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3655,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>518959</v>
+        <v>519090</v>
       </c>
       <c r="R32" t="n">
-        <v>6982485</v>
+        <v>6982633</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3717,10 +3717,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986726</v>
+        <v>128986510</v>
       </c>
       <c r="B33" t="n">
-        <v>78801</v>
+        <v>56908</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,21 +3728,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6446</v>
+        <v>102612</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3752,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519089</v>
+        <v>519116</v>
       </c>
       <c r="R33" t="n">
-        <v>6982825</v>
+        <v>6982762</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3911,32 +3911,32 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986508</v>
+        <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>98724</v>
+        <v>57727</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518986</v>
+        <v>518933</v>
       </c>
       <c r="R35" t="n">
-        <v>6982827</v>
+        <v>6982538</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,6 +3982,11 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC35" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4008,32 +4013,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986467</v>
+        <v>128986508</v>
       </c>
       <c r="B36" t="n">
-        <v>57727</v>
+        <v>98724</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4043,10 +4048,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518933</v>
+        <v>518986</v>
       </c>
       <c r="R36" t="n">
-        <v>6982538</v>
+        <v>6982827</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4079,11 +4084,6 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986457</v>
+        <v>128986713</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518740</v>
+        <v>519091</v>
       </c>
       <c r="R37" t="n">
-        <v>6982426</v>
+        <v>6982582</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,11 +4181,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4212,7 +4207,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986713</v>
+        <v>128986723</v>
       </c>
       <c r="B38" t="n">
         <v>80149</v>
@@ -4247,10 +4242,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519091</v>
+        <v>519011</v>
       </c>
       <c r="R38" t="n">
-        <v>6982582</v>
+        <v>6982694</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4309,7 +4304,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986723</v>
+        <v>128986710</v>
       </c>
       <c r="B39" t="n">
         <v>80149</v>
@@ -4344,10 +4339,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519011</v>
+        <v>519088</v>
       </c>
       <c r="R39" t="n">
-        <v>6982694</v>
+        <v>6982506</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4406,10 +4401,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986710</v>
+        <v>128986457</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4417,21 +4412,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4441,10 +4436,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519088</v>
+        <v>518740</v>
       </c>
       <c r="R40" t="n">
-        <v>6982506</v>
+        <v>6982426</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4477,6 +4472,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4503,7 +4503,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986722</v>
+        <v>128986708</v>
       </c>
       <c r="B41" t="n">
         <v>80149</v>
@@ -4538,10 +4538,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518975</v>
+        <v>518983</v>
       </c>
       <c r="R41" t="n">
-        <v>6982829</v>
+        <v>6982481</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4600,7 +4600,7 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986708</v>
+        <v>128986722</v>
       </c>
       <c r="B42" t="n">
         <v>80149</v>
@@ -4635,10 +4635,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518983</v>
+        <v>518975</v>
       </c>
       <c r="R42" t="n">
-        <v>6982481</v>
+        <v>6982829</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4697,7 +4697,7 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986509</v>
+        <v>128986502</v>
       </c>
       <c r="B43" t="n">
         <v>98724</v>
@@ -4732,10 +4732,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>518970</v>
+        <v>519145</v>
       </c>
       <c r="R43" t="n">
-        <v>6982749</v>
+        <v>6982681</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4891,7 +4891,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986502</v>
+        <v>128986509</v>
       </c>
       <c r="B45" t="n">
         <v>98724</v>
@@ -4926,10 +4926,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>519145</v>
+        <v>518970</v>
       </c>
       <c r="R45" t="n">
-        <v>6982681</v>
+        <v>6982749</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5182,10 +5182,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986474</v>
+        <v>128986482</v>
       </c>
       <c r="B48" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5193,21 +5193,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5217,10 +5217,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>518955</v>
+        <v>519112</v>
       </c>
       <c r="R48" t="n">
-        <v>6982588</v>
+        <v>6982533</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5279,7 +5279,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986482</v>
+        <v>128986721</v>
       </c>
       <c r="B49" t="n">
         <v>80149</v>
@@ -5314,10 +5314,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519112</v>
+        <v>519110</v>
       </c>
       <c r="R49" t="n">
-        <v>6982533</v>
+        <v>6982770</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5376,10 +5376,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986465</v>
+        <v>128986484</v>
       </c>
       <c r="B50" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5387,21 +5387,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5411,10 +5411,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519109</v>
+        <v>519153</v>
       </c>
       <c r="R50" t="n">
-        <v>6982756</v>
+        <v>6982677</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5447,11 +5447,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5478,7 +5473,7 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986461</v>
+        <v>128986465</v>
       </c>
       <c r="B51" t="n">
         <v>57727</v>
@@ -5513,10 +5508,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519127</v>
+        <v>519109</v>
       </c>
       <c r="R51" t="n">
-        <v>6982642</v>
+        <v>6982756</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5553,7 +5548,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5580,10 +5575,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986721</v>
+        <v>128986461</v>
       </c>
       <c r="B52" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5591,21 +5586,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5615,10 +5610,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519110</v>
+        <v>519127</v>
       </c>
       <c r="R52" t="n">
-        <v>6982770</v>
+        <v>6982642</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5651,6 +5646,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5677,10 +5677,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986484</v>
+        <v>128986474</v>
       </c>
       <c r="B53" t="n">
-        <v>80149</v>
+        <v>80150</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5688,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5712,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>519153</v>
+        <v>518955</v>
       </c>
       <c r="R53" t="n">
-        <v>6982677</v>
+        <v>6982588</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6943,32 +6943,32 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986470</v>
+        <v>128986479</v>
       </c>
       <c r="B66" t="n">
-        <v>57727</v>
+        <v>79068</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6434</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6978,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518794</v>
+        <v>518960</v>
       </c>
       <c r="R66" t="n">
-        <v>6982445</v>
+        <v>6982834</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7014,11 +7014,6 @@
       <c r="AA66" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7045,10 +7040,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986466</v>
+        <v>128986714</v>
       </c>
       <c r="B67" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7056,21 +7051,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7080,10 +7075,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519061</v>
+        <v>519102</v>
       </c>
       <c r="R67" t="n">
-        <v>6982707</v>
+        <v>6982627</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7116,11 +7111,6 @@
       <c r="AA67" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7147,32 +7137,32 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986479</v>
+        <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>79068</v>
+        <v>57727</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6434</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7182,10 +7172,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518960</v>
+        <v>518794</v>
       </c>
       <c r="R68" t="n">
-        <v>6982834</v>
+        <v>6982445</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7218,6 +7208,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7244,10 +7239,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986714</v>
+        <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7255,21 +7250,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7279,10 +7274,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519102</v>
+        <v>519061</v>
       </c>
       <c r="R69" t="n">
-        <v>6982627</v>
+        <v>6982707</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7315,6 +7310,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,27 +7341,27 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986472</v>
+        <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>57568</v>
+        <v>57727</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>102621</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7376,10 +7376,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519067</v>
+        <v>519008</v>
       </c>
       <c r="R70" t="n">
-        <v>6982817</v>
+        <v>6982491</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,6 +7412,11 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7438,10 +7443,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986460</v>
+        <v>128986511</v>
       </c>
       <c r="B71" t="n">
-        <v>57727</v>
+        <v>56908</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7449,16 +7454,16 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>102612</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -7473,10 +7478,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>519008</v>
+        <v>518948</v>
       </c>
       <c r="R71" t="n">
-        <v>6982491</v>
+        <v>6982848</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7509,11 +7514,6 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -7540,27 +7540,27 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986511</v>
+        <v>128986472</v>
       </c>
       <c r="B72" t="n">
-        <v>56908</v>
+        <v>57568</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102612</v>
+        <v>102621</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -7575,10 +7575,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>518948</v>
+        <v>519067</v>
       </c>
       <c r="R72" t="n">
-        <v>6982848</v>
+        <v>6982817</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8413,32 +8413,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128986734</v>
+        <v>128986709</v>
       </c>
       <c r="B81" t="n">
-        <v>98724</v>
+        <v>80149</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8448,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518945</v>
+        <v>518996</v>
       </c>
       <c r="R81" t="n">
-        <v>6982764</v>
+        <v>6982470</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8510,32 +8510,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128986709</v>
+        <v>128986734</v>
       </c>
       <c r="B82" t="n">
-        <v>80149</v>
+        <v>98724</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -8545,10 +8545,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518996</v>
+        <v>518945</v>
       </c>
       <c r="R82" t="n">
-        <v>6982470</v>
+        <v>6982764</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986464</v>
+        <v>128986727</v>
       </c>
       <c r="B84" t="n">
-        <v>57727</v>
+        <v>78801</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519152</v>
+        <v>519019</v>
       </c>
       <c r="R84" t="n">
-        <v>6982692</v>
+        <v>6982859</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8775,11 +8775,6 @@
       <c r="AA84" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC84" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -8806,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986727</v>
+        <v>128986703</v>
       </c>
       <c r="B85" t="n">
-        <v>78801</v>
+        <v>80149</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8817,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8841,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519019</v>
+        <v>518965</v>
       </c>
       <c r="R85" t="n">
-        <v>6982859</v>
+        <v>6982610</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8877,6 +8872,11 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,32 +8903,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986703</v>
+        <v>128986517</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>79300</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518965</v>
+        <v>518977</v>
       </c>
       <c r="R86" t="n">
-        <v>6982610</v>
+        <v>6982833</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,11 +8974,6 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9005,32 +9000,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986517</v>
+        <v>128986711</v>
       </c>
       <c r="B87" t="n">
-        <v>79300</v>
+        <v>80149</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9040,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518977</v>
+        <v>519123</v>
       </c>
       <c r="R87" t="n">
-        <v>6982833</v>
+        <v>6982555</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9102,10 +9097,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986711</v>
+        <v>128986464</v>
       </c>
       <c r="B88" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9113,21 +9108,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9137,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519123</v>
+        <v>519152</v>
       </c>
       <c r="R88" t="n">
-        <v>6982555</v>
+        <v>6982692</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9173,6 +9168,11 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -1951,32 +1951,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986478</v>
+        <v>128986515</v>
       </c>
       <c r="B15" t="n">
-        <v>75145</v>
+        <v>80184</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1460</v>
+        <v>6463</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1986,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>518949</v>
+        <v>519023</v>
       </c>
       <c r="R15" t="n">
-        <v>6982601</v>
+        <v>6982774</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2048,32 +2048,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986515</v>
+        <v>128986485</v>
       </c>
       <c r="B16" t="n">
-        <v>80184</v>
+        <v>80149</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6463</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2083,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519023</v>
+        <v>519104</v>
       </c>
       <c r="R16" t="n">
-        <v>6982774</v>
+        <v>6982762</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2145,10 +2145,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986485</v>
+        <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2156,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2180,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>519104</v>
+        <v>518751</v>
       </c>
       <c r="R17" t="n">
-        <v>6982762</v>
+        <v>6982439</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,6 +2216,11 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2242,7 +2247,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986458</v>
+        <v>128986468</v>
       </c>
       <c r="B18" t="n">
         <v>57727</v>
@@ -2277,10 +2282,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518751</v>
+        <v>518944</v>
       </c>
       <c r="R18" t="n">
-        <v>6982439</v>
+        <v>6982537</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2317,7 +2322,7 @@
       </c>
       <c r="AC18" t="inlineStr">
         <is>
-          <t>Färska ringhack</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2344,10 +2349,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986468</v>
+        <v>128986478</v>
       </c>
       <c r="B19" t="n">
-        <v>57727</v>
+        <v>75145</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2355,21 +2360,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>1460</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2379,10 +2384,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518944</v>
+        <v>518949</v>
       </c>
       <c r="R19" t="n">
-        <v>6982537</v>
+        <v>6982601</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2415,11 +2420,6 @@
       <c r="AA19" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2839,10 +2839,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986475</v>
+        <v>128986716</v>
       </c>
       <c r="B24" t="n">
-        <v>80150</v>
+        <v>80149</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2850,21 +2850,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -2874,10 +2874,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519074</v>
+        <v>519149</v>
       </c>
       <c r="R24" t="n">
-        <v>6982503</v>
+        <v>6982659</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2936,10 +2936,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986700</v>
+        <v>128986475</v>
       </c>
       <c r="B25" t="n">
-        <v>91550</v>
+        <v>80150</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2947,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>2081</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2971,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>518969</v>
+        <v>519074</v>
       </c>
       <c r="R25" t="n">
-        <v>6982720</v>
+        <v>6982503</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3033,10 +3033,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986716</v>
+        <v>128986700</v>
       </c>
       <c r="B26" t="n">
-        <v>80149</v>
+        <v>91550</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3044,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3068,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>519149</v>
+        <v>518969</v>
       </c>
       <c r="R26" t="n">
-        <v>6982659</v>
+        <v>6982720</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -4110,10 +4110,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986713</v>
+        <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>80149</v>
+        <v>57727</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4121,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4145,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>519091</v>
+        <v>518740</v>
       </c>
       <c r="R37" t="n">
-        <v>6982582</v>
+        <v>6982426</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,6 +4181,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4207,7 +4212,7 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>128986723</v>
+        <v>128986713</v>
       </c>
       <c r="B38" t="n">
         <v>80149</v>
@@ -4242,10 +4247,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>519011</v>
+        <v>519091</v>
       </c>
       <c r="R38" t="n">
-        <v>6982694</v>
+        <v>6982582</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4304,7 +4309,7 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986710</v>
+        <v>128986723</v>
       </c>
       <c r="B39" t="n">
         <v>80149</v>
@@ -4339,10 +4344,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519088</v>
+        <v>519011</v>
       </c>
       <c r="R39" t="n">
-        <v>6982506</v>
+        <v>6982694</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4401,10 +4406,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986457</v>
+        <v>128986710</v>
       </c>
       <c r="B40" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4412,21 +4417,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4436,10 +4441,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>518740</v>
+        <v>519088</v>
       </c>
       <c r="R40" t="n">
-        <v>6982426</v>
+        <v>6982506</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4472,11 +4477,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -8607,10 +8607,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986476</v>
+        <v>128986699</v>
       </c>
       <c r="B83" t="n">
-        <v>80150</v>
+        <v>79634</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8618,21 +8618,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>2081</v>
+        <v>229821</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8642,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>519017</v>
+        <v>518952</v>
       </c>
       <c r="R83" t="n">
-        <v>6982756</v>
+        <v>6982811</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8704,10 +8704,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986727</v>
+        <v>128986476</v>
       </c>
       <c r="B84" t="n">
-        <v>78801</v>
+        <v>80150</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8715,21 +8715,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6446</v>
+        <v>2081</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8739,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519019</v>
+        <v>519017</v>
       </c>
       <c r="R84" t="n">
-        <v>6982859</v>
+        <v>6982756</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8801,10 +8801,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986703</v>
+        <v>128986727</v>
       </c>
       <c r="B85" t="n">
-        <v>80149</v>
+        <v>78801</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8812,21 +8812,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8836,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>518965</v>
+        <v>519019</v>
       </c>
       <c r="R85" t="n">
-        <v>6982610</v>
+        <v>6982859</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8872,11 +8872,6 @@
       <c r="AA85" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -8903,32 +8898,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986517</v>
+        <v>128986703</v>
       </c>
       <c r="B86" t="n">
-        <v>79300</v>
+        <v>80149</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6459</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8938,10 +8933,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518977</v>
+        <v>518965</v>
       </c>
       <c r="R86" t="n">
-        <v>6982833</v>
+        <v>6982610</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8974,6 +8969,11 @@
       <c r="AA86" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9000,32 +9000,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986711</v>
+        <v>128986517</v>
       </c>
       <c r="B87" t="n">
-        <v>80149</v>
+        <v>79300</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9035,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>519123</v>
+        <v>518977</v>
       </c>
       <c r="R87" t="n">
-        <v>6982555</v>
+        <v>6982833</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9097,10 +9097,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986464</v>
+        <v>128986711</v>
       </c>
       <c r="B88" t="n">
-        <v>57727</v>
+        <v>80149</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9108,21 +9108,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9132,10 +9132,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519152</v>
+        <v>519123</v>
       </c>
       <c r="R88" t="n">
-        <v>6982692</v>
+        <v>6982555</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9168,11 +9168,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9199,10 +9194,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986699</v>
+        <v>128986464</v>
       </c>
       <c r="B89" t="n">
-        <v>79634</v>
+        <v>57727</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9210,21 +9205,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>229821</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9234,10 +9229,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>518952</v>
+        <v>519152</v>
       </c>
       <c r="R89" t="n">
-        <v>6982811</v>
+        <v>6982692</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9270,6 +9265,11 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-08</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,12 +1153,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
@@ -2148,7 +2148,7 @@
         <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2235,12 +2235,12 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
@@ -2250,7 +2250,7 @@
         <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2337,12 +2337,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -3424,7 +3424,7 @@
         <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3511,12 +3511,12 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
@@ -3914,7 +3914,7 @@
         <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4001,12 +4001,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -4113,7 +4113,7 @@
         <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4200,12 +4200,12 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
@@ -5476,7 +5476,7 @@
         <v>128986465</v>
       </c>
       <c r="B51" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5563,12 +5563,12 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
@@ -5578,7 +5578,7 @@
         <v>128986461</v>
       </c>
       <c r="B52" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5665,12 +5665,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7140,7 +7140,7 @@
         <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7227,12 +7227,12 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
@@ -7242,7 +7242,7 @@
         <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7329,12 +7329,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -7344,7 +7344,7 @@
         <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7431,12 +7431,12 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
@@ -9197,7 +9197,7 @@
         <v>128986464</v>
       </c>
       <c r="B89" t="n">
-        <v>57727</v>
+        <v>57735</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9284,12 +9284,12 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>128986465</v>
       </c>
       <c r="B51" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>128986461</v>
       </c>
       <c r="B52" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>128986464</v>
       </c>
       <c r="B89" t="n">
-        <v>57735</v>
+        <v>57736</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>128986465</v>
       </c>
       <c r="B51" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>128986461</v>
       </c>
       <c r="B52" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>128986464</v>
       </c>
       <c r="B89" t="n">
-        <v>57736</v>
+        <v>57737</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -1066,7 +1066,7 @@
         <v>128986459</v>
       </c>
       <c r="B6" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -2148,7 +2148,7 @@
         <v>128986458</v>
       </c>
       <c r="B17" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2250,7 +2250,7 @@
         <v>128986468</v>
       </c>
       <c r="B18" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -3424,7 +3424,7 @@
         <v>128986463</v>
       </c>
       <c r="B30" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3914,7 +3914,7 @@
         <v>128986467</v>
       </c>
       <c r="B35" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4113,7 +4113,7 @@
         <v>128986457</v>
       </c>
       <c r="B37" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -5476,7 +5476,7 @@
         <v>128986465</v>
       </c>
       <c r="B51" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5578,7 +5578,7 @@
         <v>128986461</v>
       </c>
       <c r="B52" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -7140,7 +7140,7 @@
         <v>128986470</v>
       </c>
       <c r="B68" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7242,7 +7242,7 @@
         <v>128986466</v>
       </c>
       <c r="B69" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7344,7 +7344,7 @@
         <v>128986460</v>
       </c>
       <c r="B70" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -9197,7 +9197,7 @@
         <v>128986464</v>
       </c>
       <c r="B89" t="n">
-        <v>57737</v>
+        <v>57740</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>

--- a/artfynd/A 28153-2025 artfynd.xlsx
+++ b/artfynd/A 28153-2025 artfynd.xlsx
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128986495</v>
+        <v>128986513</v>
       </c>
       <c r="B2" t="n">
-        <v>57831</v>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103031</v>
+        <v>760</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Doftticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Haploporus odorus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Sommerf.) Bondartsev &amp; Singer</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>518776</v>
+        <v>519097</v>
       </c>
       <c r="R2" t="n">
-        <v>6982385</v>
+        <v>6982582</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -760,44 +760,44 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128986731</v>
+        <v>128986700</v>
       </c>
       <c r="B3" t="n">
-        <v>98724</v>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>519104</v>
+        <v>518969</v>
       </c>
       <c r="R3" t="n">
-        <v>6982578</v>
+        <v>6982720</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -857,22 +857,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128986455</v>
+        <v>128986478</v>
       </c>
       <c r="B4" t="n">
-        <v>79634</v>
+        <v>75412</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>1460</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Rosa skärelav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Schismatomma pericleum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Branth &amp; Rostr.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>518927</v>
+        <v>518949</v>
       </c>
       <c r="R4" t="n">
-        <v>6982838</v>
+        <v>6982601</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -954,44 +954,44 @@
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128986506</v>
+        <v>128986474</v>
       </c>
       <c r="B5" t="n">
-        <v>98724</v>
+        <v>80433</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>519021</v>
+        <v>518955</v>
       </c>
       <c r="R5" t="n">
-        <v>6982805</v>
+        <v>6982588</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1051,22 +1051,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>128986459</v>
+        <v>128986475</v>
       </c>
       <c r="B6" t="n">
-        <v>57740</v>
+        <v>80433</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1074,21 +1074,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>2081</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>518814</v>
+        <v>519074</v>
       </c>
       <c r="R6" t="n">
-        <v>6982487</v>
+        <v>6982503</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1134,11 +1134,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1165,10 +1160,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>128986701</v>
+        <v>128986476</v>
       </c>
       <c r="B7" t="n">
-        <v>80150</v>
+        <v>80433</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1200,10 +1195,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>519098</v>
+        <v>519017</v>
       </c>
       <c r="R7" t="n">
-        <v>6982579</v>
+        <v>6982756</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1238,11 +1233,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>På gran</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1255,22 +1245,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>128986706</v>
+        <v>128986701</v>
       </c>
       <c r="B8" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1278,21 +1268,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1302,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>518979</v>
+        <v>519098</v>
       </c>
       <c r="R8" t="n">
-        <v>6982499</v>
+        <v>6982579</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1340,6 +1330,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>På gran</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1352,22 +1347,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>128986488</v>
+        <v>128986702</v>
       </c>
       <c r="B9" t="n">
-        <v>80149</v>
+        <v>80433</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1375,21 +1370,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>2081</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1399,10 +1394,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>519036</v>
+        <v>519099</v>
       </c>
       <c r="R9" t="n">
-        <v>6982781</v>
+        <v>6982579</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1449,44 +1444,44 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>128986513</v>
+        <v>128986477</v>
       </c>
       <c r="B10" t="n">
-        <v>92145</v>
+        <v>75300</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>760</v>
+        <v>6428</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Doftticka</t>
+          <t>Rostfläck</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Haploporus odorus</t>
+          <t>Arthonia vinosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Sommerf.) Bondartsev &amp; Singer</t>
+          <t>Leight.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1496,10 +1491,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>519097</v>
+        <v>519000</v>
       </c>
       <c r="R10" t="n">
-        <v>6982582</v>
+        <v>6982781</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1546,22 +1541,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>128986473</v>
+        <v>128986479</v>
       </c>
       <c r="B11" t="n">
-        <v>57568</v>
+        <v>79351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1569,21 +1564,21 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>102621</v>
+        <v>6434</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1593,10 +1588,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>518872</v>
+        <v>518960</v>
       </c>
       <c r="R11" t="n">
-        <v>6982457</v>
+        <v>6982834</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1643,44 +1638,44 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>128986494</v>
+        <v>128986725</v>
       </c>
       <c r="B12" t="n">
-        <v>57831</v>
+        <v>79084</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>103031</v>
+        <v>6446</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1690,10 +1685,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>519117</v>
+        <v>519052</v>
       </c>
       <c r="R12" t="n">
-        <v>6982667</v>
+        <v>6982433</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1728,11 +1723,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC12" t="inlineStr">
-        <is>
-          <t>3st</t>
-        </is>
-      </c>
       <c r="AD12" t="b">
         <v>0</v>
       </c>
@@ -1745,44 +1735,44 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>128986498</v>
+        <v>128986726</v>
       </c>
       <c r="B13" t="n">
-        <v>98724</v>
+        <v>79084</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1792,10 +1782,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>519095</v>
+        <v>519089</v>
       </c>
       <c r="R13" t="n">
-        <v>6982524</v>
+        <v>6982825</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,22 +1832,22 @@
       <c r="AT13" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>128986707</v>
+        <v>128986727</v>
       </c>
       <c r="B14" t="n">
-        <v>80149</v>
+        <v>79084</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1865,21 +1855,21 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -1889,10 +1879,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>518975</v>
+        <v>519019</v>
       </c>
       <c r="R14" t="n">
-        <v>6982487</v>
+        <v>6982859</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1939,44 +1929,44 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>128986515</v>
+        <v>128986728</v>
       </c>
       <c r="B15" t="n">
-        <v>80184</v>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6463</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -1986,10 +1976,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>519023</v>
+        <v>518928</v>
       </c>
       <c r="R15" t="n">
-        <v>6982774</v>
+        <v>6982835</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2036,22 +2026,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>128986485</v>
+        <v>128986729</v>
       </c>
       <c r="B16" t="n">
-        <v>80149</v>
+        <v>79084</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2059,21 +2049,21 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2083,10 +2073,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>519104</v>
+        <v>518952</v>
       </c>
       <c r="R16" t="n">
-        <v>6982762</v>
+        <v>6982811</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,22 +2123,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>128986458</v>
+        <v>128986480</v>
       </c>
       <c r="B17" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2156,21 +2146,21 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2180,10 +2170,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>518751</v>
+        <v>519008</v>
       </c>
       <c r="R17" t="n">
-        <v>6982439</v>
+        <v>6982457</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2216,11 +2206,6 @@
       <c r="AA17" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2247,10 +2232,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>128986468</v>
+        <v>128986481</v>
       </c>
       <c r="B18" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2258,21 +2243,21 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
@@ -2282,10 +2267,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>518944</v>
+        <v>519067</v>
       </c>
       <c r="R18" t="n">
-        <v>6982537</v>
+        <v>6982461</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2318,11 +2303,6 @@
       <c r="AA18" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2349,10 +2329,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>128986478</v>
+        <v>128986482</v>
       </c>
       <c r="B19" t="n">
-        <v>75145</v>
+        <v>80432</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2360,21 +2340,21 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>1460</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Rosa skärelav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Schismatomma pericleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Branth &amp; Rostr.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2384,10 +2364,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>518949</v>
+        <v>519112</v>
       </c>
       <c r="R19" t="n">
-        <v>6982601</v>
+        <v>6982533</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2434,22 +2414,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>128986729</v>
+        <v>128986484</v>
       </c>
       <c r="B20" t="n">
-        <v>78801</v>
+        <v>80432</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2457,21 +2437,21 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2481,10 +2461,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>518952</v>
+        <v>519153</v>
       </c>
       <c r="R20" t="n">
-        <v>6982811</v>
+        <v>6982677</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2531,44 +2511,44 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>128986505</v>
+        <v>128986485</v>
       </c>
       <c r="B21" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2578,10 +2558,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>519089</v>
+        <v>519104</v>
       </c>
       <c r="R21" t="n">
-        <v>6982812</v>
+        <v>6982762</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2628,44 +2608,44 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>128986732</v>
+        <v>128986486</v>
       </c>
       <c r="B22" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -2675,10 +2655,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>519137</v>
+        <v>519058</v>
       </c>
       <c r="R22" t="n">
-        <v>6982624</v>
+        <v>6982687</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2713,11 +2693,6 @@
           <t>2025-10-08</t>
         </is>
       </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Ca 7 st</t>
-        </is>
-      </c>
       <c r="AD22" t="b">
         <v>0</v>
       </c>
@@ -2730,44 +2705,44 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>128986730</v>
+        <v>128986488</v>
       </c>
       <c r="B23" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2777,10 +2752,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>518956</v>
+        <v>519036</v>
       </c>
       <c r="R23" t="n">
-        <v>6982758</v>
+        <v>6982781</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2827,22 +2802,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>128986716</v>
+        <v>128986489</v>
       </c>
       <c r="B24" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2874,10 +2849,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>519149</v>
+        <v>519023</v>
       </c>
       <c r="R24" t="n">
-        <v>6982659</v>
+        <v>6982778</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -2924,22 +2899,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>128986475</v>
+        <v>128986490</v>
       </c>
       <c r="B25" t="n">
-        <v>80150</v>
+        <v>80432</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2947,21 +2922,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2081</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -2971,10 +2946,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>519074</v>
+        <v>519080</v>
       </c>
       <c r="R25" t="n">
-        <v>6982503</v>
+        <v>6982814</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3021,22 +2996,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>128986700</v>
+        <v>128986491</v>
       </c>
       <c r="B26" t="n">
-        <v>91550</v>
+        <v>80432</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3044,21 +3019,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3068,10 +3043,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>518969</v>
+        <v>518942</v>
       </c>
       <c r="R26" t="n">
-        <v>6982720</v>
+        <v>6982579</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3118,22 +3093,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>128986489</v>
+        <v>128986492</v>
       </c>
       <c r="B27" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3165,10 +3140,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>519023</v>
+        <v>518959</v>
       </c>
       <c r="R27" t="n">
-        <v>6982778</v>
+        <v>6982485</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3215,22 +3190,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>128986492</v>
+        <v>128986493</v>
       </c>
       <c r="B28" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3262,10 +3237,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>518959</v>
+        <v>518940</v>
       </c>
       <c r="R28" t="n">
-        <v>6982485</v>
+        <v>6982481</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3312,22 +3287,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>128986726</v>
+        <v>128986703</v>
       </c>
       <c r="B29" t="n">
-        <v>78801</v>
+        <v>80432</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3335,21 +3310,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3359,10 +3334,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>519089</v>
+        <v>518965</v>
       </c>
       <c r="R29" t="n">
-        <v>6982825</v>
+        <v>6982610</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3397,6 +3372,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Lunglav på 3 olika sälgar</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3409,22 +3389,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>128986463</v>
+        <v>128986705</v>
       </c>
       <c r="B30" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3432,21 +3412,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3456,10 +3436,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>519129</v>
+        <v>518809</v>
       </c>
       <c r="R30" t="n">
-        <v>6982658</v>
+        <v>6982489</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3492,11 +3472,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3523,32 +3498,32 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>128986501</v>
+        <v>128986706</v>
       </c>
       <c r="B31" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3558,10 +3533,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>519091</v>
+        <v>518979</v>
       </c>
       <c r="R31" t="n">
-        <v>6982620</v>
+        <v>6982499</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3608,44 +3583,44 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>128986500</v>
+        <v>128986707</v>
       </c>
       <c r="B32" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3655,10 +3630,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>519090</v>
+        <v>518975</v>
       </c>
       <c r="R32" t="n">
-        <v>6982633</v>
+        <v>6982487</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3705,22 +3680,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>128986510</v>
+        <v>128986708</v>
       </c>
       <c r="B33" t="n">
-        <v>56908</v>
+        <v>80432</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3728,21 +3703,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>102612</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3752,10 +3727,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>519116</v>
+        <v>518983</v>
       </c>
       <c r="R33" t="n">
-        <v>6982762</v>
+        <v>6982481</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -3802,22 +3777,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>128986728</v>
+        <v>128986709</v>
       </c>
       <c r="B34" t="n">
-        <v>78801</v>
+        <v>80432</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3825,21 +3800,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -3849,10 +3824,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>518928</v>
+        <v>518996</v>
       </c>
       <c r="R34" t="n">
-        <v>6982835</v>
+        <v>6982470</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -3899,22 +3874,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>128986467</v>
+        <v>128986710</v>
       </c>
       <c r="B35" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3922,21 +3897,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -3946,10 +3921,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>518933</v>
+        <v>519088</v>
       </c>
       <c r="R35" t="n">
-        <v>6982538</v>
+        <v>6982506</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -3982,11 +3957,6 @@
       <c r="AA35" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC35" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4013,32 +3983,32 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>128986508</v>
+        <v>128986711</v>
       </c>
       <c r="B36" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4048,10 +4018,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>518986</v>
+        <v>519123</v>
       </c>
       <c r="R36" t="n">
-        <v>6982827</v>
+        <v>6982555</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4098,22 +4068,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>128986457</v>
+        <v>128986712</v>
       </c>
       <c r="B37" t="n">
-        <v>57740</v>
+        <v>80432</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4121,21 +4091,21 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4145,10 +4115,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>518740</v>
+        <v>519121</v>
       </c>
       <c r="R37" t="n">
-        <v>6982426</v>
+        <v>6982559</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4181,11 +4151,6 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4215,7 +4180,7 @@
         <v>128986713</v>
       </c>
       <c r="B38" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4297,22 +4262,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>128986723</v>
+        <v>128986714</v>
       </c>
       <c r="B39" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4344,10 +4309,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>519011</v>
+        <v>519102</v>
       </c>
       <c r="R39" t="n">
-        <v>6982694</v>
+        <v>6982627</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4394,22 +4359,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>128986710</v>
+        <v>128986715</v>
       </c>
       <c r="B40" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4441,10 +4406,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>519088</v>
+        <v>519135</v>
       </c>
       <c r="R40" t="n">
-        <v>6982506</v>
+        <v>6982624</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4491,22 +4456,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>128986708</v>
+        <v>128986716</v>
       </c>
       <c r="B41" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4538,10 +4503,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>518983</v>
+        <v>519149</v>
       </c>
       <c r="R41" t="n">
-        <v>6982481</v>
+        <v>6982659</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4588,22 +4553,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>128986722</v>
+        <v>128986717</v>
       </c>
       <c r="B42" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4635,10 +4600,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>518975</v>
+        <v>519151</v>
       </c>
       <c r="R42" t="n">
-        <v>6982829</v>
+        <v>6982660</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4685,44 +4650,44 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>128986502</v>
+        <v>128986718</v>
       </c>
       <c r="B43" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -4732,10 +4697,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>519145</v>
+        <v>519135</v>
       </c>
       <c r="R43" t="n">
-        <v>6982681</v>
+        <v>6982678</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -4782,44 +4747,44 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>128986499</v>
+        <v>128986719</v>
       </c>
       <c r="B44" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -4829,10 +4794,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>519106</v>
+        <v>519128</v>
       </c>
       <c r="R44" t="n">
-        <v>6982616</v>
+        <v>6982688</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -4879,44 +4844,44 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>128986509</v>
+        <v>128986720</v>
       </c>
       <c r="B45" t="n">
-        <v>98724</v>
+        <v>80432</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -4926,10 +4891,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>518970</v>
+        <v>519130</v>
       </c>
       <c r="R45" t="n">
-        <v>6982749</v>
+        <v>6982756</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -4976,22 +4941,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128986719</v>
+        <v>128986721</v>
       </c>
       <c r="B46" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5023,10 +4988,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>519128</v>
+        <v>519110</v>
       </c>
       <c r="R46" t="n">
-        <v>6982688</v>
+        <v>6982770</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5073,22 +5038,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128986493</v>
+        <v>128986722</v>
       </c>
       <c r="B47" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5120,10 +5085,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>518940</v>
+        <v>518975</v>
       </c>
       <c r="R47" t="n">
-        <v>6982481</v>
+        <v>6982829</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5170,22 +5135,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128986482</v>
+        <v>128986723</v>
       </c>
       <c r="B48" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5217,10 +5182,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>519112</v>
+        <v>519011</v>
       </c>
       <c r="R48" t="n">
-        <v>6982533</v>
+        <v>6982694</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5267,22 +5232,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128986721</v>
+        <v>128986724</v>
       </c>
       <c r="B49" t="n">
-        <v>80149</v>
+        <v>80432</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5314,10 +5279,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>519110</v>
+        <v>518998</v>
       </c>
       <c r="R49" t="n">
-        <v>6982770</v>
+        <v>6982673</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5352,6 +5317,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På asp</t>
+        </is>
+      </c>
       <c r="AD49" t="b">
         <v>0</v>
       </c>
@@ -5364,44 +5334,44 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128986484</v>
+        <v>128986517</v>
       </c>
       <c r="B50" t="n">
-        <v>80149</v>
+        <v>79583</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6459</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Barkkornlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Lopadium disciforme</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Flot.) Kullh.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5411,10 +5381,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>519153</v>
+        <v>518977</v>
       </c>
       <c r="R50" t="n">
-        <v>6982677</v>
+        <v>6982833</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5461,44 +5431,44 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128986465</v>
+        <v>128986514</v>
       </c>
       <c r="B51" t="n">
-        <v>57740</v>
+        <v>80467</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5508,10 +5478,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>519109</v>
+        <v>519096</v>
       </c>
       <c r="R51" t="n">
-        <v>6982756</v>
+        <v>6982528</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5544,11 +5514,6 @@
       <c r="AA51" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5575,32 +5540,32 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128986461</v>
+        <v>128986515</v>
       </c>
       <c r="B52" t="n">
-        <v>57740</v>
+        <v>80467</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>6463</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5610,10 +5575,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>519127</v>
+        <v>519023</v>
       </c>
       <c r="R52" t="n">
-        <v>6982642</v>
+        <v>6982774</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -5646,11 +5611,6 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -5677,10 +5637,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>128986474</v>
+        <v>128986457</v>
       </c>
       <c r="B53" t="n">
-        <v>80150</v>
+        <v>57953</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5688,21 +5648,21 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>2081</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -5712,10 +5672,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>518955</v>
+        <v>518740</v>
       </c>
       <c r="R53" t="n">
-        <v>6982588</v>
+        <v>6982426</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -5750,6 +5710,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD53" t="b">
         <v>0</v>
       </c>
@@ -5762,22 +5727,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>128986490</v>
+        <v>128986458</v>
       </c>
       <c r="B54" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5785,21 +5750,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -5809,10 +5774,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>519080</v>
+        <v>518751</v>
       </c>
       <c r="R54" t="n">
-        <v>6982814</v>
+        <v>6982439</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -5847,6 +5812,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD54" t="b">
         <v>0</v>
       </c>
@@ -5859,22 +5829,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>128986717</v>
+        <v>128986459</v>
       </c>
       <c r="B55" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5882,21 +5852,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -5906,10 +5876,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>519151</v>
+        <v>518814</v>
       </c>
       <c r="R55" t="n">
-        <v>6982660</v>
+        <v>6982487</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -5944,6 +5914,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD55" t="b">
         <v>0</v>
       </c>
@@ -5956,22 +5931,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128986481</v>
+        <v>128986460</v>
       </c>
       <c r="B56" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5979,21 +5954,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6003,10 +5978,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>519067</v>
+        <v>519008</v>
       </c>
       <c r="R56" t="n">
-        <v>6982461</v>
+        <v>6982491</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6041,6 +6016,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD56" t="b">
         <v>0</v>
       </c>
@@ -6053,44 +6033,44 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128986514</v>
+        <v>128986461</v>
       </c>
       <c r="B57" t="n">
-        <v>80184</v>
+        <v>57953</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6463</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6100,10 +6080,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>519096</v>
+        <v>519127</v>
       </c>
       <c r="R57" t="n">
-        <v>6982528</v>
+        <v>6982642</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6138,6 +6118,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6150,44 +6135,44 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>128986477</v>
+        <v>128986463</v>
       </c>
       <c r="B58" t="n">
-        <v>75033</v>
+        <v>57953</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6428</v>
+        <v>100109</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Rostfläck</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Arthonia vinosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>Leight.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6197,10 +6182,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>519000</v>
+        <v>519129</v>
       </c>
       <c r="R58" t="n">
-        <v>6982781</v>
+        <v>6982658</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6235,6 +6220,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6247,22 +6237,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128986486</v>
+        <v>128986464</v>
       </c>
       <c r="B59" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6270,21 +6260,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6294,10 +6284,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>519058</v>
+        <v>519152</v>
       </c>
       <c r="R59" t="n">
-        <v>6982687</v>
+        <v>6982692</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6332,6 +6322,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD59" t="b">
         <v>0</v>
       </c>
@@ -6344,22 +6339,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128986718</v>
+        <v>128986465</v>
       </c>
       <c r="B60" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6367,21 +6362,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6391,10 +6386,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>519135</v>
+        <v>519109</v>
       </c>
       <c r="R60" t="n">
-        <v>6982678</v>
+        <v>6982756</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6429,6 +6424,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD60" t="b">
         <v>0</v>
       </c>
@@ -6441,22 +6441,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128986715</v>
+        <v>128986466</v>
       </c>
       <c r="B61" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6464,21 +6464,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6488,10 +6488,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>519135</v>
+        <v>519061</v>
       </c>
       <c r="R61" t="n">
-        <v>6982624</v>
+        <v>6982707</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6526,6 +6526,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD61" t="b">
         <v>0</v>
       </c>
@@ -6538,22 +6543,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128986724</v>
+        <v>128986467</v>
       </c>
       <c r="B62" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6561,21 +6566,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -6585,10 +6590,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>518998</v>
+        <v>518933</v>
       </c>
       <c r="R62" t="n">
-        <v>6982673</v>
+        <v>6982538</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -6625,7 +6630,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På asp</t>
+          <t>Äldre ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -6640,22 +6645,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>128986705</v>
+        <v>128986468</v>
       </c>
       <c r="B63" t="n">
-        <v>80149</v>
+        <v>57953</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6663,21 +6668,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -6687,10 +6692,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>518809</v>
+        <v>518944</v>
       </c>
       <c r="R63" t="n">
-        <v>6982489</v>
+        <v>6982537</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -6725,6 +6730,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Äldre ringhack</t>
+        </is>
+      </c>
       <c r="AD63" t="b">
         <v>0</v>
       </c>
@@ -6737,44 +6747,44 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128986497</v>
+        <v>128986470</v>
       </c>
       <c r="B64" t="n">
-        <v>98724</v>
+        <v>57953</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -6784,10 +6794,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>519074</v>
+        <v>518794</v>
       </c>
       <c r="R64" t="n">
-        <v>6982512</v>
+        <v>6982445</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -6822,6 +6832,11 @@
           <t>2025-10-08</t>
         </is>
       </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Färska ringhack</t>
+        </is>
+      </c>
       <c r="AD64" t="b">
         <v>0</v>
       </c>
@@ -6834,44 +6849,44 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128986496</v>
+        <v>128986510</v>
       </c>
       <c r="B65" t="n">
-        <v>98724</v>
+        <v>57132</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -6881,10 +6896,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>518776</v>
+        <v>519116</v>
       </c>
       <c r="R65" t="n">
-        <v>6982502</v>
+        <v>6982762</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -6931,22 +6946,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>128986479</v>
+        <v>128986511</v>
       </c>
       <c r="B66" t="n">
-        <v>79068</v>
+        <v>57132</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6954,21 +6969,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6434</v>
+        <v>102612</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -6978,10 +6993,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>518960</v>
+        <v>518948</v>
       </c>
       <c r="R66" t="n">
-        <v>6982834</v>
+        <v>6982848</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7028,22 +7043,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128986714</v>
+        <v>128986472</v>
       </c>
       <c r="B67" t="n">
-        <v>80149</v>
+        <v>57794</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7051,21 +7066,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6458</v>
+        <v>102621</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7075,10 +7090,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>519102</v>
+        <v>519067</v>
       </c>
       <c r="R67" t="n">
-        <v>6982627</v>
+        <v>6982817</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7125,22 +7140,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128986470</v>
+        <v>128986473</v>
       </c>
       <c r="B68" t="n">
-        <v>57740</v>
+        <v>57794</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7148,16 +7163,16 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>102621</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Glaucidium passerinum</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -7172,10 +7187,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>518794</v>
+        <v>518872</v>
       </c>
       <c r="R68" t="n">
-        <v>6982445</v>
+        <v>6982457</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7208,11 +7223,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7239,10 +7249,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128986466</v>
+        <v>128986494</v>
       </c>
       <c r="B69" t="n">
-        <v>57740</v>
+        <v>58057</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7250,16 +7260,16 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -7274,10 +7284,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>519061</v>
+        <v>519117</v>
       </c>
       <c r="R69" t="n">
-        <v>6982707</v>
+        <v>6982667</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7314,7 +7324,7 @@
       </c>
       <c r="AC69" t="inlineStr">
         <is>
-          <t>Äldre ringhack</t>
+          <t>3st</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7341,10 +7351,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128986460</v>
+        <v>128986495</v>
       </c>
       <c r="B70" t="n">
-        <v>57740</v>
+        <v>58057</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7352,16 +7362,16 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>103031</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -7376,10 +7386,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>519008</v>
+        <v>518776</v>
       </c>
       <c r="R70" t="n">
-        <v>6982491</v>
+        <v>6982385</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7412,11 +7422,6 @@
       <c r="AA70" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7443,32 +7448,32 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>128986511</v>
+        <v>128986496</v>
       </c>
       <c r="B71" t="n">
-        <v>56908</v>
+        <v>99118</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7478,10 +7483,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>518948</v>
+        <v>518776</v>
       </c>
       <c r="R71" t="n">
-        <v>6982848</v>
+        <v>6982502</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -7528,44 +7533,44 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>128986472</v>
+        <v>128986497</v>
       </c>
       <c r="B72" t="n">
-        <v>57568</v>
+        <v>99118</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>102621</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Sparvuggla</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Glaucidium passerinum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -7575,10 +7580,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>519067</v>
+        <v>519074</v>
       </c>
       <c r="R72" t="n">
-        <v>6982817</v>
+        <v>6982512</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -7625,22 +7630,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128986504</v>
+        <v>128986498</v>
       </c>
       <c r="B73" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7672,10 +7677,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>519130</v>
+        <v>519095</v>
       </c>
       <c r="R73" t="n">
-        <v>6982767</v>
+        <v>6982524</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -7722,44 +7727,44 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>128986702</v>
+        <v>128986499</v>
       </c>
       <c r="B74" t="n">
-        <v>80150</v>
+        <v>99118</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -7769,10 +7774,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>519099</v>
+        <v>519106</v>
       </c>
       <c r="R74" t="n">
-        <v>6982579</v>
+        <v>6982616</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -7819,44 +7824,44 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>128986480</v>
+        <v>128986500</v>
       </c>
       <c r="B75" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -7866,10 +7871,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>519008</v>
+        <v>519090</v>
       </c>
       <c r="R75" t="n">
-        <v>6982457</v>
+        <v>6982633</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -7916,44 +7921,44 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>128986491</v>
+        <v>128986501</v>
       </c>
       <c r="B76" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -7963,10 +7968,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>518942</v>
+        <v>519091</v>
       </c>
       <c r="R76" t="n">
-        <v>6982579</v>
+        <v>6982620</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8013,22 +8018,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>128986503</v>
+        <v>128986502</v>
       </c>
       <c r="B77" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8060,10 +8065,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>519118</v>
+        <v>519145</v>
       </c>
       <c r="R77" t="n">
-        <v>6982684</v>
+        <v>6982681</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8110,44 +8115,44 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>128986712</v>
+        <v>128986503</v>
       </c>
       <c r="B78" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8157,10 +8162,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>519121</v>
+        <v>519118</v>
       </c>
       <c r="R78" t="n">
-        <v>6982559</v>
+        <v>6982684</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8207,44 +8212,44 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>128986720</v>
+        <v>128986504</v>
       </c>
       <c r="B79" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8257,7 +8262,7 @@
         <v>519130</v>
       </c>
       <c r="R79" t="n">
-        <v>6982756</v>
+        <v>6982767</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8304,44 +8309,44 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128986725</v>
+        <v>128986505</v>
       </c>
       <c r="B80" t="n">
-        <v>78801</v>
+        <v>99118</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8351,10 +8356,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>519052</v>
+        <v>519089</v>
       </c>
       <c r="R80" t="n">
-        <v>6982433</v>
+        <v>6982812</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8401,44 +8406,44 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128986709</v>
+        <v>128986506</v>
       </c>
       <c r="B81" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -8448,10 +8453,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>518996</v>
+        <v>519021</v>
       </c>
       <c r="R81" t="n">
-        <v>6982470</v>
+        <v>6982805</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -8498,22 +8503,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128986734</v>
+        <v>128986508</v>
       </c>
       <c r="B82" t="n">
-        <v>98724</v>
+        <v>99118</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8545,10 +8550,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>518945</v>
+        <v>518986</v>
       </c>
       <c r="R82" t="n">
-        <v>6982764</v>
+        <v>6982827</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -8595,44 +8600,44 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128986699</v>
+        <v>128986509</v>
       </c>
       <c r="B83" t="n">
-        <v>79634</v>
+        <v>99118</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>229821</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -8642,10 +8647,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>518952</v>
+        <v>518970</v>
       </c>
       <c r="R83" t="n">
-        <v>6982811</v>
+        <v>6982749</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -8692,44 +8697,44 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128986476</v>
+        <v>128986730</v>
       </c>
       <c r="B84" t="n">
-        <v>80150</v>
+        <v>99118</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>2081</v>
+        <v>220787</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Skrovellav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria scrobiculata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Scop.) DC.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -8739,10 +8744,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>519017</v>
+        <v>518956</v>
       </c>
       <c r="R84" t="n">
-        <v>6982756</v>
+        <v>6982758</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -8789,44 +8794,44 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128986727</v>
+        <v>128986731</v>
       </c>
       <c r="B85" t="n">
-        <v>78801</v>
+        <v>99118</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -8836,10 +8841,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>519019</v>
+        <v>519104</v>
       </c>
       <c r="R85" t="n">
-        <v>6982859</v>
+        <v>6982578</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -8886,44 +8891,44 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128986703</v>
+        <v>128986732</v>
       </c>
       <c r="B86" t="n">
-        <v>80149</v>
+        <v>99118</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -8933,10 +8938,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>518965</v>
+        <v>519137</v>
       </c>
       <c r="R86" t="n">
-        <v>6982610</v>
+        <v>6982624</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -8973,7 +8978,7 @@
       </c>
       <c r="AC86" t="inlineStr">
         <is>
-          <t>Lunglav på 3 olika sälgar</t>
+          <t>Ca 7 st</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -8988,44 +8993,44 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128986517</v>
+        <v>128986734</v>
       </c>
       <c r="B87" t="n">
-        <v>79300</v>
+        <v>99118</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6459</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Barkkornlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Lopadium disciforme</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Flot.) Kullh.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9035,10 +9040,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>518977</v>
+        <v>518945</v>
       </c>
       <c r="R87" t="n">
-        <v>6982833</v>
+        <v>6982764</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9085,22 +9090,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>128986711</v>
+        <v>128986455</v>
       </c>
       <c r="B88" t="n">
-        <v>80149</v>
+        <v>79917</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9108,21 +9113,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>229821</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9132,10 +9137,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>519123</v>
+        <v>518927</v>
       </c>
       <c r="R88" t="n">
-        <v>6982555</v>
+        <v>6982838</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9182,22 +9187,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Marielle Andersson</t>
+          <t>Marielle Löthman</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128986464</v>
+        <v>128986699</v>
       </c>
       <c r="B89" t="n">
-        <v>57740</v>
+        <v>79917</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9205,21 +9210,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>229821</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9229,10 +9234,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>519152</v>
+        <v>518952</v>
       </c>
       <c r="R89" t="n">
-        <v>6982692</v>
+        <v>6982811</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9265,11 +9270,6 @@
       <c r="AA89" t="inlineStr">
         <is>
           <t>2025-10-08</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Färska ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
